--- a/HOOKS_GUIDE.xlsx
+++ b/HOOKS_GUIDE.xlsx
@@ -10,24 +10,28 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الملخص العام" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. خطاف البدء والافتتاح" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. خطاف هندسة السياق" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. خطاف الإشراف العام وتصحيح" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. خطاف خط الإنتاج البرمجي" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. خطاف التكامل الفني" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. خطاف تدقيق الصيانة" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7. خطاف الفحص الأمني" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8. خطاف مراجعة وتحديث المكتب" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9. خطاف الفحص والاختبار التل" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10. خطاف معالجة الأخطاء والأع" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11. خطاف إدارة النسخ والمستود" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12. خطاف تحديث الإنجازات" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13. خطاف الذاكرة المستدامة" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14. خطاف النجاح والتحليل البع" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15. خطاف تنظيم وترتيب الأجهزة" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16. خطاف ترتيب الملفات لمسار " sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17. خطاف إدارة تليجرام" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18. خطاف التدقيق البرمجي الشا" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19. خطاف استكشاف وتكامل الموا" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20. خطاف المزامنة السحابية ال" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. خطاف التخصيص والتصدير الذ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. خطاف الإشراف العام وتصحيح" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. خطاف خط الإنتاج البرمجي" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. خطاف التكامل الفني" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7. خطاف تدقيق الصيانة" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8. خطاف الفحص الأمني" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9. خطاف مراجعة وتحديث المكتب" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10. خطاف الفحص والاختبار التل" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11. خطاف معالجة الأخطاء والأع" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12. خطاف إدارة النسخ والمستود" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13. خطاف تحديث الإنجازات" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14. خطاف الذاكرة المستدامة" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15. خطاف النجاح والتحليل البع" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16. خطاف تنظيم وترتيب الأجهزة" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17. خطاف ترتيب الملفات لمسار " sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18. خطاف إدارة تليجرام" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19. خطاف التدقيق البرمجي الشا" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20. خطاف استكشاف وتكامل الموا" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21. خطاف المزامنة السحابية وا" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22. خطاف قيادة وإدارة الأسطول" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23. خطاف تحويل وأتمتة سكربتات" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24. خطاف أتمتة مسارات العمل و" sheetId="25" state="visible" r:id="rId25"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -469,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -603,12 +607,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>3. خطاف الإشراف العام وتصحيح المسار</t>
+          <t>3. خطاف التخصيص والتصدير الذكي لطاقم المشروع</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>تصحيح مسار, تعديل البرومبت, خطأ بالخطاف, تصحيح خطاف</t>
+          <t>اعتمد سياق المشروع, تخصيص وكلاء المشروع, تصدير بيئة المشروع, تخصيص الوكلاء</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -619,15 +623,55 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>[code-architect], [agent-optimizer], [prompt-engineer]</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>تحليل سياق المشروع وتصدير حزم الوكلاء محلياً مع التنظيف التلقائي (Pruning) وتوليد سكربت المزامنة.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **تحليل سياق المشروع المعتمد (`project_agent_tailor.py`):** فحص ملف `PROJECT_CONTEXT.md` واكتشاف حزم التقنيات المستخدمة (مثل: `android_compose`, `web`, `python_ai`, `construction_survey`).
+  2. **تصدير حزم الوكلاء والمهارات المطلوبة:** نسخ مهارات وبطاقات الوكلاء المتخصصين وحزمة النواة حصرياً إلى مجلد المشروع المحلي `.agents/`.
+  3. **التنظيف التلقائي الصارم للمهارات الفائضة (Pruning Engine):** مسح وحذف أي مهارات أو بطاقات وكلاء غير مستخدمة في المشروع المستهدف، لحماية نافذة السياق (Context Budget) من الهدر بنسبة 100%.
+  4. **توليد قالب المزامنة المحلي (`sync_local_agents.py`):** إنشاء سكربت خفيف داخل المشروع لتمكين المطور من تحديث طاقم المشروع بنقرة زر واحدة مستقبلاً دون المساس بخصوصية المشروع.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>4. خطاف الإشراف العام وتصحيح المسار</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>تصحيح مسار, تعديل البرومبت, خطأ بالخطاف, تصحيح خطاف</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>[prompt-engineer], [agent-optimizer]</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>تصحيح الخطافات الخاطئة والبرومبتات غير الاحترافية وتوجيهها للمسار الصحيح تلقائياً.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
   1. **الرصد التلقائي والإيقاف:** يقوم الوكيل الرئيسي بمراقبة المحادثة. عند استخدام المستخدم لمحفز "تصحيح مسار"، أو عند رصد دخول وكيل في دائرة مفرغة، يتم اعتراض العمل وإيقافه فوراً.
@@ -637,85 +681,43 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>4. خطاف خط الإنتاج البرمجي</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>ابدأ ميزة, تطوير ميزة, اصنع ميزة, إصلاح ميزة</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
- البديل: `Claude Opus 4.6 (Thinking)`</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>[code-architect], [android-kotlin-pro], [jetpack-compose-ui], [code-reviewer-quality], [clean-code-guard], [android-testing], [test-guard]</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>تنفيذ دورة التطوير الكاملة (المعمارية، البرمجة، حراسة الكود النظيف، والفحص والاختبار).</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>* **طريقة العمل والإجراءات:**
-  0. **حقن السياق الإجباري (Mandatory Context Injection):** يُلزم الوكيل الرئيسي بتشغيل أداة حقن السياق (`python .agents/inject_context.py`) وتمرير مخرجاتها كـ `System Alert` أو `&gt; [!WARNING] Mandatory Constraints` في المحادثة قبل بدء أي عمل.
-  1. **التصميم المعماري الهيكلي (`code-architect`):** يبدأ برسم معمارية الميزة وتحديد مواقع وتسمية الملفات الجديدة/المعدلة في الهيكل المناسب (Data/Domain/UI).
-  2. **التدقيق المعماري الصارم وحلقة الـ 7 مرات (7-Iterations Devil's Advocate Loop):** يُمنع منعاً باتاً البدء بكتابة الكود. يجب إدخال خطة التنفيذ (`implementation_plan.md`) في حلقة مراجعة وتدقيق مع "محامي الشيطان" **لـ 7 مرات متتالية** حتى يتم سد كل الثغرات والوصول لنسبة نجاح 99.99% وتأمين قسم `[UNINTENDED SIDE-EFFECTS &amp; LIFECYCLE HAZARDS]` بالكامل قبل السماح بالكتابة.
-  3. **الكتابة البرمجية (Surgical Precision Execution):** يستلم الوكيل `[android-kotlin-pro]` أو `[jetpack-compose-ui]` الخطة المعتمدة ويبدأ بالتنفيذ. **يُحقن الوكيل بالبرومبت الإجباري التالي:** *(يُمنع منعاً باتاً المساس، أو تعديل، أو حذف أي كود حالي في المشروع لا ينص عليه صراحة في خطة التنفيذ. تصرف كجراح دقيق: أضف ميزتك فقط دون إحداث أي تغييرات جانبية في الملفات المفتوحة).*
-  4. **المراجعة وحراسة الكود النظيف (`code-reviewer-quality` + `clean-code-guard`):** يفحص الكود بعد كتابته للتحقق من الاتساق، وخلوه من أخطاء الـ AI الـ 14 الشائعة (ابتلاع الأخطاء، تضخم الدوال، الأكواد المكررة).
-  5. **الأتمتة والاختبار النظيف (`android-testing` + `test-guard`):** ينهي الدورة بكتابة وتشغيل اختبارات الوحدة (JUnit/MockK) وفق معايير `test-guard` للتحقق من سلوك النظام الفعلي وليس فقط الـ Happy Path، وتجنب الـ Mocks المفرطة.</t>
-        </is>
-      </c>
-    </row>
     <row r="6">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>5. خطاف التكامل الفني</t>
+          <t>5. خطاف خط الإنتاج البرمجي</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>ربط API, تكامل خارجي</t>
+          <t>ابدأ ميزة, تطوير ميزة, اصنع ميزة, إصلاح ميزة</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 3.7 Flash (High)` 
- البديل: `Claude Sonnet 4.6 (Thinking)`</t>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Claude Opus 4.6 (Thinking)`</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>[devops-deployer], [backend-architect]</t>
+          <t>[code-architect], [ui-ux-pro-max], [clean-code-guard], [test-guard]</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>ربط وتكامل الخدمات الخارجية بعد مراجعة وثائقها الرسمية وتأمين المتغيرات.</t>
+          <t>تنفيذ دورة التطوير الكاملة (المعمارية، الذكاء التصميمي، البرمجة، حراسة الكود النظيف، والفحص والاختبار).</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  1. **قراءة الوثائق:** يقرأ الوكيل `[devops-deployer]` وثائق الـ API الخارجية الرسمية المدخلة قبل البدء بالدمج.
-  2. **تحصين الانقطاع (API FAULT TOLERANCE CHECK):** يُمنع الدمج دون بناء `Interceptor` لمعالجة انقطاع الشبكة وإعادة المحاولة (Retry Mechanism)، وتغليف الردود بـ `Result&lt;T&gt;` أو `ErrorMapper` لمعالجة أخطاء HTTP (401, 404, 500).
-  3. **توليد الـ Wrapper:** عزل منطق التكامل في كلاسات مغلفة منفصلة لتجنب تشتيت الكود الأساسي للمشروع وضمان التخزين المؤقت (Offline-First).
-  4. **حماية البيئة:** التأكد من عدم كتابة أي كود يحتوي على مفاتيح سرية (API Keys) في مستودع الكود وتخزينها في متغيرات البيئة فقط.</t>
+  1. **التصميم الهيكلي والذكاء التصميمي (`code-architect` + `ui-ux-pro-max`):** تحديد المعمارية المناسبة، واستدعاء محرك الاستدلال التصميمي لتحديد نمط الواجهات (Style)، باليت الألوان الدلالية، والخطوط وقواعد سهولة الوصول بدقة قبل كتابة أي واجهة.
+  2. **التدقيق المعماري الصارم (Devil's Advocate Audit):** مراجعة الخطة وكشف الثغرات وحالات الحافة لمنع الآثار الجانبية.
+  3. **الكتابة البرمجية والتنفيذ:** كتابة الكود وبناء الواجهات وقواعد البيانات محلياً.
+  4. **المراجعة وضمان الجودة (`clean-code-guard` + `test-guard`):** فحص الكود للأمان، الأداء، والتوافق مع المعايير.</t>
         </is>
       </c>
     </row>
@@ -725,36 +727,36 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>6. خطاف تدقيق الصيانة</t>
+          <t>6. خطاف التكامل الفني</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>تدقيق صيانة, مراجعة DRY, كود نظيف</t>
+          <t>ربط API, تكامل خارجي</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
- البديل: `Gemini 3.7 Flash (High)`</t>
+          <t>الأساسي: `Gemini 3.7 Flash (High)` 
+ البديل: `Claude Sonnet 4.6 (Thinking)`</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>[code-reviewer-quality], [clean-code-guard], [performance-optimizer]</t>
+          <t>[devops-deployer], [backend-architect]</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>مراجعة الكود البرمجي بانتظام لمنع التكرار وتراكم الديون التقنية وتطبيق معايير الكود النظيف.</t>
+          <t>ربط وتكامل الخدمات الخارجية بعد مراجعة وثائقها الرسمية وتأمين المتغيرات.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  1. **فحص الكود النظيف والمكرر:** استدعاء الوكيل `[code-reviewer-quality]` و `[clean-code-guard]` لمسح الملفات والتحقق من عدم وجود دوال أو منطق مكرر (تطبيق مبدأ DRY/KISS/YAGNI) والحد من التعقيد الحسابي.
-  2. **فحص Recomposition والأداء:** قياس كفاءة الرسم وإعاقات الأداء في Compose بواسطة `[performance-optimizer]`.
-  3. **إنشاء تقرير Refactoring:** تزويد المطور بقائمة تعديلات مقترحة لتسهيل القراءة وضغط الكود وحذف الأكواد الميتة (Dead Code).</t>
+  1. **قراءة الوثائق:** يقرأ الوكيل `[devops-deployer]` وثائق الـ API الخارجية الرسمية المدخلة قبل البدء بالدمج.
+  2. **تحصين الانقطاع (API FAULT TOLERANCE CHECK):** بناء Interceptor لمعالجة انقطاع الشبكة وإعادة المحاولة وتأمين المفاتيح في متغيرات البيئة.
+  3. **توليد الـ Wrapper:** عزل منطق التكامل في كلاسات مغلفة منفصلة لتجنب تشتيت الكود الأساسي للمشروع.</t>
         </is>
       </c>
     </row>
@@ -764,36 +766,35 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>7. خطاف الفحص الأمني</t>
+          <t>7. خطاف تدقيق الصيانة</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>فحص أمني, مراجعة أمان</t>
+          <t>تدقيق صيانة, مراجعة DRY, كود نظيف</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
           <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
- البديل: `Claude Opus 4.6 (Thinking)`</t>
+ البديل: `Gemini 3.7 Flash (High)`</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>[security-auditor], [code-reviewer-quality]</t>
+          <t>[code-reviewer-quality], [clean-code-guard], [performance-optimizer]</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>مراجعة ثغرات الأمان والتحقق من صحة المدخلات وتشفير البيانات وتأمين الوصول.</t>
+          <t>مراجعة الكود البرمجي بانتظام لمنع التكرار وتراكم الديون التقنية وتطبيق معايير الكود النظيف.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  1. **مصفوفة الثغرات الصارمة (VULNERABILITY MATRIX):** مسح إجباري لـ AndroidManifest للبحث عن المكونات المكشوفة (`Exported=true`)، وتسريب البيانات عبر `Intents` (Intent Hijacking)، وقواعد `ProGuard`.
-  2. **التحقق من صحة المدخلات:** التأكد من وجود معالجة وفحص صريح لكل المدخلات والطلبات الخارجية قبل تمريرها لطبقة البيانات.
-  3. **فحص تشفير البيانات:** التحقق من تشفير البيانات الحساسة و `SharedPreferences` والجلسات وحمايتها محلياً وسحابياً (إلزام إخراج تقرير يؤكد الفحص).</t>
+  1. **فحص الكود النظيف والمكرر:** استدعاء الوكيل `[code-reviewer-quality]` و `[clean-code-guard]` لمسح الملفات والتحقق من عدم وجود دوال مكررة (تطبيق DRY/KISS/YAGNI).
+  2. **فحص Recomposition والأداء:** قياس كفاءة الرسم وإعاقات الأداء في Compose بواسطة `[performance-optimizer]`.</t>
         </is>
       </c>
     </row>
@@ -803,44 +804,35 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>8. خطاف مراجعة وتحديث المكتبات والنماذج</t>
+          <t>8. خطاف الفحص الأمني</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>تحديث الاعتماديات, تحديث المكتبات, تحديث النماذج, معايرة النماذج, update models</t>
+          <t>فحص أمني, مراجعة أمان</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 3.7 Flash (High)` 
- البديل: `Gemini 3.6 Flash (Medium)`</t>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Claude Opus 4.6 (Thinking)`</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>[github-talent-scout], [code-architect], [agent-optimizer]</t>
+          <t>[security-auditor], [code-reviewer-quality]</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>فحص ملفات Gradle وتحديث المكتبات، والتحقق التلقائي عبر الإنترنت (antigravity.google) لتحديث مصفوفة النماذج ودليل hooks_user_guide.md دون لقطات شاشة.</t>
+          <t>مراجعة ثغرات الأمان والتحقق من صحة المدخلات وتشفير البيانات وتأمين الوصول.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  1. **فحص إصدارات المكتبات:** مسح ملفات `build.gradle.kts` ومقارنة إصدارات المكتبات الحالية بأحدث الإصدارات المستقرة.
-  2. **الاستكشاف والمعايرة التلقائية للنماذج عبر الإنترنت (Online Model Discovery):**
-     - عند كتابة محفز `"تحديث النماذج"` أو `"معايرة النماذج"`، يقوم الوكيل `[agent-optimizer]` بالاستعلام الفوري عبر الإنترنت من المصادر الرسمية:
-       - 🌐 بوابة Google Antigravity الرسمية: `https://antigravity.google`
-       - 🌐 مدونة مطوري جوجل: `https://google.dev` و `https://blog.google`
-       - 🌐 دليل وثائق Anthropic: `https://docs.anthropic.com`
-     - يتم استخراج قائمة النماذج الفعالة في المحرر (مثل `Gemini 3.7 Flash`, `Claude Sonnet 4.6 (Thinking)`).
-  3. **التحديث والمزامنة الشاملة:**
-     - تحديث مصفوفة النماذج في `HOOKS_GUIDE.md` ودليل مسار العمل `hooks_user_guide.md`.
-     - تشغيل السكربتات لتحديث ملف الإكسيل `HOOKS_GUIDE.xlsx` وتطبيق مكتبة الأوامر HTML.
-     - تشغيل `sync_global_ecosystem.py` ورفع التحديثات لـ GitHub تلقائياً.</t>
+  1. **مصفوفة الثغرات الصارمة (VULNERABILITY MATRIX):** مسح إجباري لـ AndroidManifest والمكونات المكشوفة وتسريب البيانات.
+  2. **التحقق من صحة المدخلات وتشفير البيانات:** فحص تشفير البيانات الحساسة والجلسات وتأمين الوصول محلياً وسحابياً.</t>
         </is>
       </c>
     </row>
@@ -850,37 +842,35 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>9. خطاف الفحص والاختبار التلقائي</t>
+          <t>9. خطاف مراجعة وتحديث المكتبات والنماذج</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>قم بالاختبار, جاهز للتجربة</t>
+          <t>تحديث الاعتماديات, تحديث المكتبات, تحديث النماذج, معايرة النماذج, update models</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
- البديل: `Gemini 3.7 Flash (High)`</t>
+          <t>الأساسي: `Gemini 3.7 Flash (High)` 
+ البديل: `Gemini 3.6 Flash (Medium)`</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>[android-testing], [test-guard], [code-reviewer-quality]</t>
+          <t>[github-talent-scout], [code-architect], [agent-optimizer]</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>تشغيل اختبارات الوحدة وفحص جودة الكود واختبار السلوك الفعلي بدون Mock مفرط.</t>
+          <t>فحص ملفات Gradle وتحديث المكتبات، والتحقق التلقائي عبر الإنترنت (antigravity.google) لتحديث مصفوفة النماذج ودليل hooks_user_guide.md دون لقطات شاشة.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  1. **التقمص (Persona):** يتصرف الوكيل كمدير فحص جودة صارم (Pre-Flight Inspector &amp; Senior DevOps QA). بصرامة تامة وبدون أي مجاملات.
-  2. **حراسة الاختبارات (`test-guard`):** التحقق من أن الاختبارات تفحص سلوك النظام الفعلي ومخرجاته القابلة للملاحظة، ومنع الاختبارات الوهمية (Tautological Tests) والـ Mocks الزائدة.
-  3. **قاعدة التغطية الإجبارية (TEST COVERAGE MANDATE):** يُرفض أي اختبار يغطي مسار النجاح فقط (Happy Path). يجب كتابة اختبار للنجاح، الفشل، والحالات الطرفية (مثل: Network Off، Configuration Change).
-  4. **تقرير الفحص الصارم:** تزويد المطور بتقرير يحاكي المطالبة القياسية: `[BLOCKERS]`, `[WARNINGS]`, `[PRE-FLIGHT FIXES]`, `[GO / NO-GO]`.</t>
+  1. **فحص إصدارات المكتبات:** مسح ملفات `build.gradle.kts` ومقارنة إصدارات المكتبات الحالية بأحدث الإصدارات المستقرة.
+  2. **الاستكشاف والمعايرة التلقائية للنماذج عبر الإنترنت (Online Model Discovery):** الاستعلام الفوري عبر المصادر الرسمية (antigravity.google, docs.anthropic.com) ومعايرة مصفوفة النماذج.</t>
         </is>
       </c>
     </row>
@@ -890,12 +880,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>10. خطاف معالجة الأخطاء والأعطال</t>
+          <t>10. خطاف الفحص والاختبار التلقائي</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>حدث خطأ, التطبيق توقف, Crash</t>
+          <t>قم بالاختبار, جاهز للتجربة</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -906,20 +896,19 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>[debugger]</t>
+          <t>[android-testing], [test-guard], [code-reviewer-quality]</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>تحليل سجلات الأخطاء والـ Stack Trace وعزل الكود المسبب للمشكلة وإصلاحه.</t>
+          <t>تشغيل اختبارات الوحدة وفحص جودة الكود واختبار السلوك الفعلي بدون Mock مفرط.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  1. **تحليل الـ Stack Trace:** قراءة السجلات بدقة وتحديد السطر المسبب للخلل.
-  2. **عزل المشكلة:** حصر الكود المسبب للأخطاء لمعرفة إن كان يتعلق بالشبكة، قاعدة البيانات، أو دورة حياة المكونات.
-  3. **اقتراح وتثبيت الحل:** تطبيق التعديل الأدنى الكافي لحل المشكلة مع حماية الأجزاء الأخرى من النظام.</t>
+  1. **حراسة الاختبارات (`test-guard`):** التحقق من أن الاختبارات تفحص سلوك النظام الفعلي ومنع Mocks الوهمية.
+  2. **قاعدة التغطية الإجبارية:** اختبار مسار النجاح، الفشل، والحالات الطرفية (Network Off, Lifecycle).</t>
         </is>
       </c>
     </row>
@@ -929,36 +918,34 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>11. خطاف إدارة النسخ والمستودعات</t>
+          <t>11. خطاف معالجة الأخطاء والأعطال</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>نظم جيت, ارفع لجيتهاب, تحديث المستودع, git commit</t>
+          <t>حدث خطأ, التطبيق توقف, Crash</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 3.7 Flash (High)` 
- البديل: `Gemini 3.6 Flash (Medium)`</t>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>[git-github-manager]</t>
+          <t>[debugger]</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>تهيئة المشاريع الجديدة على Git، إدارة التفرعات، وحل تعارضات الدمج ورفعها لـ GitHub بشكل نظيف.</t>
+          <t>تحليل سجلات الأخطاء والـ Stack Trace وعزل الكود المسبب للمشكلة وإصلاحه.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  1. **التحقق من حالة المستودع:** فحص حالة Git باستخدام `git status` ومعرفة الملفات المعدلة والمحذوفة والجديدة.
-  2. **التنظيم والتصنيف:** مساعدة المطور في فرز الملفات، واستثناء الملفات غير الضرورية (تحديث `.gitignore`).
-  3. **التنفيذ والرفع:** كتابة رسائل Commit احترافية وواضحة، وإنشاء فروع عند الحاجة (Branching)، وحل تعارضات الدمج، ثم دفع التغييرات إلى GitHub بأمان.</t>
+  1. **تحليل الـ Stack Trace:** قراءة السجلات بدقة وتحديد السطر المسبب للخلل وعزله وإصلاحه بأقل تعديل كافٍ.</t>
         </is>
       </c>
     </row>
@@ -968,37 +955,35 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>12. خطاف تحديث الإنجازات</t>
+          <t>12. خطاف إدارة النسخ والمستودعات</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>حدث الإنجازات, تحديث README, وثق الإنجازات</t>
+          <t>نظم جيت, ارفع لجيتهاب, تحديث المستودع, git commit</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
           <t>الأساسي: `Gemini 3.7 Flash (High)` 
- البديل: `Claude Sonnet 4.6 (Thinking)`</t>
+ البديل: `Gemini 3.6 Flash (Medium)`</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>[git-github-manager], [docs-guard]</t>
+          <t>[git-github-manager]</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>صياغة التعديلات كإنجازات ومطابقتها برمجياً وتحديث README.md و hooks_user_guide.md ثم الرفع لـ GitHub.</t>
+          <t>تهيئة المشاريع الجديدة على Git، إدارة التفرعات، وحل تعارضات الدمج ورفعها لـ GitHub بشكل نظيف.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  1. **قراءة السجل والذاكرة:** مراجعة التغييرات الأخيرة في الملفات وقراءة `MEMORY_STORE.md` لاستخلاص ما تم إنجازه.
-  2. **مطابقة التوثيق (`docs-guard`):** مطابقة كل رمز برمجي أو مسار أو دالة مذكورة في التوثيق مع الكود الحقيقي لمنع أي تباين أو اختلاق (Docs-vs-Code Drift).
-  3. **صياغة الإنجازات وتحديث التوثيق:** كتابة الإنجازات بنسق احترافي كنقاط موجزة، وتحديث ملف `README.md` وملف [`hooks_user_guide.md`](file:///f:/AI%20PROJECTS/Blind%20App/hooks_user_guide.md).
-  4. **الرفع التلقائي (Commit &amp; Push):** إضافة التعديلات وإجراء الحفظ، ثم الرفع التلقائي إلى GitHub مباشرة كخطوة نهائية متصلة.</t>
+  1. **التحقق من حالة المستودع:** فحص حالة Git واستثناء الملفات غير الضرورية في `.gitignore`.
+  2. **التنفيذ والرفع:** كتابة رسائل Commit احترافية وحل التعارضات ودفع التغييرات إلى GitHub.</t>
         </is>
       </c>
     </row>
@@ -1008,38 +993,34 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>13. خطاف الذاكرة المستدامة</t>
+          <t>13. خطاف تحديث الإنجازات</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>حفظ ذاكرة, تحديث السياق, سجّل هذا</t>
+          <t>حدث الإنجازات, تحديث README, وثق الإنجازات</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
- البديل: `GPT-OSS 120B (Medium)`</t>
+          <t>الأساسي: `Gemini 3.7 Flash (High)` 
+ البديل: `Claude Sonnet 4.6 (Thinking)`</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>[persistent-memory-engine]</t>
+          <t>[git-github-manager], [docs-guard]</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>التقاط الدروس والقرارات وتخزينها في MEMORY_STORE.md وتصديرها للوكلاء.</t>
+          <t>صياغة التعديلات كإنجازات ومطابقتها برمجياً وتحديث README.md و hooks_user_guide.md ثم الرفع لـ GitHub.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  1. **فلترة وتدقيق الدروس (LESSON VALIDATION):** يُمنع تسجيل معلومات بديهية أو عامة. يجب أن تكون الذكريات مركزة على القواعد المعمارية الجديدة، حيل تقنية فريدة، أو تحذيرات من أخطاء مكررة. يجب تضمين قسم `[ANTI-PATTERN AVOIDED]` لكل درس لمنع تكرار الخطأ.
-  2. **التقاط السياق (Capture):** يقوم الوكيل `[persistent-memory-engine]` بتحليل الجلسة الحالية لاستخراج القرارات المعمارية العميقة والحلول.
-  3. **التخزين الهيكلي (Store):** كتابة الذكريات المستخرجة في `MEMORY_STORE.md` بصيغة YAML الموحدة مع التصنيف بالوسوم والتوقيت.
-  4. **التصدير الانتقائي (Export):** تحديث حزمة السياق لكل وكيل حسب بروتوكول التصدير في `MEMORY_EXPORT_PROTOCOL.md`.
-  5. **التنقيح (Prune):** مراجعة الذكريات القديمة وحذف المتقادمة أو المتناقضة.</t>
+  1. **قراءة السجل ومطابقة التوثيق (`docs-guard`):** مراجعة التغييرات الأخيرة وصياغة الإنجازات وتحديث `README.md`.</t>
         </is>
       </c>
     </row>
@@ -1049,37 +1030,34 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>14. خطاف النجاح والتحليل البعدي</t>
+          <t>14. خطاف الذاكرة المستدامة</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>تم بنجاح, انتهى المشروع بنجاح</t>
+          <t>حفظ ذاكرة, تحديث السياق, سجّل هذا</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
           <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
- البديل: `Gemini 3.7 Flash (High)`</t>
+ البديل: `GPT-OSS 120B (Medium)`</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>[agent-optimizer]</t>
+          <t>[persistent-memory-engine]</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>إجراء تحليل بعدي للمشروع وتحديث سجل التعلم وسد الثغرات البرمجية.</t>
+          <t>التقاط الدروس والقرارات وتخزينها في MEMORY_STORE.md وتصديرها للوكلاء.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  1. **التحليل البعدي (Post-Mortem Analysis):** دراسة سجل المحادثة واستخراج العقبات التي واجهت الفريق والحلول البرمجية الفعالة التي تم تطبيقها.
-  2. **تحديث سجل التعلم (Learning Log):** توثيق المشاكل البرمجية المكتشفة وحلولها مباشرة في القسم الثامن من ملف `AGENTS.md` لتجنب تكرارها.
-  3. **تطوير مهارات الفريق:** مراجعة وتعديل مهارات الوكلاء وتحديث التعليمات تلقائياً.
-  4. **سد الفجوات البرمجية:** استدعاء الوكيل `[github-talent-scout]` للبحث عن أي مكتبات أو أدوات مفتوحة المصدر يمكنها تسريع العمل مستقبلاً ودمجها.</t>
+  1. **التقاط وتخزين الدروس:** حفظ القرارات المعمارية وتفضيلات المستخدم في `MEMORY_STORE.md`.</t>
         </is>
       </c>
     </row>
@@ -1089,36 +1067,34 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>15. خطاف تنظيم وترتيب الأجهزة الشامل</t>
+          <t>15. خطاف النجاح والتحليل البعدي</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>رتب جهازى, فرز الملفات, ترتيب ملفات</t>
+          <t>تم بنجاح, انتهى المشروع بنجاح</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 3.7 Flash (High)` 
- البديل: `Gemini 3.6 Flash (Medium)`</t>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>[windows-c-drive-optimizer], [windows-file-organizer]</t>
+          <t>[agent-optimizer]</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>ترتيب ملفات جذور الأقراص بالكامل مع تنظيف وتحسين مساحة قرص الـ C بآن واحد.</t>
+          <t>إجراء تحليل بعدي للمشروع وتحديث سجل التعلم وسد الثغرات البرمجية.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  1. **فرز وتصنيف جذور الأقراص:** نقل الملفات السائبة بالكامل لمجلدات مخصصة وآمنة.
-  2. **تنظيف وتحسين النظام:** تحفيز وكيل C لضغط النظام وتفريغ الفيديوهات المؤقتة لزيادة السرعة والمساحة معاً.
-  3. **فحص سلامة الروابط وتوليد الفهارس:** التحقق من Junction Links وتحديث الفهارس لـ NotebookLM.</t>
+  1. **التحليل البعدي (Post-Mortem Analysis):** دراسة سجل المحادثة واستخراج العقبات وتحديث سجل التعلم وسد الفجوات.</t>
         </is>
       </c>
     </row>
@@ -1128,36 +1104,34 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>16. خطاف ترتيب الملفات لمسار محدد</t>
+          <t>16. خطاف تنظيم وترتيب الأجهزة الشامل</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>رتب المسار, نظم المجلد, ترتيب مسار</t>
+          <t>رتب جهازى, فرز الملفات, ترتيب ملفات</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 3.6 Flash (Medium)` 
- البديل: `Gemini 3.5 Flash (Medium)`</t>
+          <t>الأساسي: `Gemini 3.7 Flash (High)` 
+ البديل: `Gemini 3.6 Flash (Medium)`</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>[windows-file-organizer]</t>
+          <t>[windows-c-drive-optimizer], [windows-file-organizer]</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>تنظيم وفرز الملفات داخل مجلد أو مسار مخصص يحدده المستخدم بذكاء ودقة.</t>
+          <t>ترتيب ملفات جذور الأقراص بالكامل مع تنظيف وتحسين مساحة قرص الـ C بآن واحد.</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  1. **تحديد وفحص المسار المستهدف:** التحقق من وجود المجلد المخصص وقراءة هيكل الملفات والمجلدات بداخله.
-  2. **تصنيف الملفات حسب النوع والتاريخ:** فرز الملفات حسب امتداداتها (مستندات، صور، فيديوهات، أكواد) أو تاريخ إنشائها.
-  3. **إعادة التسمية والتنظيم:** نقل الملفات إلى مجلدات فرعية مخصصة مع إعادة تسمية خالية من التعارضات.</t>
+  1. **فرز وتصنيف جذور الأقراص:** تنظيف وتحسين مساحة قرص C وترتيب الملفات السائبة.</t>
         </is>
       </c>
     </row>
@@ -1167,37 +1141,34 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>17. خطاف إدارة تليجرام</t>
+          <t>17. خطاف ترتيب الملفات لمسار محدد</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>شغل البوت, تفعيل تليجرام, Telegram Bot</t>
+          <t>رتب المسار, نظم المجلد, ترتيب مسار</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 3.5 Flash (Medium)` 
- البديل: `Gemini 3.1 Pro (Low)`</t>
+          <t>الأساسي: `Gemini 3.6 Flash (Medium)` 
+ البديل: `Gemini 3.5 Flash (Medium)`</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>[devops-deployer], [persistent-memory-engine]</t>
+          <t>[windows-file-organizer]</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>تشغيل بوت تليجرام في الخلفية بنمط الاستماع للطلبات عن بعد دون تعارض.</t>
+          <t>تنظيم وفرز الملفات داخل مجلد أو مسار مخصص يحدده المستخدم بذكاء ودقة.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  1. **التحقق من البيئة:** فحص وجود رمز البوت (TELEGRAM_BOT_TOKEN) والاعتماديات.
-  2. **معالجة التعارض (Conflict Resolution):** رصد وإنهاء أي عمليات بوت سابقة معلقة (معالجة خطأ 409 Conflict) عبر `taskkill`.
-  3. **التشغيل بنمط الاستماع الفردي:** تشغيل السكربت `poll_once.py` في الخلفية (One-Shot Polling) ليستمع لطلب واحد ويخرج، مما يوقظ الوكيل للعمل.
-  4. **إشعار الجاهزية:** تأكيد نجاح التشغيل واستعداد البوت لاستقبال الأوامر عبر التطبيق.</t>
+  1. **تنظيم وفرز الملفات:** تصنيف الملفات داخل مجلد محدد بذكاء ودقة.</t>
         </is>
       </c>
     </row>
@@ -1207,37 +1178,34 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>18. خطاف التدقيق البرمجي الشامل وحراسة الجودة</t>
+          <t>18. خطاف إدارة تليجرام</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>تدقيق الجودة, فحص الكود النظيف, حراسة الجودة, clean code audit</t>
+          <t>شغل البوت, تفعيل تليجرام, Telegram Bot</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
- البديل: `Claude Opus 4.6 (Thinking)`</t>
+          <t>الأساسي: `Gemini 3.5 Flash (Medium)` 
+ البديل: `Gemini 3.1 Pro (Low)`</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>[code-reviewer-quality], [clean-code-guard], [test-guard], [docs-guard]</t>
+          <t>[devops-deployer], [persistent-memory-engine]</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>تفعيل بوابات الحماية الثلاث لفحص الكود النظيف، سلامة الاختبارات، ومطابقة التوثيق.</t>
+          <t>تشغيل بوت تليجرام في الخلفية بنمط الاستماع للطلبات عن بعد دون تعارض.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  1. **فحص الكود النظيف (`clean-code-guard`):** مراجعة جميع التغييرات البرمجية الأخيرة للتأكد من عدم ابتلاع الأخطاء، صغر حجم الدوال، غياب الكود المكرر، ودقة التسميات ومطابقة المعايير المعمارية.
-  2. **حراسة جودة الاختبارات (`test-guard`):** فحص جميع ملفات الاختبار للتحقق من عدم وجود Mocks وهمية أو اختبارات فارغة لا تكتشف الأخطاء الحقيقية.
-  3. **حراسة التوثيق ومطابقة الرموز (`docs-guard`):** مطابقة كافة ملفات التوثيق والـ Markdown مع الكود البرمجي الفعلي لضمان عدم وجود أي انحراف (Docs-vs-Code Drift).
-  4. **إصدار تقرير الجودة والحراسة:** تزويد المطور بتقرير شامل يحدد المخالفات المكتشفة وتصحيحاتها الفورية قبل الرفع والدمج.</t>
+  1. **التشغيل بنمط الاستماع الفردي (One-Shot Polling):** تشغيل البوت للاستماع لطلب واحد دون تعارض مع بيئة التطوير.</t>
         </is>
       </c>
     </row>
@@ -1247,38 +1215,34 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>19. خطاف استكشاف وتكامل الموارد العالمية</t>
+          <t>19. خطاف التدقيق البرمجي الشامل وحراسة الجودة</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>استكشف المورد, حلل المستودع, تكامل المورد, scout resource, integrate repo</t>
+          <t>تدقيق الجودة, فحص الكود النظيف, حراسة الجودة, clean code audit</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
           <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
- البديل: `Gemini 3.7 Flash (High)`</t>
+ البديل: `Claude Opus 4.6 (Thinking)`</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>[resource-scout-integrator], [github-talent-scout], [skill-forge-builder], [agent-optimizer], [frontend-design-builder], [git-github-manager]</t>
+          <t>[code-reviewer-quality], [clean-code-guard], [test-guard], [docs-guard]</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>تحليل المستودعات الخارجية واستيراد المهارات وتعميمها وتحديث الخطافات والإكسيل وتطبيق مكتبة الأوامر ودليل hooks_user_guide.md ومزامنة المنظومة.</t>
+          <t>تفعيل بوابات الحماية الثلاث لفحص الكود النظيف، سلامة الاختبارات، ومطابقة التوثيق.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  1. **فحص وتقييم المورد (`resource-scout-integrator` + `github-talent-scout`):** استلام رابط المستودع الخارجي وفحص ملفات README والأكواد وتحديد ما إذا كان يُحدث نقلة نوعية واستبعاد ما لا يتوافق مع البيئة.
-  2. **بناء وهيكلة المهارات (`skill-forge-builder`):** استخراج المهارات الفعالة وصياغة ملفات `SKILL.md` وفق المعايير العالمية عبر `skill-creator` و `find-skills`.
-  3. **التعميم العالمي (`global-deployment`):** نشر المهارات في `C:\Users\Kt\.gemini\config\skills/` لتصبح متاحة لكل المشاريع.
-  4. **تحديث الخطافات والإكسيل وتطبيق مكتبة الأوامر ودليل المستخدم (`agent-optimizer` + `frontend-design-builder`):** إضافة المهارات للخطافات ذات الصلة، وتحديث `hooks_user_guide.md` و `USER_GUIDE.md`، وتشغيل سكربت `convert_hooks_to_sheets.py` لتحديث ملف الإكسيل `HOOKS_GUIDE.xlsx` وتشغيل `update_html.py` لتحديث تطبيق مكتبة الأوامر التفاعلي (`03_Dynamic_Prompt_Library/index.html`).
-  5. **مزامنة المستودع العام سحابياً (`git-github-manager`):** تشغيل `sync_global_ecosystem.py` لمزامنة كامل منظومة الوكلاء والمهارات والدليل مع مستودع `Claude-Antigravity-Workspace` ورفعه إلى GitHub.</t>
+  1. **تفعيل بوابات الحماية الثلاث:** فحص الكود النظيف (`clean-code-guard`)، سلامة الاختبارات (`test-guard`)، ومطابقة التوثيق (`docs-guard`).</t>
         </is>
       </c>
     </row>
@@ -1288,38 +1252,226 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>20. خطاف المزامنة السحابية الشاملة ومطابقة المنظومة</t>
+          <t>20. خطاف استكشاف وتكامل الموارد العالمية</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>مزامنة المنظومة, مزامنة المستودع العام, تحديث المنظومة العالمية, sync ecosystem, sync workspace</t>
+          <t>استكشف المورد, حلل المستودع, تكامل المورد, scout resource, integrate repo</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>[resource-scout-integrator], [ui-ux-pro-max], [github-talent-scout], [skill-forge-builder], [agent-optimizer], [frontend-design-builder], [git-github-manager]</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>تحليل المستودعات الخارجية واستيراد المهارات وتعميمها وتحديث الخطافات والإكسيل وتطبيق مكتبة الأوامر ودليل hooks_user_guide.md ومزامنة المنظومة.</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **استيراد وتعميم المهارات العالمية:** تحليل المستودعات الخارجية وبناء مهارات `SKILL.md` ونشرها عالمياً وتحديث المنظومة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>21. خطاف المزامنة السحابية والمساهمة المجتمعية</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>مزامنة المنظومة, sync ecosystem, ارسل pull request, مساهمة في المستودع, create PR, contribute repo</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>الأساسي: `Gemini 3.7 Flash (High)` 
  البديل: `Claude Sonnet 4.6 (Thinking)`</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>[git-github-manager], [persistent-memory-engine], [agent-optimizer], [docs-guard]</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>مطابقة ومزامنة كافة الإضافات (Plugins)، المراجع والذاكرة، إعدادات MCP، المهارات والوكلاء، وتحديث الإكسيل ومكتبة الأوامر، ورفعها لـ GitHub بتطابق 100%.</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>* **طريقة العمل والإجراءات:**
-  1. **التحقق من سلامة المكونات والبيئة (`agent-optimizer`):** فحص حزم الإضافات (Plugins)، المهارات، والوكلاء والتكوينات العالمية في `~/.gemini/config/` ومقارنتها بالمشروع.
-  2. **تحديث ملفات الإكسيل وتطبيق مكتبة الأوامر:** تشغيل `convert_hooks_to_sheets.py` و `update_html.py` لتحديث `HOOKS_GUIDE.xlsx` و `index.html` بكافة الخطافات وتفاصيلها.
-  3. **تشغيل محرك المزامنة الشاملة (`sync_global_ecosystem.py`):** نسخ ومطابقة كافة الإضافات (Plugins)، والمراجع والذاكرة (References)، والمهارات، والوكلاء، وإعدادات MCP إلى `Claude-Antigravity-Workspace` بضمان تطابق 100%.
-  4. **فحص ومطابقة التوثيق (`docs-guard`):** مراجعة سلامة `README.md`, `USER_GUIDE.md`, `hooks_user_guide.md` لضمان عدم وجود أي انحراف.
-  5. **الالتزام والرفع التلقائي إلى GitHub (`git-github-manager`):** تنفيذ `git commit` موثق ودفع كافة التحديثات إلى المستودع العام [Claude-Antigravity-Workspace](https://github.com/ibrahimalkateb965-tech/Claude-Antigravity-Workspace) على GitHub بنقرة واحدة.
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>للمطور المالك: مطابقة ومزامنة كافة الإضافات والمهارات وتطبيق الأوامر مع GitHub. للمساهمين والمجتمع: تجهيز فرع الميزة وإنشاء وتوجيه Pull Request للمستودع المركزي للمشاركة.</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **المسار الأول (للمطور المالك / Maintainer):**
+     - تشغيل `sync_global_ecosystem.py` لمطابقة كامل منظومة الوكلاء والمهارات والمراجع مع المسار العالمي ورفعها إلى مستودع GitHub الرئيسي بنقرة واحدة.
+  2. **المسار الثاني (للمساهمين والمجتمع / Community &amp; Contributors):**
+     - عند إضافة مهارة أو ميزة جديدة في نسخة Fork، يقوم الخطاف بفحص توافق الكود والتوثيق مع معايير Autovem.
+     - إنشاء فرع مساهمة (Feature Branch) وصياغة رسالة الالتزام وفق مواصفات Conventional Commits.
+     - فتح وتوجيه رابط **Pull Request** تلقائياً إلى المستودع المركزي [Claude-Antigravity-Workspace على GitHub](https://github.com/ibrahimalkateb965-tech/Claude-Antigravity-Workspace) لمراجعتها ودمجها لصالح المجتمع.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>22. خطاف قيادة وإدارة الأسطول التشاركي</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>أسطول الـ CLIs, تشغيل الأسطول, تنسيق الأسطول, fleet orchestrator, multi cli fleet, إدارة الأسطول</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Opus 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>[fleet-orchestrator], [code-architect], [agent-optimizer], [persistent-memory-engine]</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>تفعيل وضبط أسطول الوكلاء المتعدد، إدارة وتنسيق التكليف بين CLIs، حوكمة بوابات مراجعة الأكواد، وترشيد التوكنز.</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **التهيئة والتوليد التلقائي (Auto-Provisioning):**
+     - فحص وجود مجلد `fleet_templates/` وملف `fleet_config.json` في المشروع وتوليدهما تلقائياً عند عدم وجودهما.
+  2. **توزيع المسؤوليات والحدود الحصرية وضبط النماذج:**
+     - تحديد ملكية الملفات والمهام في `fleet_config.json` لمنع التصادم:
+       - **Claude Code CLI** (النموذج: `Claude 5 Opus / Opus Max`): التخطيط والمراجعة المعمارية، **التنفيذ الحصري لكافة الاختبارات التلقائية**، واعتماد الأكواد وبوابات الجودة (Quality Gates).
+       - **OpenCode CLI** (النموذج: `Ox Alpha Unlimited`): التنفيذ الطرفي، إدارة قواعد البيانات Drift/ORM، وعملاء الاتصال والبيانات (كتابة وبناء فقط دون تشغيل أي اختبارات).
+       - **Antigravity IDE** (النموذج: `Gemini 3.7 Flash High`): بناء الواجهات والـ Domain Logic، إدارة الذاكرة المستدامة، وهندسة السياق (كتابة وبناء فقط دون تشغيل أي اختبارات).
+  3. **التشغيل المباشر لأدوات الـ CLI (Headless Direct Invocation):**
+     - تشغيل واستدعاء أدوات الـ CLI المثبتة مباشرة عبر سطر الأوامر غير التفاعلي:
+       - استدعاء `Claude Code CLI` للمراجعة المعمارية وتشغيل الاختبارات وتدقيق الكود عبر: `claude -p "&lt;prompt&gt;"` أو `claude --print`.
+       - استدعاء `OpenCode CLI` لتنفيذ الأوامر السريعة والطرفية وبناء قواعد البيانات عبر: `opencode run "&lt;message&gt;"`.
+     - معالجة وإدراج مخرجات الـ CLIs تلقائياً في دورة التطوير وبوابات الجودة.
+  4. **التحويل المستدام لنمط المحادثة (Session-Wide Fleet Mode Transformation):**
+     - **قاعدة حاسمة:** بمجرد استدعاء وتفعيل الخطاف 22 (بالمحفزات المعتمدة أو ذكر خطاف 22)، يدخل المساعد فوراً ومستداماً في **نمط قيادة الأسطول (Fleet Command Mode)** لكامل ما تبقى من الجلسة.
+     - تتحول كافة طلبات وأوامر المستخدم اللاحقة تلقائياً إلى أوامر وهياكل تفويض وتنسيق موجهة للأسطول باللغة الإنجليزية وفق الهيكل المعياري المعتمد (`Template 02: Task Delegation Protocol` و `Template 03: Code Review Audit`) مع حصر الملكية الدليلية، وفرض حظر تشغيل الاختبارات على غير Claude Code، وتأكيد خلو الأخطاء (`flutter analyze = 0`) دون الحاجة لتكرار تفعيل الخطاف في كل رسالة.
+  5. **احتكار الفحص والاختبار لـ Claude Code فقط (Testing Monopoly):**
+     - يُحظر حظراً تاماً تشغيل الاختبارات بواسطة OpenCode أو Antigravity. يتولى Claude Code تشغيل الاختبارات وفحص واعتماد أي كود مكتوب قبل دمجه.
+  6. **حوكمة بوابات الجودة وترشيد التوكنز:**
+     - مراجعة diffs كل مرحلة وفرض اللغة الإنجليزية بالكامل في طرفيات الـ CLIs مع حظر كتابة البويلربليت على النماذج العليا.
+  7. **إدارة الكوتا والتسليم السلس (Quota Failover &amp; Re-entry):**
+      - ضمان استمرارية المشروع وتسليم القيادة بسلاسة عند امتلاء كوتا أي نموذج مع تطبيق بروتوكول إعادة الدخول عند تجدد الحصة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>23. خطاف تحويل وأتمتة سكربتات المشاريع إلى MCP</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>حول إلى MCP, تحويل سكربتات لـ MCP, بناء أدوات MCP, convert scripts to mcp, scripts to mcp, ترقية السكربتات</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>[mcp-tool-builder], [script-to-mcp-converter], [code-architect], [agent-optimizer]</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>مسح سكربتات بايثون المبعثرة في مسار المشروع، تجريد منطق العمل وبناء دوال FastMCP ونماذج Pydantic، تسجيل الخادم، وأرشفة السكربتات في القرص الثانوي (G:) وحماية قرص C:.</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **المسح والاكتشاف الشامل (Script Discovery &amp; AST Analysis):**
+     - تشغيل `project_scripts_to_mcp.py` لمسح كافة ملفات بايثون المتناثرة داخل مجلدات المشروع، وتحليل أسماء الدوال، المعاملات، والمخرجات برمجياً.
+  2. **تجريد المنطق وهيكلة Pydantic (Decoupling &amp; Schema Generation):**
+     - فصل كود المعالجة عن المسارات الصلبة (Hardcoded Paths)، وصياغة كلاسات Pydantic Request لكل أداة لضمان التحقق من صحة المدخلات.
+  3. **البناء والتسجيل في FastMCP (FastMCP Tool Registration):**
+     - دمج الدوال في خادم FastMCP موحد ومستقر مع إلزام ترميز UTF-8 ودعم التزامن `asyncio.to_thread`.
+     - تسجيل الخادم وأدواته في `mcp_config.json` للـ IDE والوكلاء.
+  4. **الأرشفة الآمنة وحماية قرص النظام (Secondary Drive Archiving):**
+     - نقل السكربتات القديمة تلقائياً إلى مجلد أرشيف منظم على القرص الثانوي (`G:\_scripts_archive` أو حسب القرص المخصص) مع حظر الحفظ على قرص النظام `C:\`.
+  5. **تحديث مهارات الوكلاء والذاكرة:**
+     - تحديث بطاقات المهارات في `.agents/skills` لتمكين الوكلاء المتخصصين من استدعاء أدوات الـ MCP الجديدة مباشرة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>24. خطاف أتمتة مسارات العمل ووكلاء n8n الذكية</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>ابني مسار n8n, أتمتة n8n, وكيل n8n, n8n ai agent, n8n workflow, تصميم ورك فلو</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>[n8n-ai-agent-architect], [mcp-tool-builder], [backend-architect], [agent-optimizer]</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>تصميم وبناء مسارات عمل ذكية مؤتمتة على n8n، ربط الوكلاء المتعددين (Multi-Agent Sub-workflows)، تتبع التحويلات وتأهيل العملاء، وربط خوادم MCP وقواعد البيانات الموجهة بالذكاء الاصطناعي.</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **التصميم المعماري للمسار (`n8n-ai-agent-architect`):**
+     - اختيار النمط المعماري المناسب (Multi-Agent Router, ReAct Tools Agent, Evaluator-Optimizer Loop, أو Human-in-the-Loop).
+  2. **بناء وهيكلة أدوات الاستدعاء (Tool Calling &amp; JSON Schemas):**
+     - بناء وتوثيق أدوات HTTP Request و Custom JavaScript Tools مع فرض JSON Schema صارم يمنع هلوسة المعاملات.
+  3. **إدارة طبقات الذاكرة (Short-Term &amp; Vector Memory):**
+     - ربط الذاكرة القصيرة (Window Buffer) والذاكرة المستمرة (Postgres/Redis) ومخازن المتجهات الدلالية (Qdrant/Pinecone/Supabase).
+  4. **أتمتة العمليات التسويقية وتأهيل العملاء (Marketing &amp; CRM Pipelines):**
+     - بناء مسارات استقبال وتحليل بيانات العملاء المحتملين من Google Ads و Facebook وتوجيه الإشعارات اللحظية عبر WhatsApp و Slack وتحديث الـ CRM.
+  5. **تحصين الانقطاع ومعالجة الأخطاء (Fault Tolerance &amp; Sub-workflow Retries):**
+     - إضافة مسارات الخطأ (Error Trigger) وإعادة المحاولة مع التراجع التلقائي (Exponential Backoff) ونماذج LLM البديلة.
 &lt;/div&gt;</t>
         </is>
       </c>
@@ -1390,37 +1542,35 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>9. خطاف الفحص والاختبار التلقائي</t>
+          <t>9. خطاف مراجعة وتحديث المكتبات والنماذج</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>قم بالاختبار, جاهز للتجربة</t>
+          <t>تحديث الاعتماديات, تحديث المكتبات, تحديث النماذج, معايرة النماذج, update models</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
- البديل: `Gemini 3.7 Flash (High)`</t>
+          <t>الأساسي: `Gemini 3.7 Flash (High)` 
+ البديل: `Gemini 3.6 Flash (Medium)`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>[android-testing], [test-guard], [code-reviewer-quality]</t>
+          <t>[github-talent-scout], [code-architect], [agent-optimizer]</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>تشغيل اختبارات الوحدة وفحص جودة الكود واختبار السلوك الفعلي بدون Mock مفرط.</t>
+          <t>فحص ملفات Gradle وتحديث المكتبات، والتحقق التلقائي عبر الإنترنت (antigravity.google) لتحديث مصفوفة النماذج ودليل hooks_user_guide.md دون لقطات شاشة.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  1. **التقمص (Persona):** يتصرف الوكيل كمدير فحص جودة صارم (Pre-Flight Inspector &amp; Senior DevOps QA). بصرامة تامة وبدون أي مجاملات.
-  2. **حراسة الاختبارات (`test-guard`):** التحقق من أن الاختبارات تفحص سلوك النظام الفعلي ومخرجاته القابلة للملاحظة، ومنع الاختبارات الوهمية (Tautological Tests) والـ Mocks الزائدة.
-  3. **قاعدة التغطية الإجبارية (TEST COVERAGE MANDATE):** يُرفض أي اختبار يغطي مسار النجاح فقط (Happy Path). يجب كتابة اختبار للنجاح، الفشل، والحالات الطرفية (مثل: Network Off، Configuration Change).
-  4. **تقرير الفحص الصارم:** تزويد المطور بتقرير يحاكي المطالبة القياسية: `[BLOCKERS]`, `[WARNINGS]`, `[PRE-FLIGHT FIXES]`, `[GO / NO-GO]`.</t>
+  1. **فحص إصدارات المكتبات:** مسح ملفات `build.gradle.kts` ومقارنة إصدارات المكتبات الحالية بأحدث الإصدارات المستقرة.
+  2. **الاستكشاف والمعايرة التلقائية للنماذج عبر الإنترنت (Online Model Discovery):** الاستعلام الفوري عبر المصادر الرسمية (antigravity.google, docs.anthropic.com) ومعايرة مصفوفة النماذج.</t>
         </is>
       </c>
     </row>
@@ -1490,12 +1640,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>10. خطاف معالجة الأخطاء والأعطال</t>
+          <t>10. خطاف الفحص والاختبار التلقائي</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>حدث خطأ, التطبيق توقف, Crash</t>
+          <t>قم بالاختبار, جاهز للتجربة</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1506,20 +1656,19 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>[debugger]</t>
+          <t>[android-testing], [test-guard], [code-reviewer-quality]</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>تحليل سجلات الأخطاء والـ Stack Trace وعزل الكود المسبب للمشكلة وإصلاحه.</t>
+          <t>تشغيل اختبارات الوحدة وفحص جودة الكود واختبار السلوك الفعلي بدون Mock مفرط.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  1. **تحليل الـ Stack Trace:** قراءة السجلات بدقة وتحديد السطر المسبب للخلل.
-  2. **عزل المشكلة:** حصر الكود المسبب للأخطاء لمعرفة إن كان يتعلق بالشبكة، قاعدة البيانات، أو دورة حياة المكونات.
-  3. **اقتراح وتثبيت الحل:** تطبيق التعديل الأدنى الكافي لحل المشكلة مع حماية الأجزاء الأخرى من النظام.</t>
+  1. **حراسة الاختبارات (`test-guard`):** التحقق من أن الاختبارات تفحص سلوك النظام الفعلي ومنع Mocks الوهمية.
+  2. **قاعدة التغطية الإجبارية:** اختبار مسار النجاح، الفشل، والحالات الطرفية (Network Off, Lifecycle).</t>
         </is>
       </c>
     </row>
@@ -1589,36 +1738,34 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>11. خطاف إدارة النسخ والمستودعات</t>
+          <t>11. خطاف معالجة الأخطاء والأعطال</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>نظم جيت, ارفع لجيتهاب, تحديث المستودع, git commit</t>
+          <t>حدث خطأ, التطبيق توقف, Crash</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 3.7 Flash (High)` 
- البديل: `Gemini 3.6 Flash (Medium)`</t>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>[git-github-manager]</t>
+          <t>[debugger]</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>تهيئة المشاريع الجديدة على Git، إدارة التفرعات، وحل تعارضات الدمج ورفعها لـ GitHub بشكل نظيف.</t>
+          <t>تحليل سجلات الأخطاء والـ Stack Trace وعزل الكود المسبب للمشكلة وإصلاحه.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  1. **التحقق من حالة المستودع:** فحص حالة Git باستخدام `git status` ومعرفة الملفات المعدلة والمحذوفة والجديدة.
-  2. **التنظيم والتصنيف:** مساعدة المطور في فرز الملفات، واستثناء الملفات غير الضرورية (تحديث `.gitignore`).
-  3. **التنفيذ والرفع:** كتابة رسائل Commit احترافية وواضحة، وإنشاء فروع عند الحاجة (Branching)، وحل تعارضات الدمج، ثم دفع التغييرات إلى GitHub بأمان.</t>
+  1. **تحليل الـ Stack Trace:** قراءة السجلات بدقة وتحديد السطر المسبب للخلل وعزله وإصلاحه بأقل تعديل كافٍ.</t>
         </is>
       </c>
     </row>
@@ -1688,37 +1835,35 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>12. خطاف تحديث الإنجازات</t>
+          <t>12. خطاف إدارة النسخ والمستودعات</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>حدث الإنجازات, تحديث README, وثق الإنجازات</t>
+          <t>نظم جيت, ارفع لجيتهاب, تحديث المستودع, git commit</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>الأساسي: `Gemini 3.7 Flash (High)` 
- البديل: `Claude Sonnet 4.6 (Thinking)`</t>
+ البديل: `Gemini 3.6 Flash (Medium)`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>[git-github-manager], [docs-guard]</t>
+          <t>[git-github-manager]</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>صياغة التعديلات كإنجازات ومطابقتها برمجياً وتحديث README.md و hooks_user_guide.md ثم الرفع لـ GitHub.</t>
+          <t>تهيئة المشاريع الجديدة على Git، إدارة التفرعات، وحل تعارضات الدمج ورفعها لـ GitHub بشكل نظيف.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  1. **قراءة السجل والذاكرة:** مراجعة التغييرات الأخيرة في الملفات وقراءة `MEMORY_STORE.md` لاستخلاص ما تم إنجازه.
-  2. **مطابقة التوثيق (`docs-guard`):** مطابقة كل رمز برمجي أو مسار أو دالة مذكورة في التوثيق مع الكود الحقيقي لمنع أي تباين أو اختلاق (Docs-vs-Code Drift).
-  3. **صياغة الإنجازات وتحديث التوثيق:** كتابة الإنجازات بنسق احترافي كنقاط موجزة، وتحديث ملف `README.md` وملف [`hooks_user_guide.md`](file:///f:/AI%20PROJECTS/Blind%20App/hooks_user_guide.md).
-  4. **الرفع التلقائي (Commit &amp; Push):** إضافة التعديلات وإجراء الحفظ، ثم الرفع التلقائي إلى GitHub مباشرة كخطوة نهائية متصلة.</t>
+  1. **التحقق من حالة المستودع:** فحص حالة Git واستثناء الملفات غير الضرورية في `.gitignore`.
+  2. **التنفيذ والرفع:** كتابة رسائل Commit احترافية وحل التعارضات ودفع التغييرات إلى GitHub.</t>
         </is>
       </c>
     </row>
@@ -1788,38 +1933,34 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>13. خطاف الذاكرة المستدامة</t>
+          <t>13. خطاف تحديث الإنجازات</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>حفظ ذاكرة, تحديث السياق, سجّل هذا</t>
+          <t>حدث الإنجازات, تحديث README, وثق الإنجازات</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
- البديل: `GPT-OSS 120B (Medium)`</t>
+          <t>الأساسي: `Gemini 3.7 Flash (High)` 
+ البديل: `Claude Sonnet 4.6 (Thinking)`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>[persistent-memory-engine]</t>
+          <t>[git-github-manager], [docs-guard]</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>التقاط الدروس والقرارات وتخزينها في MEMORY_STORE.md وتصديرها للوكلاء.</t>
+          <t>صياغة التعديلات كإنجازات ومطابقتها برمجياً وتحديث README.md و hooks_user_guide.md ثم الرفع لـ GitHub.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  1. **فلترة وتدقيق الدروس (LESSON VALIDATION):** يُمنع تسجيل معلومات بديهية أو عامة. يجب أن تكون الذكريات مركزة على القواعد المعمارية الجديدة، حيل تقنية فريدة، أو تحذيرات من أخطاء مكررة. يجب تضمين قسم `[ANTI-PATTERN AVOIDED]` لكل درس لمنع تكرار الخطأ.
-  2. **التقاط السياق (Capture):** يقوم الوكيل `[persistent-memory-engine]` بتحليل الجلسة الحالية لاستخراج القرارات المعمارية العميقة والحلول.
-  3. **التخزين الهيكلي (Store):** كتابة الذكريات المستخرجة في `MEMORY_STORE.md` بصيغة YAML الموحدة مع التصنيف بالوسوم والتوقيت.
-  4. **التصدير الانتقائي (Export):** تحديث حزمة السياق لكل وكيل حسب بروتوكول التصدير في `MEMORY_EXPORT_PROTOCOL.md`.
-  5. **التنقيح (Prune):** مراجعة الذكريات القديمة وحذف المتقادمة أو المتناقضة.</t>
+  1. **قراءة السجل ومطابقة التوثيق (`docs-guard`):** مراجعة التغييرات الأخيرة وصياغة الإنجازات وتحديث `README.md`.</t>
         </is>
       </c>
     </row>
@@ -1889,37 +2030,34 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>14. خطاف النجاح والتحليل البعدي</t>
+          <t>14. خطاف الذاكرة المستدامة</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>تم بنجاح, انتهى المشروع بنجاح</t>
+          <t>حفظ ذاكرة, تحديث السياق, سجّل هذا</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
- البديل: `Gemini 3.7 Flash (High)`</t>
+ البديل: `GPT-OSS 120B (Medium)`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>[agent-optimizer]</t>
+          <t>[persistent-memory-engine]</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>إجراء تحليل بعدي للمشروع وتحديث سجل التعلم وسد الثغرات البرمجية.</t>
+          <t>التقاط الدروس والقرارات وتخزينها في MEMORY_STORE.md وتصديرها للوكلاء.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  1. **التحليل البعدي (Post-Mortem Analysis):** دراسة سجل المحادثة واستخراج العقبات التي واجهت الفريق والحلول البرمجية الفعالة التي تم تطبيقها.
-  2. **تحديث سجل التعلم (Learning Log):** توثيق المشاكل البرمجية المكتشفة وحلولها مباشرة في القسم الثامن من ملف `AGENTS.md` لتجنب تكرارها.
-  3. **تطوير مهارات الفريق:** مراجعة وتعديل مهارات الوكلاء وتحديث التعليمات تلقائياً.
-  4. **سد الفجوات البرمجية:** استدعاء الوكيل `[github-talent-scout]` للبحث عن أي مكتبات أو أدوات مفتوحة المصدر يمكنها تسريع العمل مستقبلاً ودمجها.</t>
+  1. **التقاط وتخزين الدروس:** حفظ القرارات المعمارية وتفضيلات المستخدم في `MEMORY_STORE.md`.</t>
         </is>
       </c>
     </row>
@@ -1989,36 +2127,34 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>15. خطاف تنظيم وترتيب الأجهزة الشامل</t>
+          <t>15. خطاف النجاح والتحليل البعدي</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>رتب جهازى, فرز الملفات, ترتيب ملفات</t>
+          <t>تم بنجاح, انتهى المشروع بنجاح</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 3.7 Flash (High)` 
- البديل: `Gemini 3.6 Flash (Medium)`</t>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>[windows-c-drive-optimizer], [windows-file-organizer]</t>
+          <t>[agent-optimizer]</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>ترتيب ملفات جذور الأقراص بالكامل مع تنظيف وتحسين مساحة قرص الـ C بآن واحد.</t>
+          <t>إجراء تحليل بعدي للمشروع وتحديث سجل التعلم وسد الثغرات البرمجية.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  1. **فرز وتصنيف جذور الأقراص:** نقل الملفات السائبة بالكامل لمجلدات مخصصة وآمنة.
-  2. **تنظيف وتحسين النظام:** تحفيز وكيل C لضغط النظام وتفريغ الفيديوهات المؤقتة لزيادة السرعة والمساحة معاً.
-  3. **فحص سلامة الروابط وتوليد الفهارس:** التحقق من Junction Links وتحديث الفهارس لـ NotebookLM.</t>
+  1. **التحليل البعدي (Post-Mortem Analysis):** دراسة سجل المحادثة واستخراج العقبات وتحديث سجل التعلم وسد الفجوات.</t>
         </is>
       </c>
     </row>
@@ -2088,36 +2224,34 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>16. خطاف ترتيب الملفات لمسار محدد</t>
+          <t>16. خطاف تنظيم وترتيب الأجهزة الشامل</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>رتب المسار, نظم المجلد, ترتيب مسار</t>
+          <t>رتب جهازى, فرز الملفات, ترتيب ملفات</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 3.6 Flash (Medium)` 
- البديل: `Gemini 3.5 Flash (Medium)`</t>
+          <t>الأساسي: `Gemini 3.7 Flash (High)` 
+ البديل: `Gemini 3.6 Flash (Medium)`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>[windows-file-organizer]</t>
+          <t>[windows-c-drive-optimizer], [windows-file-organizer]</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>تنظيم وفرز الملفات داخل مجلد أو مسار مخصص يحدده المستخدم بذكاء ودقة.</t>
+          <t>ترتيب ملفات جذور الأقراص بالكامل مع تنظيف وتحسين مساحة قرص الـ C بآن واحد.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  1. **تحديد وفحص المسار المستهدف:** التحقق من وجود المجلد المخصص وقراءة هيكل الملفات والمجلدات بداخله.
-  2. **تصنيف الملفات حسب النوع والتاريخ:** فرز الملفات حسب امتداداتها (مستندات، صور، فيديوهات، أكواد) أو تاريخ إنشائها.
-  3. **إعادة التسمية والتنظيم:** نقل الملفات إلى مجلدات فرعية مخصصة مع إعادة تسمية خالية من التعارضات.</t>
+  1. **فرز وتصنيف جذور الأقراص:** تنظيف وتحسين مساحة قرص C وترتيب الملفات السائبة.</t>
         </is>
       </c>
     </row>
@@ -2187,37 +2321,34 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>17. خطاف إدارة تليجرام</t>
+          <t>17. خطاف ترتيب الملفات لمسار محدد</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>شغل البوت, تفعيل تليجرام, Telegram Bot</t>
+          <t>رتب المسار, نظم المجلد, ترتيب مسار</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 3.5 Flash (Medium)` 
- البديل: `Gemini 3.1 Pro (Low)`</t>
+          <t>الأساسي: `Gemini 3.6 Flash (Medium)` 
+ البديل: `Gemini 3.5 Flash (Medium)`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>[devops-deployer], [persistent-memory-engine]</t>
+          <t>[windows-file-organizer]</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>تشغيل بوت تليجرام في الخلفية بنمط الاستماع للطلبات عن بعد دون تعارض.</t>
+          <t>تنظيم وفرز الملفات داخل مجلد أو مسار مخصص يحدده المستخدم بذكاء ودقة.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  1. **التحقق من البيئة:** فحص وجود رمز البوت (TELEGRAM_BOT_TOKEN) والاعتماديات.
-  2. **معالجة التعارض (Conflict Resolution):** رصد وإنهاء أي عمليات بوت سابقة معلقة (معالجة خطأ 409 Conflict) عبر `taskkill`.
-  3. **التشغيل بنمط الاستماع الفردي:** تشغيل السكربت `poll_once.py` في الخلفية (One-Shot Polling) ليستمع لطلب واحد ويخرج، مما يوقظ الوكيل للعمل.
-  4. **إشعار الجاهزية:** تأكيد نجاح التشغيل واستعداد البوت لاستقبال الأوامر عبر التطبيق.</t>
+  1. **تنظيم وفرز الملفات:** تصنيف الملفات داخل مجلد محدد بذكاء ودقة.</t>
         </is>
       </c>
     </row>
@@ -2287,37 +2418,34 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>18. خطاف التدقيق البرمجي الشامل وحراسة الجودة</t>
+          <t>18. خطاف إدارة تليجرام</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>تدقيق الجودة, فحص الكود النظيف, حراسة الجودة, clean code audit</t>
+          <t>شغل البوت, تفعيل تليجرام, Telegram Bot</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
- البديل: `Claude Opus 4.6 (Thinking)`</t>
+          <t>الأساسي: `Gemini 3.5 Flash (Medium)` 
+ البديل: `Gemini 3.1 Pro (Low)`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>[code-reviewer-quality], [clean-code-guard], [test-guard], [docs-guard]</t>
+          <t>[devops-deployer], [persistent-memory-engine]</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>تفعيل بوابات الحماية الثلاث لفحص الكود النظيف، سلامة الاختبارات، ومطابقة التوثيق.</t>
+          <t>تشغيل بوت تليجرام في الخلفية بنمط الاستماع للطلبات عن بعد دون تعارض.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  1. **فحص الكود النظيف (`clean-code-guard`):** مراجعة جميع التغييرات البرمجية الأخيرة للتأكد من عدم ابتلاع الأخطاء، صغر حجم الدوال، غياب الكود المكرر، ودقة التسميات ومطابقة المعايير المعمارية.
-  2. **حراسة جودة الاختبارات (`test-guard`):** فحص جميع ملفات الاختبار للتحقق من عدم وجود Mocks وهمية أو اختبارات فارغة لا تكتشف الأخطاء الحقيقية.
-  3. **حراسة التوثيق ومطابقة الرموز (`docs-guard`):** مطابقة كافة ملفات التوثيق والـ Markdown مع الكود البرمجي الفعلي لضمان عدم وجود أي انحراف (Docs-vs-Code Drift).
-  4. **إصدار تقرير الجودة والحراسة:** تزويد المطور بتقرير شامل يحدد المخالفات المكتشفة وتصحيحاتها الفورية قبل الرفع والدمج.</t>
+  1. **التشغيل بنمط الاستماع الفردي (One-Shot Polling):** تشغيل البوت للاستماع لطلب واحد دون تعارض مع بيئة التطوير.</t>
         </is>
       </c>
     </row>
@@ -2486,38 +2614,34 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>19. خطاف استكشاف وتكامل الموارد العالمية</t>
+          <t>19. خطاف التدقيق البرمجي الشامل وحراسة الجودة</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>استكشف المورد, حلل المستودع, تكامل المورد, scout resource, integrate repo</t>
+          <t>تدقيق الجودة, فحص الكود النظيف, حراسة الجودة, clean code audit</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
- البديل: `Gemini 3.7 Flash (High)`</t>
+ البديل: `Claude Opus 4.6 (Thinking)`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>[resource-scout-integrator], [github-talent-scout], [skill-forge-builder], [agent-optimizer], [frontend-design-builder], [git-github-manager]</t>
+          <t>[code-reviewer-quality], [clean-code-guard], [test-guard], [docs-guard]</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>تحليل المستودعات الخارجية واستيراد المهارات وتعميمها وتحديث الخطافات والإكسيل وتطبيق مكتبة الأوامر ودليل hooks_user_guide.md ومزامنة المنظومة.</t>
+          <t>تفعيل بوابات الحماية الثلاث لفحص الكود النظيف، سلامة الاختبارات، ومطابقة التوثيق.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  1. **فحص وتقييم المورد (`resource-scout-integrator` + `github-talent-scout`):** استلام رابط المستودع الخارجي وفحص ملفات README والأكواد وتحديد ما إذا كان يُحدث نقلة نوعية واستبعاد ما لا يتوافق مع البيئة.
-  2. **بناء وهيكلة المهارات (`skill-forge-builder`):** استخراج المهارات الفعالة وصياغة ملفات `SKILL.md` وفق المعايير العالمية عبر `skill-creator` و `find-skills`.
-  3. **التعميم العالمي (`global-deployment`):** نشر المهارات في `C:\Users\Kt\.gemini\config\skills/` لتصبح متاحة لكل المشاريع.
-  4. **تحديث الخطافات والإكسيل وتطبيق مكتبة الأوامر ودليل المستخدم (`agent-optimizer` + `frontend-design-builder`):** إضافة المهارات للخطافات ذات الصلة، وتحديث `hooks_user_guide.md` و `USER_GUIDE.md`، وتشغيل سكربت `convert_hooks_to_sheets.py` لتحديث ملف الإكسيل `HOOKS_GUIDE.xlsx` وتشغيل `update_html.py` لتحديث تطبيق مكتبة الأوامر التفاعلي (`03_Dynamic_Prompt_Library/index.html`).
-  5. **مزامنة المستودع العام سحابياً (`git-github-manager`):** تشغيل `sync_global_ecosystem.py` لمزامنة كامل منظومة الوكلاء والمهارات والدليل مع مستودع `Claude-Antigravity-Workspace` ورفعه إلى GitHub.</t>
+  1. **تفعيل بوابات الحماية الثلاث:** فحص الكود النظيف (`clean-code-guard`)، سلامة الاختبارات (`test-guard`)، ومطابقة التوثيق (`docs-guard`).</t>
         </is>
       </c>
     </row>
@@ -2587,12 +2711,109 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>20. خطاف المزامنة السحابية الشاملة ومطابقة المنظومة</t>
+          <t>20. خطاف استكشاف وتكامل الموارد العالمية</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>مزامنة المنظومة, مزامنة المستودع العام, تحديث المنظومة العالمية, sync ecosystem, sync workspace</t>
+          <t>استكشف المورد, حلل المستودع, تكامل المورد, scout resource, integrate repo</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[resource-scout-integrator], [ui-ux-pro-max], [github-talent-scout], [skill-forge-builder], [agent-optimizer], [frontend-design-builder], [git-github-manager]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>تحليل المستودعات الخارجية واستيراد المهارات وتعميمها وتحديث الخطافات والإكسيل وتطبيق مكتبة الأوامر ودليل hooks_user_guide.md ومزامنة المنظومة.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **استيراد وتعميم المهارات العالمية:** تحليل المستودعات الخارجية وبناء مهارات `SKILL.md` ونشرها عالمياً وتحديث المنظومة.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>اسم الخطاف</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>المحفزات (الخطاف للنسخ)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>النموذج الأساسي والبديل</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>الوكلاء المسؤولون</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>الهدف الأساسي</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>الوصف والتفاصيل</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>21. خطاف المزامنة السحابية والمساهمة المجتمعية</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>مزامنة المنظومة, sync ecosystem, ارسل pull request, مساهمة في المستودع, create PR, contribute repo</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -2608,17 +2829,348 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>مطابقة ومزامنة كافة الإضافات (Plugins)، المراجع والذاكرة، إعدادات MCP، المهارات والوكلاء، وتحديث الإكسيل ومكتبة الأوامر، ورفعها لـ GitHub بتطابق 100%.</t>
+          <t>للمطور المالك: مطابقة ومزامنة كافة الإضافات والمهارات وتطبيق الأوامر مع GitHub. للمساهمين والمجتمع: تجهيز فرع الميزة وإنشاء وتوجيه Pull Request للمستودع المركزي للمشاركة.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  1. **التحقق من سلامة المكونات والبيئة (`agent-optimizer`):** فحص حزم الإضافات (Plugins)، المهارات، والوكلاء والتكوينات العالمية في `~/.gemini/config/` ومقارنتها بالمشروع.
-  2. **تحديث ملفات الإكسيل وتطبيق مكتبة الأوامر:** تشغيل `convert_hooks_to_sheets.py` و `update_html.py` لتحديث `HOOKS_GUIDE.xlsx` و `index.html` بكافة الخطافات وتفاصيلها.
-  3. **تشغيل محرك المزامنة الشاملة (`sync_global_ecosystem.py`):** نسخ ومطابقة كافة الإضافات (Plugins)، والمراجع والذاكرة (References)، والمهارات، والوكلاء، وإعدادات MCP إلى `Claude-Antigravity-Workspace` بضمان تطابق 100%.
-  4. **فحص ومطابقة التوثيق (`docs-guard`):** مراجعة سلامة `README.md`, `USER_GUIDE.md`, `hooks_user_guide.md` لضمان عدم وجود أي انحراف.
-  5. **الالتزام والرفع التلقائي إلى GitHub (`git-github-manager`):** تنفيذ `git commit` موثق ودفع كافة التحديثات إلى المستودع العام [Claude-Antigravity-Workspace](https://github.com/ibrahimalkateb965-tech/Claude-Antigravity-Workspace) على GitHub بنقرة واحدة.
+  1. **المسار الأول (للمطور المالك / Maintainer):**
+     - تشغيل `sync_global_ecosystem.py` لمطابقة كامل منظومة الوكلاء والمهارات والمراجع مع المسار العالمي ورفعها إلى مستودع GitHub الرئيسي بنقرة واحدة.
+  2. **المسار الثاني (للمساهمين والمجتمع / Community &amp; Contributors):**
+     - عند إضافة مهارة أو ميزة جديدة في نسخة Fork، يقوم الخطاف بفحص توافق الكود والتوثيق مع معايير Autovem.
+     - إنشاء فرع مساهمة (Feature Branch) وصياغة رسالة الالتزام وفق مواصفات Conventional Commits.
+     - فتح وتوجيه رابط **Pull Request** تلقائياً إلى المستودع المركزي [Claude-Antigravity-Workspace على GitHub](https://github.com/ibrahimalkateb965-tech/Claude-Antigravity-Workspace) لمراجعتها ودمجها لصالح المجتمع.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>اسم الخطاف</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>المحفزات (الخطاف للنسخ)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>النموذج الأساسي والبديل</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>الوكلاء المسؤولون</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>الهدف الأساسي</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>الوصف والتفاصيل</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>22. خطاف قيادة وإدارة الأسطول التشاركي</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>أسطول الـ CLIs, تشغيل الأسطول, تنسيق الأسطول, fleet orchestrator, multi cli fleet, إدارة الأسطول</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Opus 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[fleet-orchestrator], [code-architect], [agent-optimizer], [persistent-memory-engine]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>تفعيل وضبط أسطول الوكلاء المتعدد، إدارة وتنسيق التكليف بين CLIs، حوكمة بوابات مراجعة الأكواد، وترشيد التوكنز.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **التهيئة والتوليد التلقائي (Auto-Provisioning):**
+     - فحص وجود مجلد `fleet_templates/` وملف `fleet_config.json` في المشروع وتوليدهما تلقائياً عند عدم وجودهما.
+  2. **توزيع المسؤوليات والحدود الحصرية وضبط النماذج:**
+     - تحديد ملكية الملفات والمهام في `fleet_config.json` لمنع التصادم:
+       - **Claude Code CLI** (النموذج: `Claude 5 Opus / Opus Max`): التخطيط والمراجعة المعمارية، **التنفيذ الحصري لكافة الاختبارات التلقائية**، واعتماد الأكواد وبوابات الجودة (Quality Gates).
+       - **OpenCode CLI** (النموذج: `Ox Alpha Unlimited`): التنفيذ الطرفي، إدارة قواعد البيانات Drift/ORM، وعملاء الاتصال والبيانات (كتابة وبناء فقط دون تشغيل أي اختبارات).
+       - **Antigravity IDE** (النموذج: `Gemini 3.7 Flash High`): بناء الواجهات والـ Domain Logic، إدارة الذاكرة المستدامة، وهندسة السياق (كتابة وبناء فقط دون تشغيل أي اختبارات).
+  3. **التشغيل المباشر لأدوات الـ CLI (Headless Direct Invocation):**
+     - تشغيل واستدعاء أدوات الـ CLI المثبتة مباشرة عبر سطر الأوامر غير التفاعلي:
+       - استدعاء `Claude Code CLI` للمراجعة المعمارية وتشغيل الاختبارات وتدقيق الكود عبر: `claude -p "&lt;prompt&gt;"` أو `claude --print`.
+       - استدعاء `OpenCode CLI` لتنفيذ الأوامر السريعة والطرفية وبناء قواعد البيانات عبر: `opencode run "&lt;message&gt;"`.
+     - معالجة وإدراج مخرجات الـ CLIs تلقائياً في دورة التطوير وبوابات الجودة.
+  4. **التحويل المستدام لنمط المحادثة (Session-Wide Fleet Mode Transformation):**
+     - **قاعدة حاسمة:** بمجرد استدعاء وتفعيل الخطاف 22 (بالمحفزات المعتمدة أو ذكر خطاف 22)، يدخل المساعد فوراً ومستداماً في **نمط قيادة الأسطول (Fleet Command Mode)** لكامل ما تبقى من الجلسة.
+     - تتحول كافة طلبات وأوامر المستخدم اللاحقة تلقائياً إلى أوامر وهياكل تفويض وتنسيق موجهة للأسطول باللغة الإنجليزية وفق الهيكل المعياري المعتمد (`Template 02: Task Delegation Protocol` و `Template 03: Code Review Audit`) مع حصر الملكية الدليلية، وفرض حظر تشغيل الاختبارات على غير Claude Code، وتأكيد خلو الأخطاء (`flutter analyze = 0`) دون الحاجة لتكرار تفعيل الخطاف في كل رسالة.
+  5. **احتكار الفحص والاختبار لـ Claude Code فقط (Testing Monopoly):**
+     - يُحظر حظراً تاماً تشغيل الاختبارات بواسطة OpenCode أو Antigravity. يتولى Claude Code تشغيل الاختبارات وفحص واعتماد أي كود مكتوب قبل دمجه.
+  6. **حوكمة بوابات الجودة وترشيد التوكنز:**
+     - مراجعة diffs كل مرحلة وفرض اللغة الإنجليزية بالكامل في طرفيات الـ CLIs مع حظر كتابة البويلربليت على النماذج العليا.
+  7. **إدارة الكوتا والتسليم السلس (Quota Failover &amp; Re-entry):**
+      - ضمان استمرارية المشروع وتسليم القيادة بسلاسة عند امتلاء كوتا أي نموذج مع تطبيق بروتوكول إعادة الدخول عند تجدد الحصة.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>اسم الخطاف</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>المحفزات (الخطاف للنسخ)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>النموذج الأساسي والبديل</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>الوكلاء المسؤولون</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>الهدف الأساسي</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>الوصف والتفاصيل</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>23. خطاف تحويل وأتمتة سكربتات المشاريع إلى MCP</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>حول إلى MCP, تحويل سكربتات لـ MCP, بناء أدوات MCP, convert scripts to mcp, scripts to mcp, ترقية السكربتات</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[mcp-tool-builder], [script-to-mcp-converter], [code-architect], [agent-optimizer]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>مسح سكربتات بايثون المبعثرة في مسار المشروع، تجريد منطق العمل وبناء دوال FastMCP ونماذج Pydantic، تسجيل الخادم، وأرشفة السكربتات في القرص الثانوي (G:) وحماية قرص C:.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **المسح والاكتشاف الشامل (Script Discovery &amp; AST Analysis):**
+     - تشغيل `project_scripts_to_mcp.py` لمسح كافة ملفات بايثون المتناثرة داخل مجلدات المشروع، وتحليل أسماء الدوال، المعاملات، والمخرجات برمجياً.
+  2. **تجريد المنطق وهيكلة Pydantic (Decoupling &amp; Schema Generation):**
+     - فصل كود المعالجة عن المسارات الصلبة (Hardcoded Paths)، وصياغة كلاسات Pydantic Request لكل أداة لضمان التحقق من صحة المدخلات.
+  3. **البناء والتسجيل في FastMCP (FastMCP Tool Registration):**
+     - دمج الدوال في خادم FastMCP موحد ومستقر مع إلزام ترميز UTF-8 ودعم التزامن `asyncio.to_thread`.
+     - تسجيل الخادم وأدواته في `mcp_config.json` للـ IDE والوكلاء.
+  4. **الأرشفة الآمنة وحماية قرص النظام (Secondary Drive Archiving):**
+     - نقل السكربتات القديمة تلقائياً إلى مجلد أرشيف منظم على القرص الثانوي (`G:\_scripts_archive` أو حسب القرص المخصص) مع حظر الحفظ على قرص النظام `C:\`.
+  5. **تحديث مهارات الوكلاء والذاكرة:**
+     - تحديث بطاقات المهارات في `.agents/skills` لتمكين الوكلاء المتخصصين من استدعاء أدوات الـ MCP الجديدة مباشرة.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>اسم الخطاف</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>المحفزات (الخطاف للنسخ)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>النموذج الأساسي والبديل</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>الوكلاء المسؤولون</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>الهدف الأساسي</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>الوصف والتفاصيل</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>24. خطاف أتمتة مسارات العمل ووكلاء n8n الذكية</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>ابني مسار n8n, أتمتة n8n, وكيل n8n, n8n ai agent, n8n workflow, تصميم ورك فلو</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[n8n-ai-agent-architect], [mcp-tool-builder], [backend-architect], [agent-optimizer]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>تصميم وبناء مسارات عمل ذكية مؤتمتة على n8n، ربط الوكلاء المتعددين (Multi-Agent Sub-workflows)، تتبع التحويلات وتأهيل العملاء، وربط خوادم MCP وقواعد البيانات الموجهة بالذكاء الاصطناعي.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **التصميم المعماري للمسار (`n8n-ai-agent-architect`):**
+     - اختيار النمط المعماري المناسب (Multi-Agent Router, ReAct Tools Agent, Evaluator-Optimizer Loop, أو Human-in-the-Loop).
+  2. **بناء وهيكلة أدوات الاستدعاء (Tool Calling &amp; JSON Schemas):**
+     - بناء وتوثيق أدوات HTTP Request و Custom JavaScript Tools مع فرض JSON Schema صارم يمنع هلوسة المعاملات.
+  3. **إدارة طبقات الذاكرة (Short-Term &amp; Vector Memory):**
+     - ربط الذاكرة القصيرة (Window Buffer) والذاكرة المستمرة (Postgres/Redis) ومخازن المتجهات الدلالية (Qdrant/Pinecone/Supabase).
+  4. **أتمتة العمليات التسويقية وتأهيل العملاء (Marketing &amp; CRM Pipelines):**
+     - بناء مسارات استقبال وتحليل بيانات العملاء المحتملين من Google Ads و Facebook وتوجيه الإشعارات اللحظية عبر WhatsApp و Slack وتحديث الـ CRM.
+  5. **تحصين الانقطاع ومعالجة الأخطاء (Fault Tolerance &amp; Sub-workflow Retries):**
+     - إضافة مسارات الخطأ (Error Trigger) وإعادة المحاولة مع التراجع التلقائي (Exponential Backoff) ونماذج LLM البديلة.
 &lt;/div&gt;</t>
         </is>
       </c>
@@ -2789,12 +3341,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>3. خطاف الإشراف العام وتصحيح المسار</t>
+          <t>3. خطاف التخصيص والتصدير الذكي لطاقم المشروع</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>تصحيح مسار, تعديل البرومبت, خطأ بالخطاف, تصحيح خطاف</t>
+          <t>اعتمد سياق المشروع, تخصيص وكلاء المشروع, تصدير بيئة المشروع, تخصيص الوكلاء</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -2805,21 +3357,21 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>[prompt-engineer], [agent-optimizer]</t>
+          <t>[code-architect], [agent-optimizer], [prompt-engineer]</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>تصحيح الخطافات الخاطئة والبرومبتات غير الاحترافية وتوجيهها للمسار الصحيح تلقائياً.</t>
+          <t>تحليل سياق المشروع وتصدير حزم الوكلاء محلياً مع التنظيف التلقائي (Pruning) وتوليد سكربت المزامنة.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  1. **الرصد التلقائي والإيقاف:** يقوم الوكيل الرئيسي بمراقبة المحادثة. عند استخدام المستخدم لمحفز "تصحيح مسار"، أو عند رصد دخول وكيل في دائرة مفرغة، يتم اعتراض العمل وإيقافه فوراً.
-  2. **التشريح الاستباقي الصارم (Prompt Autopsy &amp; Root-Cause Analysis):** يُمنع على `prompt-engineer` تقديم برومبت جديد مباشرة. يجب أولاً طباعة قسم `[ROOT-CAUSE ANALYSIS]` يشرح بوضوح سبب الانحراف السابق (هلوسة وكيل، غياب سياق، أو معمارية خاطئة).
-  3. **حماية السياق (Context Preservation):** تحديد المتطلبات أو الملفات التي كانت تنقص الوكيل السابق للعمل بشكل صحيح تحت قسم `[MISSING ARTIFACTS / INFO]`.
-  4. **إعادة الصياغة والتوجيه القاطع (Explicit Rerouting):** توليد التوجيه الهندسي الجديد تحت قسم `[RE-ENGINEERED PROMPT]` مقترناً بشكل صريح بالوكيل الفرعي المستهدف `[TARGET HOOK]` الذي سيستلم المهمة ليكملها بنظافة.</t>
+  1. **تحليل سياق المشروع المعتمد (`project_agent_tailor.py`):** فحص ملف `PROJECT_CONTEXT.md` واكتشاف حزم التقنيات المستخدمة (مثل: `android_compose`, `web`, `python_ai`, `construction_survey`).
+  2. **تصدير حزم الوكلاء والمهارات المطلوبة:** نسخ مهارات وبطاقات الوكلاء المتخصصين وحزمة النواة حصرياً إلى مجلد المشروع المحلي `.agents/`.
+  3. **التنظيف التلقائي الصارم للمهارات الفائضة (Pruning Engine):** مسح وحذف أي مهارات أو بطاقات وكلاء غير مستخدمة في المشروع المستهدف، لحماية نافذة السياق (Context Budget) من الهدر بنسبة 100%.
+  4. **توليد قالب المزامنة المحلي (`sync_local_agents.py`):** إنشاء سكربت خفيف داخل المشروع لتمكين المطور من تحديث طاقم المشروع بنقرة زر واحدة مستقبلاً دون المساس بخصوصية المشروع.</t>
         </is>
       </c>
     </row>
@@ -2889,39 +3441,37 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>4. خطاف خط الإنتاج البرمجي</t>
+          <t>4. خطاف الإشراف العام وتصحيح المسار</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>ابدأ ميزة, تطوير ميزة, اصنع ميزة, إصلاح ميزة</t>
+          <t>تصحيح مسار, تعديل البرومبت, خطأ بالخطاف, تصحيح خطاف</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
- البديل: `Claude Opus 4.6 (Thinking)`</t>
+ البديل: `Gemini 3.7 Flash (High)`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>[code-architect], [android-kotlin-pro], [jetpack-compose-ui], [code-reviewer-quality], [clean-code-guard], [android-testing], [test-guard]</t>
+          <t>[prompt-engineer], [agent-optimizer]</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>تنفيذ دورة التطوير الكاملة (المعمارية، البرمجة، حراسة الكود النظيف، والفحص والاختبار).</t>
+          <t>تصحيح الخطافات الخاطئة والبرومبتات غير الاحترافية وتوجيهها للمسار الصحيح تلقائياً.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  0. **حقن السياق الإجباري (Mandatory Context Injection):** يُلزم الوكيل الرئيسي بتشغيل أداة حقن السياق (`python .agents/inject_context.py`) وتمرير مخرجاتها كـ `System Alert` أو `&gt; [!WARNING] Mandatory Constraints` في المحادثة قبل بدء أي عمل.
-  1. **التصميم المعماري الهيكلي (`code-architect`):** يبدأ برسم معمارية الميزة وتحديد مواقع وتسمية الملفات الجديدة/المعدلة في الهيكل المناسب (Data/Domain/UI).
-  2. **التدقيق المعماري الصارم وحلقة الـ 7 مرات (7-Iterations Devil's Advocate Loop):** يُمنع منعاً باتاً البدء بكتابة الكود. يجب إدخال خطة التنفيذ (`implementation_plan.md`) في حلقة مراجعة وتدقيق مع "محامي الشيطان" **لـ 7 مرات متتالية** حتى يتم سد كل الثغرات والوصول لنسبة نجاح 99.99% وتأمين قسم `[UNINTENDED SIDE-EFFECTS &amp; LIFECYCLE HAZARDS]` بالكامل قبل السماح بالكتابة.
-  3. **الكتابة البرمجية (Surgical Precision Execution):** يستلم الوكيل `[android-kotlin-pro]` أو `[jetpack-compose-ui]` الخطة المعتمدة ويبدأ بالتنفيذ. **يُحقن الوكيل بالبرومبت الإجباري التالي:** *(يُمنع منعاً باتاً المساس، أو تعديل، أو حذف أي كود حالي في المشروع لا ينص عليه صراحة في خطة التنفيذ. تصرف كجراح دقيق: أضف ميزتك فقط دون إحداث أي تغييرات جانبية في الملفات المفتوحة).*
-  4. **المراجعة وحراسة الكود النظيف (`code-reviewer-quality` + `clean-code-guard`):** يفحص الكود بعد كتابته للتحقق من الاتساق، وخلوه من أخطاء الـ AI الـ 14 الشائعة (ابتلاع الأخطاء، تضخم الدوال، الأكواد المكررة).
-  5. **الأتمتة والاختبار النظيف (`android-testing` + `test-guard`):** ينهي الدورة بكتابة وتشغيل اختبارات الوحدة (JUnit/MockK) وفق معايير `test-guard` للتحقق من سلوك النظام الفعلي وليس فقط الـ Happy Path، وتجنب الـ Mocks المفرطة.</t>
+  1. **الرصد التلقائي والإيقاف:** يقوم الوكيل الرئيسي بمراقبة المحادثة. عند استخدام المستخدم لمحفز "تصحيح مسار"، أو عند رصد دخول وكيل في دائرة مفرغة، يتم اعتراض العمل وإيقافه فوراً.
+  2. **التشريح الاستباقي الصارم (Prompt Autopsy &amp; Root-Cause Analysis):** يُمنع على `prompt-engineer` تقديم برومبت جديد مباشرة. يجب أولاً طباعة قسم `[ROOT-CAUSE ANALYSIS]` يشرح بوضوح سبب الانحراف السابق (هلوسة وكيل، غياب سياق، أو معمارية خاطئة).
+  3. **حماية السياق (Context Preservation):** تحديد المتطلبات أو الملفات التي كانت تنقص الوكيل السابق للعمل بشكل صحيح تحت قسم `[MISSING ARTIFACTS / INFO]`.
+  4. **إعادة الصياغة والتوجيه القاطع (Explicit Rerouting):** توليد التوجيه الهندسي الجديد تحت قسم `[RE-ENGINEERED PROMPT]` مقترناً بشكل صريح بالوكيل الفرعي المستهدف `[TARGET HOOK]` الذي سيستلم المهمة ليكملها بنظافة.</t>
         </is>
       </c>
     </row>
@@ -2991,37 +3541,37 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>5. خطاف التكامل الفني</t>
+          <t>5. خطاف خط الإنتاج البرمجي</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>ربط API, تكامل خارجي</t>
+          <t>ابدأ ميزة, تطوير ميزة, اصنع ميزة, إصلاح ميزة</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 3.7 Flash (High)` 
- البديل: `Claude Sonnet 4.6 (Thinking)`</t>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Claude Opus 4.6 (Thinking)`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>[devops-deployer], [backend-architect]</t>
+          <t>[code-architect], [ui-ux-pro-max], [clean-code-guard], [test-guard]</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>ربط وتكامل الخدمات الخارجية بعد مراجعة وثائقها الرسمية وتأمين المتغيرات.</t>
+          <t>تنفيذ دورة التطوير الكاملة (المعمارية، الذكاء التصميمي، البرمجة، حراسة الكود النظيف، والفحص والاختبار).</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  1. **قراءة الوثائق:** يقرأ الوكيل `[devops-deployer]` وثائق الـ API الخارجية الرسمية المدخلة قبل البدء بالدمج.
-  2. **تحصين الانقطاع (API FAULT TOLERANCE CHECK):** يُمنع الدمج دون بناء `Interceptor` لمعالجة انقطاع الشبكة وإعادة المحاولة (Retry Mechanism)، وتغليف الردود بـ `Result&lt;T&gt;` أو `ErrorMapper` لمعالجة أخطاء HTTP (401, 404, 500).
-  3. **توليد الـ Wrapper:** عزل منطق التكامل في كلاسات مغلفة منفصلة لتجنب تشتيت الكود الأساسي للمشروع وضمان التخزين المؤقت (Offline-First).
-  4. **حماية البيئة:** التأكد من عدم كتابة أي كود يحتوي على مفاتيح سرية (API Keys) في مستودع الكود وتخزينها في متغيرات البيئة فقط.</t>
+  1. **التصميم الهيكلي والذكاء التصميمي (`code-architect` + `ui-ux-pro-max`):** تحديد المعمارية المناسبة، واستدعاء محرك الاستدلال التصميمي لتحديد نمط الواجهات (Style)، باليت الألوان الدلالية، والخطوط وقواعد سهولة الوصول بدقة قبل كتابة أي واجهة.
+  2. **التدقيق المعماري الصارم (Devil's Advocate Audit):** مراجعة الخطة وكشف الثغرات وحالات الحافة لمنع الآثار الجانبية.
+  3. **الكتابة البرمجية والتنفيذ:** كتابة الكود وبناء الواجهات وقواعد البيانات محلياً.
+  4. **المراجعة وضمان الجودة (`clean-code-guard` + `test-guard`):** فحص الكود للأمان، الأداء، والتوافق مع المعايير.</t>
         </is>
       </c>
     </row>
@@ -3091,36 +3641,36 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>6. خطاف تدقيق الصيانة</t>
+          <t>6. خطاف التكامل الفني</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>تدقيق صيانة, مراجعة DRY, كود نظيف</t>
+          <t>ربط API, تكامل خارجي</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
- البديل: `Gemini 3.7 Flash (High)`</t>
+          <t>الأساسي: `Gemini 3.7 Flash (High)` 
+ البديل: `Claude Sonnet 4.6 (Thinking)`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>[code-reviewer-quality], [clean-code-guard], [performance-optimizer]</t>
+          <t>[devops-deployer], [backend-architect]</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>مراجعة الكود البرمجي بانتظام لمنع التكرار وتراكم الديون التقنية وتطبيق معايير الكود النظيف.</t>
+          <t>ربط وتكامل الخدمات الخارجية بعد مراجعة وثائقها الرسمية وتأمين المتغيرات.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  1. **فحص الكود النظيف والمكرر:** استدعاء الوكيل `[code-reviewer-quality]` و `[clean-code-guard]` لمسح الملفات والتحقق من عدم وجود دوال أو منطق مكرر (تطبيق مبدأ DRY/KISS/YAGNI) والحد من التعقيد الحسابي.
-  2. **فحص Recomposition والأداء:** قياس كفاءة الرسم وإعاقات الأداء في Compose بواسطة `[performance-optimizer]`.
-  3. **إنشاء تقرير Refactoring:** تزويد المطور بقائمة تعديلات مقترحة لتسهيل القراءة وضغط الكود وحذف الأكواد الميتة (Dead Code).</t>
+  1. **قراءة الوثائق:** يقرأ الوكيل `[devops-deployer]` وثائق الـ API الخارجية الرسمية المدخلة قبل البدء بالدمج.
+  2. **تحصين الانقطاع (API FAULT TOLERANCE CHECK):** بناء Interceptor لمعالجة انقطاع الشبكة وإعادة المحاولة وتأمين المفاتيح في متغيرات البيئة.
+  3. **توليد الـ Wrapper:** عزل منطق التكامل في كلاسات مغلفة منفصلة لتجنب تشتيت الكود الأساسي للمشروع.</t>
         </is>
       </c>
     </row>
@@ -3190,36 +3740,35 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>7. خطاف الفحص الأمني</t>
+          <t>7. خطاف تدقيق الصيانة</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>فحص أمني, مراجعة أمان</t>
+          <t>تدقيق صيانة, مراجعة DRY, كود نظيف</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
- البديل: `Claude Opus 4.6 (Thinking)`</t>
+ البديل: `Gemini 3.7 Flash (High)`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>[security-auditor], [code-reviewer-quality]</t>
+          <t>[code-reviewer-quality], [clean-code-guard], [performance-optimizer]</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>مراجعة ثغرات الأمان والتحقق من صحة المدخلات وتشفير البيانات وتأمين الوصول.</t>
+          <t>مراجعة الكود البرمجي بانتظام لمنع التكرار وتراكم الديون التقنية وتطبيق معايير الكود النظيف.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  1. **مصفوفة الثغرات الصارمة (VULNERABILITY MATRIX):** مسح إجباري لـ AndroidManifest للبحث عن المكونات المكشوفة (`Exported=true`)، وتسريب البيانات عبر `Intents` (Intent Hijacking)، وقواعد `ProGuard`.
-  2. **التحقق من صحة المدخلات:** التأكد من وجود معالجة وفحص صريح لكل المدخلات والطلبات الخارجية قبل تمريرها لطبقة البيانات.
-  3. **فحص تشفير البيانات:** التحقق من تشفير البيانات الحساسة و `SharedPreferences` والجلسات وحمايتها محلياً وسحابياً (إلزام إخراج تقرير يؤكد الفحص).</t>
+  1. **فحص الكود النظيف والمكرر:** استدعاء الوكيل `[code-reviewer-quality]` و `[clean-code-guard]` لمسح الملفات والتحقق من عدم وجود دوال مكررة (تطبيق DRY/KISS/YAGNI).
+  2. **فحص Recomposition والأداء:** قياس كفاءة الرسم وإعاقات الأداء في Compose بواسطة `[performance-optimizer]`.</t>
         </is>
       </c>
     </row>
@@ -3289,44 +3838,35 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>8. خطاف مراجعة وتحديث المكتبات والنماذج</t>
+          <t>8. خطاف الفحص الأمني</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>تحديث الاعتماديات, تحديث المكتبات, تحديث النماذج, معايرة النماذج, update models</t>
+          <t>فحص أمني, مراجعة أمان</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>الأساسي: `Gemini 3.7 Flash (High)` 
- البديل: `Gemini 3.6 Flash (Medium)`</t>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Claude Opus 4.6 (Thinking)`</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>[github-talent-scout], [code-architect], [agent-optimizer]</t>
+          <t>[security-auditor], [code-reviewer-quality]</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>فحص ملفات Gradle وتحديث المكتبات، والتحقق التلقائي عبر الإنترنت (antigravity.google) لتحديث مصفوفة النماذج ودليل hooks_user_guide.md دون لقطات شاشة.</t>
+          <t>مراجعة ثغرات الأمان والتحقق من صحة المدخلات وتشفير البيانات وتأمين الوصول.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  1. **فحص إصدارات المكتبات:** مسح ملفات `build.gradle.kts` ومقارنة إصدارات المكتبات الحالية بأحدث الإصدارات المستقرة.
-  2. **الاستكشاف والمعايرة التلقائية للنماذج عبر الإنترنت (Online Model Discovery):**
-     - عند كتابة محفز `"تحديث النماذج"` أو `"معايرة النماذج"`، يقوم الوكيل `[agent-optimizer]` بالاستعلام الفوري عبر الإنترنت من المصادر الرسمية:
-       - 🌐 بوابة Google Antigravity الرسمية: `https://antigravity.google`
-       - 🌐 مدونة مطوري جوجل: `https://google.dev` و `https://blog.google`
-       - 🌐 دليل وثائق Anthropic: `https://docs.anthropic.com`
-     - يتم استخراج قائمة النماذج الفعالة في المحرر (مثل `Gemini 3.7 Flash`, `Claude Sonnet 4.6 (Thinking)`).
-  3. **التحديث والمزامنة الشاملة:**
-     - تحديث مصفوفة النماذج في `HOOKS_GUIDE.md` ودليل مسار العمل `hooks_user_guide.md`.
-     - تشغيل السكربتات لتحديث ملف الإكسيل `HOOKS_GUIDE.xlsx` وتطبيق مكتبة الأوامر HTML.
-     - تشغيل `sync_global_ecosystem.py` ورفع التحديثات لـ GitHub تلقائياً.</t>
+  1. **مصفوفة الثغرات الصارمة (VULNERABILITY MATRIX):** مسح إجباري لـ AndroidManifest والمكونات المكشوفة وتسريب البيانات.
+  2. **التحقق من صحة المدخلات وتشفير البيانات:** فحص تشفير البيانات الحساسة والجلسات وتأمين الوصول محلياً وسحابياً.</t>
         </is>
       </c>
     </row>

--- a/HOOKS_GUIDE.xlsx
+++ b/HOOKS_GUIDE.xlsx
@@ -32,6 +32,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22. خطاف قيادة وإدارة الأسطول" sheetId="23" state="visible" r:id="rId23"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23. خطاف تحويل وأتمتة سكربتات" sheetId="24" state="visible" r:id="rId24"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24. خطاف أتمتة مسارات العمل و" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25. خطاف تجميد وتسليم الجلسة " sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -473,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1471,7 +1472,49 @@
   4. **أتمتة العمليات التسويقية وتأهيل العملاء (Marketing &amp; CRM Pipelines):**
      - بناء مسارات استقبال وتحليل بيانات العملاء المحتملين من Google Ads و Facebook وتوجيه الإشعارات اللحظية عبر WhatsApp و Slack وتحديث الـ CRM.
   5. **تحصين الانقطاع ومعالجة الأخطاء (Fault Tolerance &amp; Sub-workflow Retries):**
-     - إضافة مسارات الخطأ (Error Trigger) وإعادة المحاولة مع التراجع التلقائي (Exponential Backoff) ونماذج LLM البديلة.
+     - إضافة مسارات الخطأ (Error Trigger) وإعادة المحاولة مع التراجع التلقائي (Exponential Backoff) ونماذج LLM البديلة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>25. خطاف تجميد وتسليم الجلسة قبل التصفير</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>استعد للتصفير, تجهيز clear, تجميد الجلسة, pre-clear handoff, prepare clear, freeze session, قبل التصفير</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Opus 5 (Thinking)` 
+ البديل: `Claude Sonnet 5`</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>[fleet-orchestrator], [persistent-memory-engine], [git-github-manager]</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>تجميد وتوثيق حالة الجلسة بالكامل قبل تنفيذ أمر /clear أو /compact، وتحديث ملف الحالة CURRENT_STATE.md وسجل الـ Git، وتوليد برومبت الاستئناف الفوري بنقرة واحدة لتفادي فقدان السياق عند امتلاء الجلسة (session:90%+).</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **الرصد والاستعداد للحد الحرج:** يُستدعى هذا الخطاف تلقائياً أو يدوياً عندما تبلغ الجلسة حداً مرتفعاً من الاستهلاك (مثل `session:90%` كما في طرفية Claude Code CLI أو `40%` كحد وقائي قبل تراجع جودة الذاكرة).
+  2. **تجميد وتوثيق الحالة (Freeze State):** يقوم الوكيل بمطابقة وتحديث ملف `fleet_orders/CURRENT_STATE.md` فوراً، وتوثيق آخر Commit تم اعتماده، والفرع النشط، والمهام المكتملة ونتائج بوابات الجودة (Quality Gates).
+  3. **فحص الـ Git وتأمين شجرة العمل:** التأكد من عدم وجود تعديلات عائمة أو غير محفوظة، ومزامنة أي دروس مستفادة أو ملاحظات عتادية (مثل اختناق ذاكرة R8 B-17) في `MEMORY_STORE.md`.
+  4. **تحديد خيارات المطور للمرحلة القادمة:** توضيح الخيارات والخطوة التالية المتاحة للمطور (Next Action / Next Orders) بصياغة مباشرة محددة.
+  5. **توليد برومبت الاستئناف الفوري (Resume Prompt):** طباعة برومبت جاهز للنسخ بنقرة واحدة ليلصقه المطور مباشرة في الجلسة الجديدة فور كتابة `/clear`.
+  6. **إعطاء الضوء الأخضر:** إشعار المستخدم باكتمال التجميد وإمكانية كتابة أمر `/clear` في الطرفية بأمان تام دون أي خطر لفقدان السياق.
 &lt;/div&gt;</t>
         </is>
       </c>
@@ -3170,7 +3213,109 @@
   4. **أتمتة العمليات التسويقية وتأهيل العملاء (Marketing &amp; CRM Pipelines):**
      - بناء مسارات استقبال وتحليل بيانات العملاء المحتملين من Google Ads و Facebook وتوجيه الإشعارات اللحظية عبر WhatsApp و Slack وتحديث الـ CRM.
   5. **تحصين الانقطاع ومعالجة الأخطاء (Fault Tolerance &amp; Sub-workflow Retries):**
-     - إضافة مسارات الخطأ (Error Trigger) وإعادة المحاولة مع التراجع التلقائي (Exponential Backoff) ونماذج LLM البديلة.
+     - إضافة مسارات الخطأ (Error Trigger) وإعادة المحاولة مع التراجع التلقائي (Exponential Backoff) ونماذج LLM البديلة.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>اسم الخطاف</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>المحفزات (الخطاف للنسخ)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>النموذج الأساسي والبديل</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>الوكلاء المسؤولون</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>الهدف الأساسي</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>الوصف والتفاصيل</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>25. خطاف تجميد وتسليم الجلسة قبل التصفير</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>استعد للتصفير, تجهيز clear, تجميد الجلسة, pre-clear handoff, prepare clear, freeze session, قبل التصفير</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Opus 5 (Thinking)` 
+ البديل: `Claude Sonnet 5`</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[fleet-orchestrator], [persistent-memory-engine], [git-github-manager]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>تجميد وتوثيق حالة الجلسة بالكامل قبل تنفيذ أمر /clear أو /compact، وتحديث ملف الحالة CURRENT_STATE.md وسجل الـ Git، وتوليد برومبت الاستئناف الفوري بنقرة واحدة لتفادي فقدان السياق عند امتلاء الجلسة (session:90%+).</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **الرصد والاستعداد للحد الحرج:** يُستدعى هذا الخطاف تلقائياً أو يدوياً عندما تبلغ الجلسة حداً مرتفعاً من الاستهلاك (مثل `session:90%` كما في طرفية Claude Code CLI أو `40%` كحد وقائي قبل تراجع جودة الذاكرة).
+  2. **تجميد وتوثيق الحالة (Freeze State):** يقوم الوكيل بمطابقة وتحديث ملف `fleet_orders/CURRENT_STATE.md` فوراً، وتوثيق آخر Commit تم اعتماده، والفرع النشط، والمهام المكتملة ونتائج بوابات الجودة (Quality Gates).
+  3. **فحص الـ Git وتأمين شجرة العمل:** التأكد من عدم وجود تعديلات عائمة أو غير محفوظة، ومزامنة أي دروس مستفادة أو ملاحظات عتادية (مثل اختناق ذاكرة R8 B-17) في `MEMORY_STORE.md`.
+  4. **تحديد خيارات المطور للمرحلة القادمة:** توضيح الخيارات والخطوة التالية المتاحة للمطور (Next Action / Next Orders) بصياغة مباشرة محددة.
+  5. **توليد برومبت الاستئناف الفوري (Resume Prompt):** طباعة برومبت جاهز للنسخ بنقرة واحدة ليلصقه المطور مباشرة في الجلسة الجديدة فور كتابة `/clear`.
+  6. **إعطاء الضوء الأخضر:** إشعار المستخدم باكتمال التجميد وإمكانية كتابة أمر `/clear` في الطرفية بأمان تام دون أي خطر لفقدان السياق.
 &lt;/div&gt;</t>
         </is>
       </c>

--- a/HOOKS_GUIDE.xlsx
+++ b/HOOKS_GUIDE.xlsx
@@ -32,7 +32,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22. خطاف قيادة وإدارة الأسطول" sheetId="23" state="visible" r:id="rId23"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23. خطاف تحويل وأتمتة سكربتات" sheetId="24" state="visible" r:id="rId24"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24. خطاف أتمتة مسارات العمل و" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25. خطاف تجميد وتسليم الجلسة " sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25. خطاف التصفير الاستراتيجي " sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1482,12 +1482,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>25. خطاف تجميد وتسليم الجلسة قبل التصفير</t>
+          <t>25. خطاف التصفير الاستراتيجي وتسليم الجلسة</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>استعد للتصفير, تجهيز clear, تجميد الجلسة, pre-clear handoff, prepare clear, freeze session, قبل التصفير</t>
+          <t>التصفير الاستراتيجي, strategic clear, استعد للتصفير, تجهيز clear, تجميد الجلسة, pre-clear handoff, freeze session</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1503,18 +1503,25 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>تجميد وتوثيق حالة الجلسة بالكامل قبل تنفيذ أمر /clear أو /compact، وتحديث ملف الحالة CURRENT_STATE.md وسجل الـ Git، وتوليد برومبت الاستئناف الفوري بنقرة واحدة لتفادي فقدان السياق عند امتلاء الجلسة (session:90%+).</t>
+          <t>تقييم وإنهاء أي مهام عالقة أو ذات أولوية عاجلة لتأمين استقرار الكود، ثم تجميد وتوثيق الحالة في CURRENT_STATE.md وتوليد برومبت الاستئناف الفوري قبل تنفيذ /clear أو /compact عند امتلاء الجلسة (session:90%+).</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  1. **الرصد والاستعداد للحد الحرج:** يُستدعى هذا الخطاف تلقائياً أو يدوياً عندما تبلغ الجلسة حداً مرتفعاً من الاستهلاك (مثل `session:90%` كما في طرفية Claude Code CLI أو `40%` كحد وقائي قبل تراجع جودة الذاكرة).
-  2. **تجميد وتوثيق الحالة (Freeze State):** يقوم الوكيل بمطابقة وتحديث ملف `fleet_orders/CURRENT_STATE.md` فوراً، وتوثيق آخر Commit تم اعتماده، والفرع النشط، والمهام المكتملة ونتائج بوابات الجودة (Quality Gates).
-  3. **فحص الـ Git وتأمين شجرة العمل:** التأكد من عدم وجود تعديلات عائمة أو غير محفوظة، ومزامنة أي دروس مستفادة أو ملاحظات عتادية (مثل اختناق ذاكرة R8 B-17) في `MEMORY_STORE.md`.
-  4. **تحديد خيارات المطور للمرحلة القادمة:** توضيح الخيارات والخطوة التالية المتاحة للمطور (Next Action / Next Orders) بصياغة مباشرة محددة.
-  5. **توليد برومبت الاستئناف الفوري (Resume Prompt):** طباعة برومبت جاهز للنسخ بنقرة واحدة ليلصقه المطور مباشرة في الجلسة الجديدة فور كتابة `/clear`.
-  6. **إعطاء الضوء الأخضر:** إشعار المستخدم باكتمال التجميد وإمكانية كتابة أمر `/clear` في الطرفية بأمان تام دون أي خطر لفقدان السياق.
+  1. **المرحلة الأولى: المسح السريع وإنهاء المهام العالقة ذات الأولوية (In-Flight Work Resolution &amp; Stabilization):**
+     - جرد فوري لأي مهام أو أوامر ذات أولوية قصوى قيد التنفيذ قبل اتخاذ قرار التصفير.
+     - إذا كانت المهمة قريبة من الإنجاز: يتم إكمالها فوراً وبناء الكود وفحصه برمجياً واعتماده بعمل `git commit` نظيف ومحكم.
+     - إذا كانت المهمة كبيرة وتحتاج جولات إضافية: يتم تثبيت الكود عند محطة استقرار آمنة (Compilable Milestone) وعزل أي تجارب ناقصة لضمان بقاء الفرع أخضر 100% وخالياً من أي أخطاء كسر بناء.
+  2. **المرحلة الثانية: تجميد الحالة وتوثيق سياق المشروع وحراسة الذاكرة (State Freeze &amp; Memory Quarantine):**
+     - مطابقة وتحديث ملف الحالة `fleet_orders/CURRENT_STATE.md` (أو `PROJECT_CONTEXT.md`) وتحديث بند "الخطوة التالية المحددة" (The One Thing To Do Next).
+     - فحص ومطابقة `git status --short --branch` للتأكد من خلو شجرة العمل من أي تعديلات تائهة أو غير معتمدة.
+     - تسجيل أي اكتشافات أو ملاحظات عتادية أو فخاخ برمجية جديدة في `MEMORY_STORE.md`.
+  3. **المرحلة الثالثة: تحديد القرارات وتوليد برومبت الاستئناف الفوري (Resume Prompt &amp; Green Light):**
+     - صياغة ملخص تسليم محكم يتضمن: ما تم إنجازه، آخر Commit معتمد، والخيارات المتاحة أمام المطور للجلسة القادمة.
+     - توليد برومبت استئناف دقيق (Ready to copy-paste) لنسخه ولصقه فور تنفيذ أمر التصفير:
+       `Read CLAUDE.md and fleet_orders/CURRENT_STATE.md. State where we are and present the choices for the next order.`
+     - منح الضوء الأخضر الصريح للمطور: تأكيد إمكانية تنفيذ أمر `/clear` أو `/compact` بأمان تام وبدون أي هدر للسياق.
 &lt;/div&gt;</t>
         </is>
       </c>
@@ -3283,12 +3290,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>25. خطاف تجميد وتسليم الجلسة قبل التصفير</t>
+          <t>25. خطاف التصفير الاستراتيجي وتسليم الجلسة</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>استعد للتصفير, تجهيز clear, تجميد الجلسة, pre-clear handoff, prepare clear, freeze session, قبل التصفير</t>
+          <t>التصفير الاستراتيجي, strategic clear, استعد للتصفير, تجهيز clear, تجميد الجلسة, pre-clear handoff, freeze session</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -3304,18 +3311,25 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>تجميد وتوثيق حالة الجلسة بالكامل قبل تنفيذ أمر /clear أو /compact، وتحديث ملف الحالة CURRENT_STATE.md وسجل الـ Git، وتوليد برومبت الاستئناف الفوري بنقرة واحدة لتفادي فقدان السياق عند امتلاء الجلسة (session:90%+).</t>
+          <t>تقييم وإنهاء أي مهام عالقة أو ذات أولوية عاجلة لتأمين استقرار الكود، ثم تجميد وتوثيق الحالة في CURRENT_STATE.md وتوليد برومبت الاستئناف الفوري قبل تنفيذ /clear أو /compact عند امتلاء الجلسة (session:90%+).</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  1. **الرصد والاستعداد للحد الحرج:** يُستدعى هذا الخطاف تلقائياً أو يدوياً عندما تبلغ الجلسة حداً مرتفعاً من الاستهلاك (مثل `session:90%` كما في طرفية Claude Code CLI أو `40%` كحد وقائي قبل تراجع جودة الذاكرة).
-  2. **تجميد وتوثيق الحالة (Freeze State):** يقوم الوكيل بمطابقة وتحديث ملف `fleet_orders/CURRENT_STATE.md` فوراً، وتوثيق آخر Commit تم اعتماده، والفرع النشط، والمهام المكتملة ونتائج بوابات الجودة (Quality Gates).
-  3. **فحص الـ Git وتأمين شجرة العمل:** التأكد من عدم وجود تعديلات عائمة أو غير محفوظة، ومزامنة أي دروس مستفادة أو ملاحظات عتادية (مثل اختناق ذاكرة R8 B-17) في `MEMORY_STORE.md`.
-  4. **تحديد خيارات المطور للمرحلة القادمة:** توضيح الخيارات والخطوة التالية المتاحة للمطور (Next Action / Next Orders) بصياغة مباشرة محددة.
-  5. **توليد برومبت الاستئناف الفوري (Resume Prompt):** طباعة برومبت جاهز للنسخ بنقرة واحدة ليلصقه المطور مباشرة في الجلسة الجديدة فور كتابة `/clear`.
-  6. **إعطاء الضوء الأخضر:** إشعار المستخدم باكتمال التجميد وإمكانية كتابة أمر `/clear` في الطرفية بأمان تام دون أي خطر لفقدان السياق.
+  1. **المرحلة الأولى: المسح السريع وإنهاء المهام العالقة ذات الأولوية (In-Flight Work Resolution &amp; Stabilization):**
+     - جرد فوري لأي مهام أو أوامر ذات أولوية قصوى قيد التنفيذ قبل اتخاذ قرار التصفير.
+     - إذا كانت المهمة قريبة من الإنجاز: يتم إكمالها فوراً وبناء الكود وفحصه برمجياً واعتماده بعمل `git commit` نظيف ومحكم.
+     - إذا كانت المهمة كبيرة وتحتاج جولات إضافية: يتم تثبيت الكود عند محطة استقرار آمنة (Compilable Milestone) وعزل أي تجارب ناقصة لضمان بقاء الفرع أخضر 100% وخالياً من أي أخطاء كسر بناء.
+  2. **المرحلة الثانية: تجميد الحالة وتوثيق سياق المشروع وحراسة الذاكرة (State Freeze &amp; Memory Quarantine):**
+     - مطابقة وتحديث ملف الحالة `fleet_orders/CURRENT_STATE.md` (أو `PROJECT_CONTEXT.md`) وتحديث بند "الخطوة التالية المحددة" (The One Thing To Do Next).
+     - فحص ومطابقة `git status --short --branch` للتأكد من خلو شجرة العمل من أي تعديلات تائهة أو غير معتمدة.
+     - تسجيل أي اكتشافات أو ملاحظات عتادية أو فخاخ برمجية جديدة في `MEMORY_STORE.md`.
+  3. **المرحلة الثالثة: تحديد القرارات وتوليد برومبت الاستئناف الفوري (Resume Prompt &amp; Green Light):**
+     - صياغة ملخص تسليم محكم يتضمن: ما تم إنجازه، آخر Commit معتمد، والخيارات المتاحة أمام المطور للجلسة القادمة.
+     - توليد برومبت استئناف دقيق (Ready to copy-paste) لنسخه ولصقه فور تنفيذ أمر التصفير:
+       `Read CLAUDE.md and fleet_orders/CURRENT_STATE.md. State where we are and present the choices for the next order.`
+     - منح الضوء الأخضر الصريح للمطور: تأكيد إمكانية تنفيذ أمر `/clear` أو `/compact` بأمان تام وبدون أي هدر للسياق.
 &lt;/div&gt;</t>
         </is>
       </c>

--- a/HOOKS_GUIDE.xlsx
+++ b/HOOKS_GUIDE.xlsx
@@ -1365,11 +1365,13 @@
      - تحديد ملكية الملفات والمهام في `fleet_config.json` لمنع التصادم:
        - **Claude Code CLI** (النموذج: `Claude 5 Opus / Opus Max`): التخطيط والمراجعة المعمارية، **التنفيذ الحصري لكافة الاختبارات التلقائية**، واعتماد الأكواد وبوابات الجودة (Quality Gates).
        - **OpenCode CLI** (النموذج: `Ox Alpha Unlimited`): التنفيذ الطرفي، إدارة قواعد البيانات Drift/ORM، وعملاء الاتصال والبيانات (كتابة وبناء فقط دون تشغيل أي اختبارات).
-       - **Antigravity IDE** (النموذج: `Gemini 3.7 Flash High`): بناء الواجهات والـ Domain Logic، إدارة الذاكرة المستدامة، وهندسة السياق (كتابة وبناء فقط دون تشغيل أي اختبارات).
+       - **Antigravity CLI (`agcli`)** (النموذج: `Gemini 3.8 Flash High` / `hermes3:8b` Ollama): المنفذ الطرفي الذاتي لبناء الواجهات (UI)، تكييف المنصات، عقود الـ Domain، وهندسة الملفات (كتابة وبناء دون تشغيل اختبارات عبر سطر الأوامر دون نسخ ولصق).
+       - **Antigravity IDE** (النموذج: `Gemini 3.8 Flash High`): بيئة العمل التفاعلية وحاضنة المطور المركزية (Interactive Cockpit) لإدارة الجلسة والمحادثة واستعراض الفروقات (Diffs)؛ ولا تُوجّه أوامر تفويض الـ CLI البرمجية إليها لمنع تعليق الأتمتة.
   3. **التشغيل المباشر لأدوات الـ CLI (Headless Direct Invocation):**
      - تشغيل واستدعاء أدوات الـ CLI المثبتة مباشرة عبر سطر الأوامر غير التفاعلي:
        - استدعاء `Claude Code CLI` للمراجعة المعمارية وتشغيل الاختبارات وتدقيق الكود عبر: `claude -p "&lt;prompt&gt;"` أو `claude --print`.
        - استدعاء `OpenCode CLI` لتنفيذ الأوامر السريعة والطرفية وبناء قواعد البيانات عبر: `opencode run "&lt;message&gt;"`.
+       - استدعاء `Antigravity CLI` لمهام الواجهات وعقود الـ Domain عبر: `agcli run "&lt;message&gt;"`.
      - معالجة وإدراج مخرجات الـ CLIs تلقائياً في دورة التطوير وبوابات الجودة.
   4. **التحويل المستدام لنمط المحادثة (Session-Wide Fleet Mode Transformation):**
      - **قاعدة حاسمة:** بمجرد استدعاء وتفعيل الخطاف 22 (بالمحفزات المعتمدة أو ذكر خطاف 22)، يدخل المساعد فوراً ومستداماً في **نمط قيادة الأسطول (Fleet Command Mode)** لكامل ما تبقى من الجلسة.
@@ -2993,11 +2995,13 @@
      - تحديد ملكية الملفات والمهام في `fleet_config.json` لمنع التصادم:
        - **Claude Code CLI** (النموذج: `Claude 5 Opus / Opus Max`): التخطيط والمراجعة المعمارية، **التنفيذ الحصري لكافة الاختبارات التلقائية**، واعتماد الأكواد وبوابات الجودة (Quality Gates).
        - **OpenCode CLI** (النموذج: `Ox Alpha Unlimited`): التنفيذ الطرفي، إدارة قواعد البيانات Drift/ORM، وعملاء الاتصال والبيانات (كتابة وبناء فقط دون تشغيل أي اختبارات).
-       - **Antigravity IDE** (النموذج: `Gemini 3.7 Flash High`): بناء الواجهات والـ Domain Logic، إدارة الذاكرة المستدامة، وهندسة السياق (كتابة وبناء فقط دون تشغيل أي اختبارات).
+       - **Antigravity CLI (`agcli`)** (النموذج: `Gemini 3.8 Flash High` / `hermes3:8b` Ollama): المنفذ الطرفي الذاتي لبناء الواجهات (UI)، تكييف المنصات، عقود الـ Domain، وهندسة الملفات (كتابة وبناء دون تشغيل اختبارات عبر سطر الأوامر دون نسخ ولصق).
+       - **Antigravity IDE** (النموذج: `Gemini 3.8 Flash High`): بيئة العمل التفاعلية وحاضنة المطور المركزية (Interactive Cockpit) لإدارة الجلسة والمحادثة واستعراض الفروقات (Diffs)؛ ولا تُوجّه أوامر تفويض الـ CLI البرمجية إليها لمنع تعليق الأتمتة.
   3. **التشغيل المباشر لأدوات الـ CLI (Headless Direct Invocation):**
      - تشغيل واستدعاء أدوات الـ CLI المثبتة مباشرة عبر سطر الأوامر غير التفاعلي:
        - استدعاء `Claude Code CLI` للمراجعة المعمارية وتشغيل الاختبارات وتدقيق الكود عبر: `claude -p "&lt;prompt&gt;"` أو `claude --print`.
        - استدعاء `OpenCode CLI` لتنفيذ الأوامر السريعة والطرفية وبناء قواعد البيانات عبر: `opencode run "&lt;message&gt;"`.
+       - استدعاء `Antigravity CLI` لمهام الواجهات وعقود الـ Domain عبر: `agcli run "&lt;message&gt;"`.
      - معالجة وإدراج مخرجات الـ CLIs تلقائياً في دورة التطوير وبوابات الجودة.
   4. **التحويل المستدام لنمط المحادثة (Session-Wide Fleet Mode Transformation):**
      - **قاعدة حاسمة:** بمجرد استدعاء وتفعيل الخطاف 22 (بالمحفزات المعتمدة أو ذكر خطاف 22)، يدخل المساعد فوراً ومستداماً في **نمط قيادة الأسطول (Fleet Command Mode)** لكامل ما تبقى من الجلسة.

--- a/HOOKS_GUIDE.xlsx
+++ b/HOOKS_GUIDE.xlsx
@@ -33,6 +33,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23. خطاف تحويل وأتمتة سكربتات" sheetId="24" state="visible" r:id="rId24"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24. خطاف أتمتة مسارات العمل و" sheetId="25" state="visible" r:id="rId25"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25. خطاف التصفير الاستراتيجي " sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26. خطاف إدارة وتحديث مكتبة ا" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="27. خطاف الاستشارة الاستراتيج" sheetId="28" state="visible" r:id="rId28"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -474,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1523,7 +1525,112 @@
      - صياغة ملخص تسليم محكم يتضمن: ما تم إنجازه، آخر Commit معتمد، والخيارات المتاحة أمام المطور للجلسة القادمة.
      - توليد برومبت استئناف دقيق (Ready to copy-paste) لنسخه ولصقه فور تنفيذ أمر التصفير:
        `Read CLAUDE.md and fleet_orders/CURRENT_STATE.md. State where we are and present the choices for the next order.`
-     - منح الضوء الأخضر الصريح للمطور: تأكيد إمكانية تنفيذ أمر `/clear` أو `/compact` بأمان تام وبدون أي هدر للسياق.
+     - منح الضوء الأخضر الصريح للمطور: تأكيد إمكانية تنفيذ أمر `/clear` أو `/compact` بأمان تام وبدون أي هدر للسياق.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>26. خطاف إدارة وتحديث مكتبة الأوامر الذكية</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>أضف لمكتبة الأوامر, وثق في مكتبة الأوامر, أضف برومبت للإكسيل, تحديث مكتبة الأوامر, حفظ في مكتبة الأوامر, add prompt to library, curate prompt</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Gemini 3.8 Flash (High)` 
+ البديل: `Claude Sonnet 5`</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>[prompt-engineer], [agent-optimizer], [code-architect]</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>تحويل الأفكار والحلول البرمجية لبرومبتات مهندسة جاهزة للاستخدام، وإدراجها آلياً في التبويب المناسب داخل ملف "مكتبة الأوامر.xlsx" مع الحفاظ على التنسيق والخطوط وإبلاغ المستخدم بموقع ورقم الصف المضاف.</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **الالتقاط والهندسة البرمجية للموجه (`[prompt-engineer]`):**
+     - استلام الفكرة، الميزة، أو الأمر البرمجي من سياق الجلسة الحالية.
+     - صياغته وهندسته كأمر معياري متكامل يتضمن:
+       - اسم الأمر بالعربية والإنجليزية مقروناً بإيموجي معبر (العمود B).
+       - الأمر البرمجي / الموجه الكامل (Command / Prompt) (العمود C).
+       - الوصف الدقيق، الهدف، وحالات الاستخدام المثلى (العمود D).
+  2. **التوجيه الذكي للتبويب المناسب (Smart Sheet Routing):**
+     - فحص كافة تبويبات ملف `G:\أرشيف_ونسخ_احتياطية\ملفات_مكررة_وعامة\AI\مكتبة الأوامر.xlsx`.
+     - توجيه الأمر تلقائياً للتبويب المتخصص:
+       - `CLI_Core.Claude`: أوامر الـ CLI، الأسطول، التصفير، والتحكم في المحركات.
+       - `Workflows_Pipelines.Claude`: مسارات العمل، CI/CD، البناء والتوزيع.
+       - `Gates_Hooks.Claude`: بوابات الجودة، الخطافات، والتدقيق المعماري.
+       - `Custom_Skills.Claude`: المهارات المخصصة، الوكلاء الفرعيون، وحزم الأدوات.
+       - `Config_Environments.Claude`: إعدادات البيئة، مسارات SDK، الذاكرة، و Gradle.
+       - `Construction_MCP_Suite`: أدوات الهندسة المدنية، جداول الكميات BOQ، والعقود.
+  3. **الإدراج البرمجي المحصن في الإكسيل (`prompt_library_curator.py` / `add-prompt`):**
+     - استدعاء أداة الأتمتة المدمجة `add-prompt`.
+     - حساب الرقم التسلسلي التالي (`No`) واكتشاف الصف النظيف القادم تلقائياً.
+     - تطبيق التنسيق الدقيق للخلايا (خط Segoe UI 10pt، خط Consolas للكود، محاذاة اليمين واليسار المناسبة، والحدود الرقيقة Thin Borders).
+     - معالجة قفل الملفات: في حال كان الإكسيل مفتوحاً لدى المستخدم، يتم الاعتماد تلقائياً على Excel COM Automation للكتابة الحية دون أخطاء PermissionError.
+  4. **إشعار المستخدم بالموقع الدقيق:**
+      - طباعة تقرير تأكيد فوري يتضمن: اسم الأمر، اسم التبويب (Sheet Name)، ورقم الصف الدقيق (Row Number) لسهولة الوصول إليه واستنساخه مستقبلاً.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>27. خطاف الاستشارة الاستراتيجية لإدارة نافذة السياق</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>مستشار السياق, إدارة السياق, مستشار التوكنز, ترشيد السياق, فحص نافذة السياق, context advisor, manage context, agy context advice, قرارات السياق</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Gemini 3.8 Flash (High)` 
+ البديل: `Claude Sonnet 5`</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>[prompt-engineer], [agent-optimizer], [code-architect]</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>تحليل لحظي ودقيق لاستهلاك السياق والتوكنز في Antigravity IDE/agcli، تصنيف الجلسة ضمن 4 مناطق أمان (خضراء، صفراء، برتقالية، حمراء)، وتوجيه المطور للقرار المعماري الأنسب (استمرار، ترشيد، ضغط، أو تصفير استراتيجي وتسليم).</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **الاستعلام الآلي عن استهلاك التوكنز والسياق (`context_advisor.py` / `ag-context -a`):**
+     - قراءة التليمتري الحية من قاعدة بيانات الجلسة الحالية (`input_tokens`, `output_tokens`, `thinking_tokens`, `limit`, `velocity`).
+     - المعايرة على **النطاق الذهبي للإنتاجية القصوى والدقة (30,000 إلى 300,000 توكن)** لحماية النموذج من تشتت الانتباه.
+  2. **التشخيص وتحديد منطقة الأمان (Context Health Zone Diagnostic):**
+     - 🟢 **المنطقة الخضراء (&lt; 180k توكن | أقل من 60% من النطاق الذهبي):** أمان تام وانتباه كامل (100% Attention Fidelity)؛ الاستمرار في التطوير دون أي تدخل مع ترشيد القراءة.
+     - 🟡 **المنطقة الصفراء (180k إلى 240k توكن | 60% - 80%):** تنبيه مبكر واقتراب من حافة النطاق الذهبي؛ حظر قراءة الملفات الكاملة والاعتماد الحصري على التوقيعات (Signatures) وأجزاء الأسطر عبر `lean-ctx`.
+     - 🟠 **المنطقة البرتقالية (240k إلى 300k توكن | 80% - 100%):** منطقة التخطيط للتسليم والضغط؛ تثبيت الكود الحالي بعمل `git commit`، وتوثيق الدروس في `MEMORY_STORE.md`، والاستعداد للضغط أو التصفير.
+     - 🔴 **المنطقة الحمراء (&gt; 300k توكن | تجاوز سقف النطاق الذهبي):** خروج صريح من نطاق الدقة القصوى؛ خطر فقدان الانتباه والهلوسة، والتفعيل الفوري الإلزامي للخطاف 25 (التصفير الاستراتيجي وتسليم الجلسة) وتوليد برومبت الاستئناف ثم تنفيذ `/clear`.
+  3. **توليد القرار الاستراتيجي والأوامر الجاهزة:**
+     - تقديم ملخص فني موجز باللغة العربية بتنسيق RTL.
+     - تقديم الأمر التكليفي أو التنفيذي الجاهز للنسخ بنقرة واحدة وفقاً للمنطقة المحددة.
 &lt;/div&gt;</t>
         </is>
       </c>
@@ -3333,7 +3440,232 @@
      - صياغة ملخص تسليم محكم يتضمن: ما تم إنجازه، آخر Commit معتمد، والخيارات المتاحة أمام المطور للجلسة القادمة.
      - توليد برومبت استئناف دقيق (Ready to copy-paste) لنسخه ولصقه فور تنفيذ أمر التصفير:
        `Read CLAUDE.md and fleet_orders/CURRENT_STATE.md. State where we are and present the choices for the next order.`
-     - منح الضوء الأخضر الصريح للمطور: تأكيد إمكانية تنفيذ أمر `/clear` أو `/compact` بأمان تام وبدون أي هدر للسياق.
+     - منح الضوء الأخضر الصريح للمطور: تأكيد إمكانية تنفيذ أمر `/clear` أو `/compact` بأمان تام وبدون أي هدر للسياق.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>اسم الخطاف</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>المحفزات (الخطاف للنسخ)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>النموذج الأساسي والبديل</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>الوكلاء المسؤولون</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>الهدف الأساسي</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>الوصف والتفاصيل</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>26. خطاف إدارة وتحديث مكتبة الأوامر الذكية</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>أضف لمكتبة الأوامر, وثق في مكتبة الأوامر, أضف برومبت للإكسيل, تحديث مكتبة الأوامر, حفظ في مكتبة الأوامر, add prompt to library, curate prompt</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Gemini 3.8 Flash (High)` 
+ البديل: `Claude Sonnet 5`</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[prompt-engineer], [agent-optimizer], [code-architect]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>تحويل الأفكار والحلول البرمجية لبرومبتات مهندسة جاهزة للاستخدام، وإدراجها آلياً في التبويب المناسب داخل ملف "مكتبة الأوامر.xlsx" مع الحفاظ على التنسيق والخطوط وإبلاغ المستخدم بموقع ورقم الصف المضاف.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **الالتقاط والهندسة البرمجية للموجه (`[prompt-engineer]`):**
+     - استلام الفكرة، الميزة، أو الأمر البرمجي من سياق الجلسة الحالية.
+     - صياغته وهندسته كأمر معياري متكامل يتضمن:
+       - اسم الأمر بالعربية والإنجليزية مقروناً بإيموجي معبر (العمود B).
+       - الأمر البرمجي / الموجه الكامل (Command / Prompt) (العمود C).
+       - الوصف الدقيق، الهدف، وحالات الاستخدام المثلى (العمود D).
+  2. **التوجيه الذكي للتبويب المناسب (Smart Sheet Routing):**
+     - فحص كافة تبويبات ملف `G:\أرشيف_ونسخ_احتياطية\ملفات_مكررة_وعامة\AI\مكتبة الأوامر.xlsx`.
+     - توجيه الأمر تلقائياً للتبويب المتخصص:
+       - `CLI_Core.Claude`: أوامر الـ CLI، الأسطول، التصفير، والتحكم في المحركات.
+       - `Workflows_Pipelines.Claude`: مسارات العمل، CI/CD، البناء والتوزيع.
+       - `Gates_Hooks.Claude`: بوابات الجودة، الخطافات، والتدقيق المعماري.
+       - `Custom_Skills.Claude`: المهارات المخصصة، الوكلاء الفرعيون، وحزم الأدوات.
+       - `Config_Environments.Claude`: إعدادات البيئة، مسارات SDK، الذاكرة، و Gradle.
+       - `Construction_MCP_Suite`: أدوات الهندسة المدنية، جداول الكميات BOQ، والعقود.
+  3. **الإدراج البرمجي المحصن في الإكسيل (`prompt_library_curator.py` / `add-prompt`):**
+     - استدعاء أداة الأتمتة المدمجة `add-prompt`.
+     - حساب الرقم التسلسلي التالي (`No`) واكتشاف الصف النظيف القادم تلقائياً.
+     - تطبيق التنسيق الدقيق للخلايا (خط Segoe UI 10pt، خط Consolas للكود، محاذاة اليمين واليسار المناسبة، والحدود الرقيقة Thin Borders).
+     - معالجة قفل الملفات: في حال كان الإكسيل مفتوحاً لدى المستخدم، يتم الاعتماد تلقائياً على Excel COM Automation للكتابة الحية دون أخطاء PermissionError.
+  4. **إشعار المستخدم بالموقع الدقيق:**
+      - طباعة تقرير تأكيد فوري يتضمن: اسم الأمر، اسم التبويب (Sheet Name)، ورقم الصف الدقيق (Row Number) لسهولة الوصول إليه واستنساخه مستقبلاً.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>اسم الخطاف</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>المحفزات (الخطاف للنسخ)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>النموذج الأساسي والبديل</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>الوكلاء المسؤولون</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>الهدف الأساسي</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>الوصف والتفاصيل</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>27. خطاف الاستشارة الاستراتيجية لإدارة نافذة السياق</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>مستشار السياق, إدارة السياق, مستشار التوكنز, ترشيد السياق, فحص نافذة السياق, context advisor, manage context, agy context advice, قرارات السياق</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Gemini 3.8 Flash (High)` 
+ البديل: `Claude Sonnet 5`</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[prompt-engineer], [agent-optimizer], [code-architect]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>تحليل لحظي ودقيق لاستهلاك السياق والتوكنز في Antigravity IDE/agcli، تصنيف الجلسة ضمن 4 مناطق أمان (خضراء، صفراء، برتقالية، حمراء)، وتوجيه المطور للقرار المعماري الأنسب (استمرار، ترشيد، ضغط، أو تصفير استراتيجي وتسليم).</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **الاستعلام الآلي عن استهلاك التوكنز والسياق (`context_advisor.py` / `ag-context -a`):**
+     - قراءة التليمتري الحية من قاعدة بيانات الجلسة الحالية (`input_tokens`, `output_tokens`, `thinking_tokens`, `limit`, `velocity`).
+     - المعايرة على **النطاق الذهبي للإنتاجية القصوى والدقة (30,000 إلى 300,000 توكن)** لحماية النموذج من تشتت الانتباه.
+  2. **التشخيص وتحديد منطقة الأمان (Context Health Zone Diagnostic):**
+     - 🟢 **المنطقة الخضراء (&lt; 180k توكن | أقل من 60% من النطاق الذهبي):** أمان تام وانتباه كامل (100% Attention Fidelity)؛ الاستمرار في التطوير دون أي تدخل مع ترشيد القراءة.
+     - 🟡 **المنطقة الصفراء (180k إلى 240k توكن | 60% - 80%):** تنبيه مبكر واقتراب من حافة النطاق الذهبي؛ حظر قراءة الملفات الكاملة والاعتماد الحصري على التوقيعات (Signatures) وأجزاء الأسطر عبر `lean-ctx`.
+     - 🟠 **المنطقة البرتقالية (240k إلى 300k توكن | 80% - 100%):** منطقة التخطيط للتسليم والضغط؛ تثبيت الكود الحالي بعمل `git commit`، وتوثيق الدروس في `MEMORY_STORE.md`، والاستعداد للضغط أو التصفير.
+     - 🔴 **المنطقة الحمراء (&gt; 300k توكن | تجاوز سقف النطاق الذهبي):** خروج صريح من نطاق الدقة القصوى؛ خطر فقدان الانتباه والهلوسة، والتفعيل الفوري الإلزامي للخطاف 25 (التصفير الاستراتيجي وتسليم الجلسة) وتوليد برومبت الاستئناف ثم تنفيذ `/clear`.
+  3. **توليد القرار الاستراتيجي والأوامر الجاهزة:**
+     - تقديم ملخص فني موجز باللغة العربية بتنسيق RTL.
+     - تقديم الأمر التكليفي أو التنفيذي الجاهز للنسخ بنقرة واحدة وفقاً للمنطقة المحددة.
 &lt;/div&gt;</t>
         </is>
       </c>

--- a/HOOKS_GUIDE.xlsx
+++ b/HOOKS_GUIDE.xlsx
@@ -35,6 +35,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25. خطاف التصفير الاستراتيجي " sheetId="26" state="visible" r:id="rId26"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26. خطاف إدارة وتحديث مكتبة ا" sheetId="27" state="visible" r:id="rId27"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="27. خطاف الاستشارة الاستراتيج" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="28. خطاف ترحيل وتطهير أدوات ا" sheetId="29" state="visible" r:id="rId29"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -476,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1626,11 +1627,55 @@
   2. **التشخيص وتحديد منطقة الأمان (Context Health Zone Diagnostic):**
      - 🟢 **المنطقة الخضراء (&lt; 180k توكن | أقل من 60% من النطاق الذهبي):** أمان تام وانتباه كامل (100% Attention Fidelity)؛ الاستمرار في التطوير دون أي تدخل مع ترشيد القراءة.
      - 🟡 **المنطقة الصفراء (180k إلى 240k توكن | 60% - 80%):** تنبيه مبكر واقتراب من حافة النطاق الذهبي؛ حظر قراءة الملفات الكاملة والاعتماد الحصري على التوقيعات (Signatures) وأجزاء الأسطر عبر `lean-ctx`.
-     - 🟠 **المنطقة البرتقالية (240k إلى 300k توكن | 80% - 100%):** منطقة التخطيط للتسليم والضغط؛ تثبيت الكود الحالي بعمل `git commit`، وتوثيق الدروس في `MEMORY_STORE.md`، والاستعداد للضغط أو التصفير.
+     - 🟠 **المنطقة البرتقالية (240k إلى 300k توكن | 80% - 100%):** منطقة التخطيط للتسليم والضغط؛ تثبيت الكود الحالي بعمل `git commit`، وتوثيق الدروس في `MEMORY_STORE.md`, والاستعداد للضغط أو التصفير.
      - 🔴 **المنطقة الحمراء (&gt; 300k توكن | تجاوز سقف النطاق الذهبي):** خروج صريح من نطاق الدقة القصوى؛ خطر فقدان الانتباه والهلوسة، والتفعيل الفوري الإلزامي للخطاف 25 (التصفير الاستراتيجي وتسليم الجلسة) وتوليد برومبت الاستئناف ثم تنفيذ `/clear`.
   3. **توليد القرار الاستراتيجي والأوامر الجاهزة:**
      - تقديم ملخص فني موجز باللغة العربية بتنسيق RTL.
-     - تقديم الأمر التكليفي أو التنفيذي الجاهز للنسخ بنقرة واحدة وفقاً للمنطقة المحددة.
+     - تقديم الأمر التكليفي أو التنفيذي الجاهز للنسخ بنقرة واحدة وفقاً للمنطقة المحددة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>28. خطاف ترحيل وتطهير أدوات المحرر والذكاء الاصطناعي</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>تطهير المحرر, نقل أدوات المحرر, ترحيل أدوات المحرر, تطهير المشروع, evacuate editor tools, clean workspace tooling, evacuate-tools</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Gemini 3.8 Flash (High)` 
+ البديل: `Claude Sonnet 5`</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>[devops-deployer], [agent-optimizer], [code-architect]</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>فحص ومزامنة أدوات المحرر في الإعدادات العالمية (~/.gemini/config)، ونقل كافة الأدلة والمستندات والسكربتات إلى المستودع المركزي (Claude+Antigravity) بعد التحقق التشفيري الإلزامي (SHA-256) قبل الحذف، وتنظيف مخلفات الذاكرة وحطام JVM لضمان نقاء بيئة المشاريع البرمجية.</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **المزامنة والتحديث للسيستم العالمي (`C:\Users\Kt\.gemini\config\tools\`):**
+     - جرد أدوات المحرر في مجلد `tools/` بالمشروع ومقارنتها بالنسخ العالمية وتحديثها لضمان عدم ضياع أي ميزة جديدة.
+  2. **الترحيل والأرشفة المركزية (`F:\AI PROJECTS\Claude+Antigravity\`):**
+     - نقل أدلة المحرر (`*.docx`, `*.pdf`, `*.md`) إلى مجلد `docs/`، والمخططات إلى `assets/`، والسكربتات إلى `tools/`.
+  3. **التدقيق التشفيري الإلزامي قبل الحذف (SHA-256 Verification):**
+     - يُحظر حذف أي ملف محلي إلا بعد حساب بصمة SHA-256 للمصدر والوجهة والتأكد من التطابق التام 100%. وفي حال وجود نسخة أحدث في المركز، تُحفظ كنسخة أرشيفية.
+  4. **التطهير الآمن للمشروع المحلي (Clean Workspace Guarantee):**
+     - حذف الأدوات المنقولة، وإزالة مجلد `tools/` بعد فراغه، وتنظيف مخلفات JVM (`hs_err_*.log`, `replay_*.log`) وأقفال Word المؤقتة، واستعادة الشجرة النظيفة الخالية من أي Untracked files.
 &lt;/div&gt;</t>
         </is>
       </c>
@@ -3661,11 +3706,115 @@
   2. **التشخيص وتحديد منطقة الأمان (Context Health Zone Diagnostic):**
      - 🟢 **المنطقة الخضراء (&lt; 180k توكن | أقل من 60% من النطاق الذهبي):** أمان تام وانتباه كامل (100% Attention Fidelity)؛ الاستمرار في التطوير دون أي تدخل مع ترشيد القراءة.
      - 🟡 **المنطقة الصفراء (180k إلى 240k توكن | 60% - 80%):** تنبيه مبكر واقتراب من حافة النطاق الذهبي؛ حظر قراءة الملفات الكاملة والاعتماد الحصري على التوقيعات (Signatures) وأجزاء الأسطر عبر `lean-ctx`.
-     - 🟠 **المنطقة البرتقالية (240k إلى 300k توكن | 80% - 100%):** منطقة التخطيط للتسليم والضغط؛ تثبيت الكود الحالي بعمل `git commit`، وتوثيق الدروس في `MEMORY_STORE.md`، والاستعداد للضغط أو التصفير.
+     - 🟠 **المنطقة البرتقالية (240k إلى 300k توكن | 80% - 100%):** منطقة التخطيط للتسليم والضغط؛ تثبيت الكود الحالي بعمل `git commit`، وتوثيق الدروس في `MEMORY_STORE.md`, والاستعداد للضغط أو التصفير.
      - 🔴 **المنطقة الحمراء (&gt; 300k توكن | تجاوز سقف النطاق الذهبي):** خروج صريح من نطاق الدقة القصوى؛ خطر فقدان الانتباه والهلوسة، والتفعيل الفوري الإلزامي للخطاف 25 (التصفير الاستراتيجي وتسليم الجلسة) وتوليد برومبت الاستئناف ثم تنفيذ `/clear`.
   3. **توليد القرار الاستراتيجي والأوامر الجاهزة:**
      - تقديم ملخص فني موجز باللغة العربية بتنسيق RTL.
-     - تقديم الأمر التكليفي أو التنفيذي الجاهز للنسخ بنقرة واحدة وفقاً للمنطقة المحددة.
+     - تقديم الأمر التكليفي أو التنفيذي الجاهز للنسخ بنقرة واحدة وفقاً للمنطقة المحددة.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>اسم الخطاف</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>المحفزات (الخطاف للنسخ)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>النموذج الأساسي والبديل</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>الوكلاء المسؤولون</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>الهدف الأساسي</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>الوصف والتفاصيل</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>28. خطاف ترحيل وتطهير أدوات المحرر والذكاء الاصطناعي</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>تطهير المحرر, نقل أدوات المحرر, ترحيل أدوات المحرر, تطهير المشروع, evacuate editor tools, clean workspace tooling, evacuate-tools</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Gemini 3.8 Flash (High)` 
+ البديل: `Claude Sonnet 5`</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[devops-deployer], [agent-optimizer], [code-architect]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>فحص ومزامنة أدوات المحرر في الإعدادات العالمية (~/.gemini/config)، ونقل كافة الأدلة والمستندات والسكربتات إلى المستودع المركزي (Claude+Antigravity) بعد التحقق التشفيري الإلزامي (SHA-256) قبل الحذف، وتنظيف مخلفات الذاكرة وحطام JVM لضمان نقاء بيئة المشاريع البرمجية.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **المزامنة والتحديث للسيستم العالمي (`C:\Users\Kt\.gemini\config\tools\`):**
+     - جرد أدوات المحرر في مجلد `tools/` بالمشروع ومقارنتها بالنسخ العالمية وتحديثها لضمان عدم ضياع أي ميزة جديدة.
+  2. **الترحيل والأرشفة المركزية (`F:\AI PROJECTS\Claude+Antigravity\`):**
+     - نقل أدلة المحرر (`*.docx`, `*.pdf`, `*.md`) إلى مجلد `docs/`، والمخططات إلى `assets/`، والسكربتات إلى `tools/`.
+  3. **التدقيق التشفيري الإلزامي قبل الحذف (SHA-256 Verification):**
+     - يُحظر حذف أي ملف محلي إلا بعد حساب بصمة SHA-256 للمصدر والوجهة والتأكد من التطابق التام 100%. وفي حال وجود نسخة أحدث في المركز، تُحفظ كنسخة أرشيفية.
+  4. **التطهير الآمن للمشروع المحلي (Clean Workspace Guarantee):**
+     - حذف الأدوات المنقولة، وإزالة مجلد `tools/` بعد فراغه، وتنظيف مخلفات JVM (`hs_err_*.log`, `replay_*.log`) وأقفال Word المؤقتة، واستعادة الشجرة النظيفة الخالية من أي Untracked files.
 &lt;/div&gt;</t>
         </is>
       </c>

--- a/HOOKS_GUIDE.xlsx
+++ b/HOOKS_GUIDE.xlsx
@@ -7,16 +7,35 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. مشروع جديد" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. جدول زمني" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. منهجية" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. جدول كميات" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. إدارة مخاطر" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. تنسيق وإخراج" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7. مطابقة" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8. ضبط مرجع" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9. تنظيم الأرشيف" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10. تنظيم ملفات الجهاز" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الملخص العام" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. خطاف البدء والافتتاح" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. خطاف هندسة السياق" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. خطاف التخصيص والتصدير الذ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. خطاف الإشراف العام وتصحيح" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. خطاف خط الإنتاج البرمجي" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. خطاف التكامل الفني" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7. خطاف تدقيق الصيانة" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8. خطاف الفحص الأمني" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9. خطاف مراجعة وتحديث المكتب" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10. خطاف الفحص والاختبار التل" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11. خطاف معالجة الأخطاء والأع" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12. خطاف إدارة النسخ والمستود" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13. خطاف تحديث الإنجازات" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14. خطاف الذاكرة المستدامة" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15. خطاف النجاح والتحليل البع" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16. خطاف تنظيم وترتيب الأجهزة" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17. خطاف ترتيب الملفات لمسار " sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18. خطاف إدارة تليجرام" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19. خطاف التدقيق البرمجي الشا" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20. خطاف استكشاف وتكامل الموا" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21. خطاف المزامنة السحابية وا" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22. خطاف قيادة وإدارة الأسطول" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23. خطاف تحويل وأتمتة سكربتات" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24. خطاف أتمتة مسارات العمل و" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25. خطاف التصفير الاستراتيجي " sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26. خطاف إدارة وتحديث مكتبة ا" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="27. خطاف الاستشارة الاستراتيج" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="28. خطاف ترحيل وتطهير أدوات ا" sheetId="29" state="visible" r:id="rId29"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -35,14 +54,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Segoe UI"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="14"/>
+      <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <sz val="16"/>
+      <name val="Segoe UI"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
@@ -54,8 +73,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F497D"/>
-        <bgColor rgb="001F497D"/>
+        <fgColor rgb="001F4E79"/>
+        <bgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
   </fills>
@@ -69,28 +88,25 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D3D3D3"/>
+        <color rgb="00D9D9D9"/>
       </left>
       <right style="thin">
-        <color rgb="00D3D3D3"/>
+        <color rgb="00D9D9D9"/>
       </right>
       <top style="thin">
-        <color rgb="00D3D3D3"/>
+        <color rgb="00D9D9D9"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D3D3D3"/>
+        <color rgb="00D9D9D9"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -461,34 +477,52 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="80" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>م</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>اسم الخطاف</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Prompt</t>
+          <t>المحفزات (الخطاف للنسخ)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Notes or description</t>
+          <t>النموذج الأساسي والبديل</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>الوكلاء المسؤولون</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>الهدف الأساسي</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>الوصف والتفاصيل</t>
         </is>
       </c>
     </row>
@@ -496,26 +530,1167 @@
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>1. مشروع جديد</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>`"مشروع جديد"`, `"كراسة شروط"`</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>الوكلاء المسؤولون: `planning-engineer`
-الوصف العام: تحليل المشروع وتصنيفه وتوزيع المهام
-الإجراءات التفصيلية:
-1. يسأل المستخدم عن: اسم المشروع، الجهة المالكة، مدة التنفيذ، نوع المشروع
-  2. يبحث عن كراسة الشروط وجدول الكميات إذا توفرت
-  3. يصنّف المشروع (إنشاء / صيانة / توريدات)
-  4. ينشئ مجلداً جديداً للمشروع باسمه
-  5. يوجّه العمل للوكلاء المتخصصين بالتوالي</t>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>1. خطاف البدء والافتتاح</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>بسم الله, بسم الله الرحمن الرحيم</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Gemini 3.7 Flash (High)` 
+ البديل: `Gemini 3.6 Flash (Medium)`</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[prompt-engineer], [agent-optimizer]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>تهيئة الجلسة، التحقق من القواعد الفنية واللغوية، وترشيد الاستهلاك.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **تفعيل القواعد والتعليمات:** مراجعة وتطبيق كافة التوجيهات البرمجية واللغوية في المشروع (مثل الكتابة باللغة العربية، وتنسيق RTL).
+  2. **تحسين وترشيد الاستهلاك:** تحليل سياق المحادثة وتوجيهها لتكون بأعلى كفاءة مع توفير استهلاك التوكنز.
+  3. **إعلان الجاهزية:** إشعار المستخدم بتفعيل القواعد واستعداد الطاقم البرمجي للعمل.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>2. خطاف هندسة السياق</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>سياق المشروع, هندسة السياق</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Claude Opus 4.6 (Thinking)`</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>[prompt-engineer], [agent-optimizer]</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>إنشاء وتحديث ملف `PROJECT_CONTEXT.md` لضمان التوجيه وتفادي الانحراف التقني.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **مراجعة القواعد واستيراد الذاكرة العالمية:** يقوم الوكيل `[prompt-engineer]` بمراجعة الدستور المحلي والعالمي (`AGENTS.md`) بدقة، واستيراد البيانات من ملفات **الذاكرة العالمية (Global Memory)** و **الأنماط العالمية (Global Patterns)** لضمان تطبيق الدروس العابرة للمشاريع.
+  2. **قراءة هيكل المشروع:** تحليل البنية والقرارات المعمارية الحالية للمشروع.
+  3. **توليد أو تحديث الملف:** كتابة أو تعديل ملف `PROJECT_CONTEXT.md` ليعكس التحديثات المعمارية والقرارات التقنية.
+  4. **التأكيد والمزامنة:** إعلام طاقم الوكلاء بالتحديثات المعتمدة لضمان التوافق.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>3. خطاف التخصيص والتصدير الذكي لطاقم المشروع</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>اعتمد سياق المشروع, تخصيص وكلاء المشروع, تصدير بيئة المشروع, تخصيص الوكلاء</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>[code-architect], [agent-optimizer], [prompt-engineer]</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>تحليل سياق المشروع وتصدير حزم الوكلاء محلياً مع التنظيف التلقائي (Pruning) وتوليد سكربت المزامنة.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **تحليل سياق المشروع المعتمد (`project_agent_tailor.py`):** فحص ملف `PROJECT_CONTEXT.md` واكتشاف حزم التقنيات المستخدمة (مثل: `android_compose`, `web`, `python_ai`, `construction_survey`).
+  2. **تصدير حزم الوكلاء والمهارات المطلوبة:** نسخ مهارات وبطاقات الوكلاء المتخصصين وحزمة النواة حصرياً إلى مجلد المشروع المحلي `.agents/`.
+  3. **التنظيف التلقائي الصارم للمهارات الفائضة (Pruning Engine):** مسح وحذف أي مهارات أو بطاقات وكلاء غير مستخدمة في المشروع المستهدف، لحماية نافذة السياق (Context Budget) من الهدر بنسبة 100%.
+  4. **توليد قالب المزامنة المحلي (`sync_local_agents.py`):** إنشاء سكربت خفيف داخل المشروع لتمكين المطور من تحديث طاقم المشروع بنقرة زر واحدة مستقبلاً دون المساس بخصوصية المشروع.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>4. خطاف الإشراف العام وتصحيح المسار</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>تصحيح مسار, تعديل البرومبت, خطأ بالخطاف, تصحيح خطاف</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>[prompt-engineer], [agent-optimizer]</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>تصحيح الخطافات الخاطئة والبرومبتات غير الاحترافية وتوجيهها للمسار الصحيح تلقائياً.</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **الرصد التلقائي والإيقاف:** يقوم الوكيل الرئيسي بمراقبة المحادثة. عند استخدام المستخدم لمحفز "تصحيح مسار"، أو عند رصد دخول وكيل في دائرة مفرغة، يتم اعتراض العمل وإيقافه فوراً.
+  2. **التشريح الاستباقي الصارم (Prompt Autopsy &amp; Root-Cause Analysis):** يُمنع على `prompt-engineer` تقديم برومبت جديد مباشرة. يجب أولاً طباعة قسم `[ROOT-CAUSE ANALYSIS]` يشرح بوضوح سبب الانحراف السابق (هلوسة وكيل، غياب سياق، أو معمارية خاطئة).
+  3. **حماية السياق (Context Preservation):** تحديد المتطلبات أو الملفات التي كانت تنقص الوكيل السابق للعمل بشكل صحيح تحت قسم `[MISSING ARTIFACTS / INFO]`.
+  4. **إعادة الصياغة والتوجيه القاطع (Explicit Rerouting):** توليد التوجيه الهندسي الجديد تحت قسم `[RE-ENGINEERED PROMPT]` مقترناً بشكل صريح بالوكيل الفرعي المستهدف `[TARGET HOOK]` الذي سيستلم المهمة ليكملها بنظافة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>5. خطاف خط الإنتاج البرمجي</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>ابدأ ميزة, تطوير ميزة, اصنع ميزة, إصلاح ميزة</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Claude Opus 4.6 (Thinking)`</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>[code-architect], [ui-ux-pro-max], [clean-code-guard], [test-guard]</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>تنفيذ دورة التطوير الكاملة (المعمارية، الذكاء التصميمي، البرمجة، حراسة الكود النظيف، والفحص والاختبار).</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **التصميم الهيكلي والذكاء التصميمي (`code-architect` + `ui-ux-pro-max`):** تحديد المعمارية المناسبة، واستدعاء محرك الاستدلال التصميمي لتحديد نمط الواجهات (Style)، باليت الألوان الدلالية، والخطوط وقواعد سهولة الوصول بدقة قبل كتابة أي واجهة.
+  2. **التدقيق المعماري الصارم (Devil's Advocate Audit):** مراجعة الخطة وكشف الثغرات وحالات الحافة لمنع الآثار الجانبية.
+  3. **الكتابة البرمجية والتنفيذ:** كتابة الكود وبناء الواجهات وقواعد البيانات محلياً.
+  4. **المراجعة وضمان الجودة (`clean-code-guard` + `test-guard`):** فحص الكود للأمان، الأداء، والتوافق مع المعايير.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>6. خطاف التكامل الفني</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>ربط API, تكامل خارجي</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Gemini 3.7 Flash (High)` 
+ البديل: `Claude Sonnet 4.6 (Thinking)`</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>[devops-deployer], [backend-architect]</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>ربط وتكامل الخدمات الخارجية بعد مراجعة وثائقها الرسمية وتأمين المتغيرات.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **قراءة الوثائق:** يقرأ الوكيل `[devops-deployer]` وثائق الـ API الخارجية الرسمية المدخلة قبل البدء بالدمج.
+  2. **تحصين الانقطاع (API FAULT TOLERANCE CHECK):** بناء Interceptor لمعالجة انقطاع الشبكة وإعادة المحاولة وتأمين المفاتيح في متغيرات البيئة.
+  3. **توليد الـ Wrapper:** عزل منطق التكامل في كلاسات مغلفة منفصلة لتجنب تشتيت الكود الأساسي للمشروع.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>7. خطاف تدقيق الصيانة</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>تدقيق صيانة, مراجعة DRY, كود نظيف</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>[code-reviewer-quality], [clean-code-guard], [performance-optimizer]</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>مراجعة الكود البرمجي بانتظام لمنع التكرار وتراكم الديون التقنية وتطبيق معايير الكود النظيف.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **فحص الكود النظيف والمكرر:** استدعاء الوكيل `[code-reviewer-quality]` و `[clean-code-guard]` لمسح الملفات والتحقق من عدم وجود دوال مكررة (تطبيق DRY/KISS/YAGNI).
+  2. **فحص Recomposition والأداء:** قياس كفاءة الرسم وإعاقات الأداء في Compose بواسطة `[performance-optimizer]`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>8. خطاف الفحص الأمني</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>فحص أمني, مراجعة أمان</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Claude Opus 4.6 (Thinking)`</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>[security-auditor], [code-reviewer-quality]</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>مراجعة ثغرات الأمان والتحقق من صحة المدخلات وتشفير البيانات وتأمين الوصول.</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **مصفوفة الثغرات الصارمة (VULNERABILITY MATRIX):** مسح إجباري لـ AndroidManifest والمكونات المكشوفة وتسريب البيانات.
+  2. **التحقق من صحة المدخلات وتشفير البيانات:** فحص تشفير البيانات الحساسة والجلسات وتأمين الوصول محلياً وسحابياً.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>9. خطاف مراجعة وتحديث المكتبات والنماذج</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>تحديث الاعتماديات, تحديث المكتبات, تحديث النماذج, معايرة النماذج, update models</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Gemini 3.7 Flash (High)` 
+ البديل: `Gemini 3.6 Flash (Medium)`</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>[github-talent-scout], [code-architect], [agent-optimizer]</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>فحص ملفات Gradle وتحديث المكتبات، والتحقق التلقائي عبر الإنترنت (antigravity.google) لتحديث مصفوفة النماذج ودليل hooks_user_guide.md دون لقطات شاشة.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **فحص إصدارات المكتبات:** مسح ملفات `build.gradle.kts` ومقارنة إصدارات المكتبات الحالية بأحدث الإصدارات المستقرة.
+  2. **الاستكشاف والمعايرة التلقائية للنماذج عبر الإنترنت (Online Model Discovery):** الاستعلام الفوري عبر المصادر الرسمية (antigravity.google, docs.anthropic.com) ومعايرة مصفوفة النماذج.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>10. خطاف الفحص والاختبار التلقائي</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>قم بالاختبار, جاهز للتجربة</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>[android-testing], [test-guard], [code-reviewer-quality]</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>تشغيل اختبارات الوحدة وفحص جودة الكود واختبار السلوك الفعلي بدون Mock مفرط.</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **حراسة الاختبارات (`test-guard`):** التحقق من أن الاختبارات تفحص سلوك النظام الفعلي ومنع Mocks الوهمية.
+  2. **قاعدة التغطية الإجبارية:** اختبار مسار النجاح، الفشل، والحالات الطرفية (Network Off, Lifecycle).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>11. خطاف معالجة الأخطاء والأعطال</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>حدث خطأ, التطبيق توقف, Crash</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>[debugger]</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>تحليل سجلات الأخطاء والـ Stack Trace وعزل الكود المسبب للمشكلة وإصلاحه.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **تحليل الـ Stack Trace:** قراءة السجلات بدقة وتحديد السطر المسبب للخلل وعزله وإصلاحه بأقل تعديل كافٍ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>12. خطاف إدارة النسخ والمستودعات</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>نظم جيت, ارفع لجيتهاب, تحديث المستودع, git commit</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Gemini 3.7 Flash (High)` 
+ البديل: `Gemini 3.6 Flash (Medium)`</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>[git-github-manager]</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>تهيئة المشاريع الجديدة على Git، إدارة التفرعات، وحل تعارضات الدمج ورفعها لـ GitHub بشكل نظيف.</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **التحقق من حالة المستودع:** فحص حالة Git واستثناء الملفات غير الضرورية في `.gitignore`.
+  2. **التنفيذ والرفع:** كتابة رسائل Commit احترافية وحل التعارضات ودفع التغييرات إلى GitHub.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>13. خطاف تحديث الإنجازات</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>حدث الإنجازات, تحديث README, وثق الإنجازات</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Gemini 3.7 Flash (High)` 
+ البديل: `Claude Sonnet 4.6 (Thinking)`</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>[git-github-manager], [docs-guard]</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>صياغة التعديلات كإنجازات ومطابقتها برمجياً وتحديث README.md و hooks_user_guide.md ثم الرفع لـ GitHub.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **قراءة السجل ومطابقة التوثيق (`docs-guard`):** مراجعة التغييرات الأخيرة وصياغة الإنجازات وتحديث `README.md`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>14. خطاف الذاكرة المستدامة</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>حفظ ذاكرة, تحديث السياق, سجّل هذا</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `GPT-OSS 120B (Medium)`</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>[persistent-memory-engine]</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>التقاط الدروس والقرارات وتخزينها في MEMORY_STORE.md وتصديرها للوكلاء.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **التقاط وتخزين الدروس:** حفظ القرارات المعمارية وتفضيلات المستخدم في `MEMORY_STORE.md`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>15. خطاف النجاح والتحليل البعدي</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>تم بنجاح, انتهى المشروع بنجاح</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>[agent-optimizer]</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>إجراء تحليل بعدي للمشروع وتحديث سجل التعلم وسد الثغرات البرمجية.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **التحليل البعدي (Post-Mortem Analysis):** دراسة سجل المحادثة واستخراج العقبات وتحديث سجل التعلم وسد الفجوات.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>16. خطاف تنظيم وترتيب الأجهزة الشامل</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>رتب جهازى, فرز الملفات, ترتيب ملفات</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Gemini 3.7 Flash (High)` 
+ البديل: `Gemini 3.6 Flash (Medium)`</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>[windows-c-drive-optimizer], [windows-file-organizer]</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>ترتيب ملفات جذور الأقراص بالكامل مع تنظيف وتحسين مساحة قرص الـ C بآن واحد.</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **تحليل وتحرير مساحة القرص C: السريع والمتقدم:**
+     - تفريغ كاش حزم بايثون الحديثة (`uv cache clean`) وكاش `npm` وملفات `CrashDumps`.
+     - تفريغ المجلدات المؤقتة (`AppData\Local\Temp` و `C:\Windows\Temp`).
+     - استدعاء سكربت التنظيف الشامل: `&amp; "C:\Users\Kt\.gemini\config\tools\Deep_Clean_C_Drive.ps1"`.
+  2. **معمارية ترحيل الأقراص الافتراضية وكاش التطوير (DevCache Junctions):**
+     - فحص وتأمين ترحيل أقراص Docker WSL (`docker_data.vhdx`) إلى `D:\DevCache\Docker_wsl\disk`.
+     - ترحيل حزم Claude Desktop VM (`vm_bundles` بحجم 10.36 GB) إلى `D:\DevCache\Claude_vm_bundles` عبر `&amp; "C:\Users\Kt\.gemini\config\tools\Relocate_Claude_VM_Bundles.ps1"`.
+     - التحقق من ربط نماذج Ollama بالقرص الثانوي (`D:\AI_Models\Ollama\models`).
+  3. **فرز وتصنيف جذور الأقراص (F:, G:, D:, E:):**
+     - جرد الملفات السائبة في جذور الأقراص وتصنيفها فوراً إلى مجلداتها الموضوعية (رسومات هندسية، مشاريع مونتاج، تسجيلات، مستندات).
+     - التخلص من ملفات سجلات الانهيار القديمة (مثل `DUMP*.tmp`).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>17. خطاف ترتيب الملفات لمسار محدد</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>رتب المسار, نظم المجلد, ترتيب مسار</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Gemini 3.6 Flash (Medium)` 
+ البديل: `Gemini 3.5 Flash (Medium)`</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>[windows-file-organizer]</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>تنظيم وفرز الملفات داخل مجلد أو مسار مخصص يحدده المستخدم بذكاء ودقة.</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **تنظيم وفرز الملفات:** تصنيف الملفات داخل مجلد محدد بذكاء ودقة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>18. خطاف إدارة تليجرام</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>شغل البوت, تفعيل تليجرام, Telegram Bot</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Gemini 3.5 Flash (Medium)` 
+ البديل: `Gemini 3.1 Pro (Low)`</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>[devops-deployer], [persistent-memory-engine]</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>تشغيل بوت تليجرام في الخلفية بنمط الاستماع للطلبات عن بعد دون تعارض.</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **التشغيل بنمط الاستماع الفردي (One-Shot Polling):** تشغيل البوت للاستماع لطلب واحد دون تعارض مع بيئة التطوير.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>19. خطاف التدقيق البرمجي الشامل وحراسة الجودة</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>تدقيق الجودة, فحص الكود النظيف, حراسة الجودة, clean code audit</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Claude Opus 4.6 (Thinking)`</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>[code-reviewer-quality], [clean-code-guard], [test-guard], [docs-guard]</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>تفعيل بوابات الحماية الثلاث لفحص الكود النظيف، سلامة الاختبارات، ومطابقة التوثيق.</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **تفعيل بوابات الحماية الثلاث:** فحص الكود النظيف (`clean-code-guard`)، سلامة الاختبارات (`test-guard`)، ومطابقة التوثيق (`docs-guard`).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>20. خطاف استكشاف وتكامل الموارد العالمية</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>استكشف المورد, حلل المستودع, تكامل المورد, scout resource, integrate repo</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>[resource-scout-integrator], [ui-ux-pro-max], [github-talent-scout], [skill-forge-builder], [agent-optimizer], [frontend-design-builder], [git-github-manager], [powershell-runtime-pro]</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>تحليل المستودعات الخارجية واستيراد المهارات وتعميمها وتحديث الخطافات والإكسيل وتطبيق مكتبة الأوامر ودليل hooks_user_guide.md ومزامنة المنظومة.</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **استيراد وتعميم المهارات العالمية:** تحليل المستودعات الخارجية وبناء مهارات `SKILL.md` ونشرها عالمياً وتحديث المنظومة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>21. خطاف المزامنة السحابية والمساهمة المجتمعية</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>مزامنة المنظومة, sync ecosystem, ارسل pull request, مساهمة في المستودع, create PR, contribute repo</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Gemini 3.7 Flash (High)` 
+ البديل: `Claude Sonnet 4.6 (Thinking)`</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>[git-github-manager], [persistent-memory-engine], [agent-optimizer], [docs-guard]</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>للمطور المالك: مطابقة ومزامنة كافة الإضافات والمهارات وتطبيق الأوامر مع GitHub. للمساهمين والمجتمع: تجهيز فرع الميزة وإنشاء وتوجيه Pull Request للمستودع المركزي للمشاركة.</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **المسار الأول (للمطور المالك / Maintainer):**
+     - تشغيل `sync_global_ecosystem.py` لمطابقة كامل منظومة الوكلاء والمهارات والمراجع مع المسار العالمي ورفعها إلى مستودع GitHub الرئيسي بنقرة واحدة.
+  2. **المسار الثاني (للمساهمين والمجتمع / Community &amp; Contributors):**
+     - عند إضافة مهارة أو ميزة جديدة في نسخة Fork، يقوم الخطاف بفحص توافق الكود والتوثيق مع معايير Autovem.
+     - إنشاء فرع مساهمة (Feature Branch) وصياغة رسالة الالتزام وفق مواصفات Conventional Commits.
+     - فتح وتوجيه رابط **Pull Request** تلقائياً إلى المستودع المركزي [Claude-Antigravity-Workspace على GitHub](https://github.com/ibrahimalkateb965-tech/Claude-Antigravity-Workspace) لمراجعتها ودمجها لصالح المجتمع.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>22. خطاف قيادة وإدارة الأسطول التشاركي</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>أسطول الـ CLIs, تشغيل الأسطول, تنسيق الأسطول, fleet orchestrator, multi cli fleet, إدارة الأسطول</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Opus 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>[fleet-orchestrator], [code-architect], [agent-optimizer], [persistent-memory-engine]</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>تفعيل وضبط أسطول الوكلاء المتعدد، إدارة وتنسيق التكليف بين CLIs، حوكمة بوابات مراجعة الأكواد، وترشيد التوكنز.</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **التهيئة والتوليد التلقائي (Auto-Provisioning):**
+     - فحص وجود مجلد `fleet_templates/` وملف `fleet_config.json` في المشروع وتوليدهما تلقائياً عند عدم وجودهما.
+  2. **توزيع المسؤوليات والحدود الحصرية وضبط النماذج:**
+     - تحديد ملكية الملفات والمهام في `fleet_config.json` لمنع التصادم:
+       - **Claude Code CLI** (النموذج: `Claude 5 Opus / Opus Max`): التخطيط والمراجعة المعمارية، **التنفيذ الحصري لكافة الاختبارات التلقائية**، واعتماد الأكواد وبوابات الجودة (Quality Gates).
+       - **OpenCode CLI** (النموذج: `Ox Alpha Unlimited`): التنفيذ الطرفي، إدارة قواعد البيانات Drift/ORM، وعملاء الاتصال والبيانات (كتابة وبناء فقط دون تشغيل أي اختبارات).
+       - **Antigravity CLI (`agcli`)** (النموذج: `Gemini 3.8 Flash High` / `hermes3:8b` Ollama): المنفذ الطرفي الذاتي لبناء الواجهات (UI)، تكييف المنصات، عقود الـ Domain، وهندسة الملفات (كتابة وبناء دون تشغيل اختبارات عبر سطر الأوامر دون نسخ ولصق).
+       - **Antigravity IDE** (النموذج: `Gemini 3.8 Flash High`): بيئة العمل التفاعلية وحاضنة المطور المركزية (Interactive Cockpit) لإدارة الجلسة والمحادثة واستعراض الفروقات (Diffs)؛ ولا تُوجّه أوامر تفويض الـ CLI البرمجية إليها لمنع تعليق الأتمتة.
+  3. **التشغيل المباشر لأدوات الـ CLI (Headless Direct Invocation):**
+     - تشغيل واستدعاء أدوات الـ CLI المثبتة مباشرة عبر سطر الأوامر غير التفاعلي:
+       - استدعاء `Claude Code CLI` للمراجعة المعمارية وتشغيل الاختبارات وتدقيق الكود عبر: `claude -p "&lt;prompt&gt;"` أو `claude --print`.
+       - استدعاء `OpenCode CLI` لتنفيذ الأوامر السريعة والطرفية وبناء قواعد البيانات عبر: `opencode run "&lt;message&gt;"`.
+       - استدعاء `Antigravity CLI` لمهام الواجهات وعقود الـ Domain عبر: `agcli run "&lt;message&gt;"`.
+     - معالجة وإدراج مخرجات الـ CLIs تلقائياً في دورة التطوير وبوابات الجودة.
+  4. **التحويل المستدام لنمط المحادثة (Session-Wide Fleet Mode Transformation):**
+     - **قاعدة حاسمة:** بمجرد استدعاء وتفعيل الخطاف 22 (بالمحفزات المعتمدة أو ذكر خطاف 22)، يدخل المساعد فوراً ومستداماً في **نمط قيادة الأسطول (Fleet Command Mode)** لكامل ما تبقى من الجلسة.
+     - تتحول كافة طلبات وأوامر المستخدم اللاحقة تلقائياً إلى أوامر وهياكل تفويض وتنسيق موجهة للأسطول باللغة الإنجليزية وفق الهيكل المعياري المعتمد (`Template 02: Task Delegation Protocol` و `Template 03: Code Review Audit`) مع حصر الملكية الدليلية، وفرض حظر تشغيل الاختبارات على غير Claude Code، وتأكيد خلو الأخطاء (`flutter analyze = 0`) دون الحاجة لتكرار تفعيل الخطاف في كل رسالة.
+  5. **احتكار الفحص والاختبار لـ Claude Code فقط (Testing Monopoly):**
+     - يُحظر حظراً تاماً تشغيل الاختبارات بواسطة OpenCode أو Antigravity. يتولى Claude Code تشغيل الاختبارات وفحص واعتماد أي كود مكتوب قبل دمجه.
+  6. **حوكمة بوابات الجودة وترشيد التوكنز:**
+     - مراجعة diffs كل مرحلة وفرض اللغة الإنجليزية بالكامل في طرفيات الـ CLIs مع حظر كتابة البويلربليت على النماذج العليا.
+  7. **إدارة الكوتا والتسليم السلس (Quota Failover &amp; Re-entry):**
+      - ضمان استمرارية المشروع وتسليم القيادة بسلاسة عند امتلاء كوتا أي نموذج مع تطبيق بروتوكول إعادة الدخول عند تجدد الحصة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>23. خطاف تحويل وأتمتة سكربتات المشاريع إلى MCP</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>حول إلى MCP, تحويل سكربتات لـ MCP, بناء أدوات MCP, convert scripts to mcp, scripts to mcp, ترقية السكربتات</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>[mcp-tool-builder], [script-to-mcp-converter], [code-architect], [agent-optimizer]</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>مسح سكربتات بايثون المبعثرة في مسار المشروع، تجريد منطق العمل وبناء دوال FastMCP ونماذج Pydantic، تسجيل الخادم، وأرشفة السكربتات في القرص الثانوي (G:) وحماية قرص C:.</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **المسح والاكتشاف الشامل (Script Discovery &amp; AST Analysis):**
+     - تشغيل `project_scripts_to_mcp.py` لمسح كافة ملفات بايثون المتناثرة داخل مجلدات المشروع، وتحليل أسماء الدوال، المعاملات، والمخرجات برمجياً.
+  2. **تجريد المنطق وهيكلة Pydantic (Decoupling &amp; Schema Generation):**
+     - فصل كود المعالجة عن المسارات الصلبة (Hardcoded Paths)، وصياغة كلاسات Pydantic Request لكل أداة لضمان التحقق من صحة المدخلات.
+  3. **البناء والتسجيل في FastMCP (FastMCP Tool Registration):**
+     - دمج الدوال في خادم FastMCP موحد ومستقر مع إلزام ترميز UTF-8 ودعم التزامن `asyncio.to_thread`.
+     - تسجيل الخادم وأدواته في `mcp_config.json` للـ IDE والوكلاء.
+  4. **الأرشفة الآمنة وحماية قرص النظام (Secondary Drive Archiving):**
+     - نقل السكربتات القديمة تلقائياً إلى مجلد أرشيف منظم على القرص الثانوي (`G:\_scripts_archive` أو حسب القرص المخصص) مع حظر الحفظ على قرص النظام `C:\`.
+  5. **تحديث مهارات الوكلاء والذاكرة:**
+     - تحديث بطاقات المهارات في `.agents/skills` لتمكين الوكلاء المتخصصين من استدعاء أدوات الـ MCP الجديدة مباشرة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>24. خطاف أتمتة مسارات العمل ووكلاء n8n الذكية</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>ابني مسار n8n, أتمتة n8n, وكيل n8n, n8n ai agent, n8n workflow, تصميم ورك فلو</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>[n8n-ai-agent-architect], [mcp-tool-builder], [backend-architect], [agent-optimizer]</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>تصميم وبناء مسارات عمل ذكية مؤتمتة على n8n، ربط الوكلاء المتعددين (Multi-Agent Sub-workflows)، تتبع التحويلات وتأهيل العملاء، وربط خوادم MCP وقواعد البيانات الموجهة بالذكاء الاصطناعي.</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **التصميم المعماري للمسار (`n8n-ai-agent-architect`):**
+     - اختيار النمط المعماري المناسب (Multi-Agent Router, ReAct Tools Agent, Evaluator-Optimizer Loop, أو Human-in-the-Loop).
+  2. **بناء وهيكلة أدوات الاستدعاء (Tool Calling &amp; JSON Schemas):**
+     - بناء وتوثيق أدوات HTTP Request و Custom JavaScript Tools مع فرض JSON Schema صارم يمنع هلوسة المعاملات.
+  3. **إدارة طبقات الذاكرة (Short-Term &amp; Vector Memory):**
+     - ربط الذاكرة القصيرة (Window Buffer) والذاكرة المستمرة (Postgres/Redis) ومخازن المتجهات الدلالية (Qdrant/Pinecone/Supabase).
+  4. **أتمتة العمليات التسويقية وتأهيل العملاء (Marketing &amp; CRM Pipelines):**
+     - بناء مسارات استقبال وتحليل بيانات العملاء المحتملين من Google Ads و Facebook وتوجيه الإشعارات اللحظية عبر WhatsApp و Slack وتحديث الـ CRM.
+  5. **تحصين الانقطاع ومعالجة الأخطاء (Fault Tolerance &amp; Sub-workflow Retries):**
+     - إضافة مسارات الخطأ (Error Trigger) وإعادة المحاولة مع التراجع التلقائي (Exponential Backoff) ونماذج LLM البديلة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>25. خطاف التصفير الاستراتيجي وتسليم الجلسة</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>التصفير الاستراتيجي, strategic clear, استعد للتصفير, تجهيز clear, تجميد الجلسة, pre-clear handoff, freeze session</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Opus 5 (Thinking)` 
+ البديل: `Claude Sonnet 5`</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>[fleet-orchestrator], [persistent-memory-engine], [git-github-manager]</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>تقييم وإنهاء أي مهام عالقة أو ذات أولوية عاجلة لتأمين استقرار الكود، ثم تجميد وتوثيق الحالة في CURRENT_STATE.md وتوليد برومبت الاستئناف الفوري قبل تنفيذ /clear أو /compact عند امتلاء الجلسة (session:90%+).</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **المرحلة الأولى: المسح السريع وإنهاء المهام العالقة ذات الأولوية (In-Flight Work Resolution &amp; Stabilization):**
+     - جرد فوري لأي مهام أو أوامر ذات أولوية قصوى قيد التنفيذ قبل اتخاذ قرار التصفير.
+     - إذا كانت المهمة قريبة من الإنجاز: يتم إكمالها فوراً وبناء الكود وفحصه برمجياً واعتماده بعمل `git commit` نظيف ومحكم.
+     - إذا كانت المهمة كبيرة وتحتاج جولات إضافية: يتم تثبيت الكود عند محطة استقرار آمنة (Compilable Milestone) وعزل أي تجارب ناقصة لضمان بقاء الفرع أخضر 100% وخالياً من أي أخطاء كسر بناء.
+  2. **المرحلة الثانية: تجميد الحالة وتوثيق سياق المشروع وحراسة الذاكرة (State Freeze &amp; Memory Quarantine):**
+     - مطابقة وتحديث ملف الحالة `fleet_orders/CURRENT_STATE.md` (أو `PROJECT_CONTEXT.md`) وتحديث بند "الخطوة التالية المحددة" (The One Thing To Do Next).
+     - فحص ومطابقة `git status --short --branch` للتأكد من خلو شجرة العمل من أي تعديلات تائهة أو غير معتمدة.
+     - تسجيل أي اكتشافات أو ملاحظات عتادية أو فخاخ برمجية جديدة في `MEMORY_STORE.md`.
+  3. **المرحلة الثالثة: تحديد القرارات وتوليد برومبت الاستئناف الفوري (Resume Prompt &amp; Green Light):**
+     - صياغة ملخص تسليم محكم يتضمن: ما تم إنجازه، آخر Commit معتمد، والخيارات المتاحة أمام المطور للجلسة القادمة.
+     - توليد برومبت استئناف دقيق (Ready to copy-paste) لنسخه ولصقه فور تنفيذ أمر التصفير:
+       `Read CLAUDE.md and fleet_orders/CURRENT_STATE.md. State where we are and present the choices for the next order.`
+     - منح الضوء الأخضر الصريح للمطور: تأكيد إمكانية تنفيذ أمر `/clear` أو `/compact` بأمان تام وبدون أي هدر للسياق.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>26. خطاف إدارة وتحديث مكتبة الأوامر الذكية</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>أضف لمكتبة الأوامر, وثق في مكتبة الأوامر, أضف برومبت للإكسيل, تحديث مكتبة الأوامر, حفظ في مكتبة الأوامر, add prompt to library, curate prompt</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Gemini 3.8 Flash (High)` 
+ البديل: `Claude Sonnet 5`</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>[prompt-engineer], [agent-optimizer], [code-architect]</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>تحويل الأفكار والحلول البرمجية لبرومبتات مهندسة جاهزة للاستخدام، وإدراجها آلياً في التبويب المناسب داخل ملف "مكتبة الأوامر.xlsx" مع الحفاظ على التنسيق والخطوط وإبلاغ المستخدم بموقع ورقم الصف المضاف.</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **الالتقاط والهندسة البرمجية للموجه (`[prompt-engineer]`):**
+     - استلام الفكرة، الميزة، أو الأمر البرمجي من سياق الجلسة الحالية.
+     - صياغته وهندسته كأمر معياري متكامل يتضمن:
+       - اسم الأمر بالعربية والإنجليزية مقروناً بإيموجي معبر (العمود B).
+       - الأمر البرمجي / الموجه الكامل (Command / Prompt) (العمود C).
+       - الوصف الدقيق، الهدف، وحالات الاستخدام المثلى (العمود D).
+  2. **التوجيه الذكي للتبويب المناسب (Smart Sheet Routing):**
+     - فحص كافة تبويبات ملف `G:\أرشيف_ونسخ_احتياطية\ملفات_مكررة_وعامة\AI\مكتبة الأوامر.xlsx`.
+     - توجيه الأمر تلقائياً للتبويب المتخصص:
+       - `CLI_Core.Claude`: أوامر الـ CLI، الأسطول، التصفير، والتحكم في المحركات.
+       - `Workflows_Pipelines.Claude`: مسارات العمل، CI/CD، البناء والتوزيع.
+       - `Gates_Hooks.Claude`: بوابات الجودة، الخطافات، والتدقيق المعماري.
+       - `Custom_Skills.Claude`: المهارات المخصصة، الوكلاء الفرعيون، وحزم الأدوات.
+       - `Config_Environments.Claude`: إعدادات البيئة، مسارات SDK، الذاكرة، و Gradle.
+       - `Construction_MCP_Suite`: أدوات الهندسة المدنية، جداول الكميات BOQ، والعقود.
+  3. **الإدراج البرمجي المحصن في الإكسيل (`prompt_library_curator.py` / `add-prompt`):**
+     - استدعاء أداة الأتمتة المدمجة `add-prompt`.
+     - حساب الرقم التسلسلي التالي (`No`) واكتشاف الصف النظيف القادم تلقائياً.
+     - تطبيق التنسيق الدقيق للخلايا (خط Segoe UI 10pt، خط Consolas للكود، محاذاة اليمين واليسار المناسبة، والحدود الرقيقة Thin Borders).
+     - معالجة قفل الملفات: في حال كان الإكسيل مفتوحاً لدى المستخدم، يتم الاعتماد تلقائياً على Excel COM Automation للكتابة الحية دون أخطاء PermissionError.
+  4. **إشعار المستخدم بالموقع الدقيق:**
+      - طباعة تقرير تأكيد فوري يتضمن: اسم الأمر، اسم التبويب (Sheet Name)، ورقم الصف الدقيق (Row Number) لسهولة الوصول إليه واستنساخه مستقبلاً.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>27. خطاف الاستشارة الاستراتيجية لإدارة نافذة السياق</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>مستشار السياق, إدارة السياق, مستشار التوكنز, ترشيد السياق, فحص نافذة السياق, context advisor, manage context, agy context advice, قرارات السياق</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Gemini 3.8 Flash (High)` 
+ البديل: `Claude Sonnet 5`</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>[prompt-engineer], [agent-optimizer], [code-architect]</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>تحليل لحظي ودقيق لاستهلاك السياق والتوكنز في Antigravity IDE/agcli، تصنيف الجلسة ضمن 4 مناطق أمان (خضراء، صفراء، برتقالية، حمراء)، وتوجيه المطور للقرار المعماري الأنسب (استمرار، ترشيد، ضغط، أو تصفير استراتيجي وتسليم).</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **الاستعلام الآلي عن استهلاك التوكنز والسياق (`context_advisor.py` / `ag-context -a`):**
+     - قراءة التليمتري الحية من قاعدة بيانات الجلسة الحالية (`input_tokens`, `output_tokens`, `thinking_tokens`, `limit`, `velocity`).
+     - المعايرة على **النطاق الذهبي للإنتاجية القصوى والدقة (30,000 إلى 300,000 توكن)** لحماية النموذج من تشتت الانتباه.
+  2. **التشخيص وتحديد منطقة الأمان (Context Health Zone Diagnostic):**
+     - 🟢 **المنطقة الخضراء (&lt; 180k توكن | أقل من 60% من النطاق الذهبي):** أمان تام وانتباه كامل (100% Attention Fidelity)؛ الاستمرار في التطوير دون أي تدخل مع ترشيد القراءة.
+     - 🟡 **المنطقة الصفراء (180k إلى 240k توكن | 60% - 80%):** تنبيه مبكر واقتراب من حافة النطاق الذهبي؛ حظر قراءة الملفات الكاملة والاعتماد الحصري على التوقيعات (Signatures) وأجزاء الأسطر عبر `lean-ctx`.
+     - 🟠 **المنطقة البرتقالية (240k إلى 300k توكن | 80% - 100%):** منطقة التخطيط للتسليم والضغط؛ تثبيت الكود الحالي بعمل `git commit`، وتوثيق الدروس في `MEMORY_STORE.md`, والاستعداد للضغط أو التصفير.
+     - 🔴 **المنطقة الحمراء (&gt; 300k توكن | تجاوز سقف النطاق الذهبي):** خروج صريح من نطاق الدقة القصوى؛ خطر فقدان الانتباه والهلوسة، والتفعيل الفوري الإلزامي للخطاف 25 (التصفير الاستراتيجي وتسليم الجلسة) وتوليد برومبت الاستئناف ثم تنفيذ `/clear`.
+  3. **توليد القرار الاستراتيجي والأوامر الجاهزة:**
+     - تقديم ملخص فني موجز باللغة العربية بتنسيق RTL.
+     - تقديم الأمر التكليفي أو التنفيذي الجاهز للنسخ بنقرة واحدة وفقاً للمنطقة المحددة.
+  4. **حوكمة استدعاء الوكلاء الفرعيين وترشيد التوكنز (Subagent Budgeting &amp; Governance):**
+     - حظر إطلاق أسراب متزامنة (Swarms) واقتصار الاستدعاء على وكيل مفرد متسلسل بهدف محدد.
+     - إلزام الوكلاء الفرعيين ببروتوكول القراءة المتدرجة (`mode=signatures`) وتمرير مقاطع الأسطر المحددة فقط.
+     - منع تشغيل الوكلاء الفرعيين كلياً في المنطقة الحمراء (&gt; 300k) وإلزام التصفير الاستراتيجي أولاً.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>28. خطاف ترحيل وتطهير أدوات المحرر والذكاء الاصطناعي</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>تطهير المحرر, نقل أدوات المحرر, ترحيل أدوات المحرر, تطهير المشروع, evacuate editor tools, clean workspace tooling, evacuate-tools</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Gemini 3.8 Flash (High)` 
+ البديل: `Claude Sonnet 5`</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>[devops-deployer], [agent-optimizer], [code-architect]</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>فحص ومزامنة أدوات المحرر في الإعدادات العالمية (~/.gemini/config)، ونقل كافة الأدلة والمستندات والسكربتات إلى المستودع المركزي (Claude+Antigravity) بعد التحقق التشفيري الإلزامي (SHA-256) قبل الحذف، وتنظيف مخلفات الذاكرة وحطام JVM لضمان نقاء بيئة المشاريع البرمجية.</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **المزامنة والتحديث للسيستم العالمي (`C:\Users\Kt\.gemini\config\tools\`):**
+     - جرد أدوات المحرر في مجلد `tools/` بالمشروع ومقارنتها بالنسخ العالمية وتحديثها لضمان عدم ضياع أي ميزة جديدة.
+  2. **الترحيل والأرشفة المركزية (`F:\AI PROJECTS\Claude+Antigravity\`):**
+     - نقل أدلة المحرر (`*.docx`, `*.pdf`, `*.md`) إلى مجلد `docs/`، والمخططات إلى `assets/`، والسكربتات إلى `tools/`.
+  3. **التدقيق التشفيري الإلزامي قبل الحذف (SHA-256 Verification):**
+     - يُحظر حذف أي ملف محلي إلا بعد حساب بصمة SHA-256 للمصدر والوجهة والتأكد من التطابق التام 100%. وفي حال وجود نسخة أحدث في المركز، تُحفظ كنسخة أرشيفية.
+  4. **التطهير الآمن للمشروع المحلي (Clean Workspace Guarantee):**
+     - حذف الأدوات المنقولة، وإزالة مجلد `tools/` بعد فراغه، وتنظيف مخلفات JVM (`hs_err_*.log`, `replay_*.log`) وأقفال Word المؤقتة، واستعادة الشجرة النظيفة الخالية من أي Untracked files.
+&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -530,34 +1705,150 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="80" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>م</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>اسم الخطاف</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Prompt</t>
+          <t>المحفزات (الخطاف للنسخ)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Notes or description</t>
+          <t>النموذج الأساسي والبديل</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>الوكلاء المسؤولون</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>الهدف الأساسي</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>الوصف والتفاصيل</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>9. خطاف مراجعة وتحديث المكتبات والنماذج</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>تحديث الاعتماديات, تحديث المكتبات, تحديث النماذج, معايرة النماذج, update models</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Gemini 3.7 Flash (High)` 
+ البديل: `Gemini 3.6 Flash (Medium)`</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[github-talent-scout], [code-architect], [agent-optimizer]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>فحص ملفات Gradle وتحديث المكتبات، والتحقق التلقائي عبر الإنترنت (antigravity.google) لتحديث مصفوفة النماذج ودليل hooks_user_guide.md دون لقطات شاشة.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **فحص إصدارات المكتبات:** مسح ملفات `build.gradle.kts` ومقارنة إصدارات المكتبات الحالية بأحدث الإصدارات المستقرة.
+  2. **الاستكشاف والمعايرة التلقائية للنماذج عبر الإنترنت (Online Model Discovery):** الاستعلام الفوري عبر المصادر الرسمية (antigravity.google, docs.anthropic.com) ومعايرة مصفوفة النماذج.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>اسم الخطاف</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>المحفزات (الخطاف للنسخ)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>النموذج الأساسي والبديل</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>الوكلاء المسؤولون</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>الهدف الأساسي</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>الوصف والتفاصيل</t>
         </is>
       </c>
     </row>
@@ -565,27 +1856,824 @@
       <c r="A2" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>10. تنظيم ملفات الجهاز</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>`"رتب جهازي"`, `"تنظيم الجهاز"`, `"ترتيب المجلد"`</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>الوكلاء المسؤولون: `windows-file-organizer` + `windows-c-drive-optimizer`
-الوصف العام: ترتيب الملفات العامة والمجلدات على الجهاز بأمان مع التحقق من روابط عبور القرص C لتجنب كسرها
-الإجراءات التفصيلية:
-1. يستقبل مسار المجلد أو القرص المراد تنظيمه على الجهاز من المستخدم.
-  2. يستدعي الوكيل `windows-c-drive-optimizer` للتحقق وفحص روابط عبور القرص C (Junction Links / Symlinks) النشطة للتأكد من عدم نقل أو تعديل مجلدات المقصد التعاقدية (مثل `.gradle` أو `.m2` أو أي مجلدات مبرمجة) لضمان عدم تعطل النظام.
-  3. يقوم الوكيل `windows-file-organizer` بجرد وتصنيف الملفات حسب موضوعاتها ونوع الامتدادات مع استثناء كلي لكافة المجلدات الهندسية ومجلدات تثبيت البرامج ومشاريع الذكاء الاصطناعي النشطة.
-  4. يجمع النسخ المكررة والملفات القديمة وينقلها لمجلد فرعي "أرشيف / نسخ احتياطية".
-  5. يعرض الهيكل الهجين المقترح وجدول النقل للمستخدم للتأكيد.
-  6. يولد وينفذ سكريبت النقل الآمن برمجياً فور الموافقة.</t>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>10. خطاف الفحص والاختبار التلقائي</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>قم بالاختبار, جاهز للتجربة</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[android-testing], [test-guard], [code-reviewer-quality]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>تشغيل اختبارات الوحدة وفحص جودة الكود واختبار السلوك الفعلي بدون Mock مفرط.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **حراسة الاختبارات (`test-guard`):** التحقق من أن الاختبارات تفحص سلوك النظام الفعلي ومنع Mocks الوهمية.
+  2. **قاعدة التغطية الإجبارية:** اختبار مسار النجاح، الفشل، والحالات الطرفية (Network Off, Lifecycle).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>اسم الخطاف</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>المحفزات (الخطاف للنسخ)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>النموذج الأساسي والبديل</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>الوكلاء المسؤولون</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>الهدف الأساسي</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>الوصف والتفاصيل</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>11. خطاف معالجة الأخطاء والأعطال</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>حدث خطأ, التطبيق توقف, Crash</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[debugger]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>تحليل سجلات الأخطاء والـ Stack Trace وعزل الكود المسبب للمشكلة وإصلاحه.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **تحليل الـ Stack Trace:** قراءة السجلات بدقة وتحديد السطر المسبب للخلل وعزله وإصلاحه بأقل تعديل كافٍ.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>اسم الخطاف</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>المحفزات (الخطاف للنسخ)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>النموذج الأساسي والبديل</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>الوكلاء المسؤولون</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>الهدف الأساسي</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>الوصف والتفاصيل</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>12. خطاف إدارة النسخ والمستودعات</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>نظم جيت, ارفع لجيتهاب, تحديث المستودع, git commit</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Gemini 3.7 Flash (High)` 
+ البديل: `Gemini 3.6 Flash (Medium)`</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[git-github-manager]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>تهيئة المشاريع الجديدة على Git، إدارة التفرعات، وحل تعارضات الدمج ورفعها لـ GitHub بشكل نظيف.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **التحقق من حالة المستودع:** فحص حالة Git واستثناء الملفات غير الضرورية في `.gitignore`.
+  2. **التنفيذ والرفع:** كتابة رسائل Commit احترافية وحل التعارضات ودفع التغييرات إلى GitHub.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>اسم الخطاف</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>المحفزات (الخطاف للنسخ)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>النموذج الأساسي والبديل</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>الوكلاء المسؤولون</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>الهدف الأساسي</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>الوصف والتفاصيل</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>13. خطاف تحديث الإنجازات</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>حدث الإنجازات, تحديث README, وثق الإنجازات</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Gemini 3.7 Flash (High)` 
+ البديل: `Claude Sonnet 4.6 (Thinking)`</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[git-github-manager], [docs-guard]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>صياغة التعديلات كإنجازات ومطابقتها برمجياً وتحديث README.md و hooks_user_guide.md ثم الرفع لـ GitHub.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **قراءة السجل ومطابقة التوثيق (`docs-guard`):** مراجعة التغييرات الأخيرة وصياغة الإنجازات وتحديث `README.md`.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>اسم الخطاف</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>المحفزات (الخطاف للنسخ)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>النموذج الأساسي والبديل</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>الوكلاء المسؤولون</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>الهدف الأساسي</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>الوصف والتفاصيل</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>14. خطاف الذاكرة المستدامة</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>حفظ ذاكرة, تحديث السياق, سجّل هذا</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `GPT-OSS 120B (Medium)`</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[persistent-memory-engine]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>التقاط الدروس والقرارات وتخزينها في MEMORY_STORE.md وتصديرها للوكلاء.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **التقاط وتخزين الدروس:** حفظ القرارات المعمارية وتفضيلات المستخدم في `MEMORY_STORE.md`.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>اسم الخطاف</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>المحفزات (الخطاف للنسخ)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>النموذج الأساسي والبديل</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>الوكلاء المسؤولون</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>الهدف الأساسي</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>الوصف والتفاصيل</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>15. خطاف النجاح والتحليل البعدي</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>تم بنجاح, انتهى المشروع بنجاح</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[agent-optimizer]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>إجراء تحليل بعدي للمشروع وتحديث سجل التعلم وسد الثغرات البرمجية.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **التحليل البعدي (Post-Mortem Analysis):** دراسة سجل المحادثة واستخراج العقبات وتحديث سجل التعلم وسد الفجوات.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>اسم الخطاف</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>المحفزات (الخطاف للنسخ)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>النموذج الأساسي والبديل</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>الوكلاء المسؤولون</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>الهدف الأساسي</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>الوصف والتفاصيل</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>16. خطاف تنظيم وترتيب الأجهزة الشامل</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>رتب جهازى, فرز الملفات, ترتيب ملفات</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Gemini 3.7 Flash (High)` 
+ البديل: `Gemini 3.6 Flash (Medium)`</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[windows-c-drive-optimizer], [windows-file-organizer]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>ترتيب ملفات جذور الأقراص بالكامل مع تنظيف وتحسين مساحة قرص الـ C بآن واحد.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **تحليل وتحرير مساحة القرص C: السريع والمتقدم:**
+     - تفريغ كاش حزم بايثون الحديثة (`uv cache clean`) وكاش `npm` وملفات `CrashDumps`.
+     - تفريغ المجلدات المؤقتة (`AppData\Local\Temp` و `C:\Windows\Temp`).
+     - استدعاء سكربت التنظيف الشامل: `&amp; "C:\Users\Kt\.gemini\config\tools\Deep_Clean_C_Drive.ps1"`.
+  2. **معمارية ترحيل الأقراص الافتراضية وكاش التطوير (DevCache Junctions):**
+     - فحص وتأمين ترحيل أقراص Docker WSL (`docker_data.vhdx`) إلى `D:\DevCache\Docker_wsl\disk`.
+     - ترحيل حزم Claude Desktop VM (`vm_bundles` بحجم 10.36 GB) إلى `D:\DevCache\Claude_vm_bundles` عبر `&amp; "C:\Users\Kt\.gemini\config\tools\Relocate_Claude_VM_Bundles.ps1"`.
+     - التحقق من ربط نماذج Ollama بالقرص الثانوي (`D:\AI_Models\Ollama\models`).
+  3. **فرز وتصنيف جذور الأقراص (F:, G:, D:, E:):**
+     - جرد الملفات السائبة في جذور الأقراص وتصنيفها فوراً إلى مجلداتها الموضوعية (رسومات هندسية، مشاريع مونتاج، تسجيلات، مستندات).
+     - التخلص من ملفات سجلات الانهيار القديمة (مثل `DUMP*.tmp`).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>اسم الخطاف</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>المحفزات (الخطاف للنسخ)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>النموذج الأساسي والبديل</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>الوكلاء المسؤولون</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>الهدف الأساسي</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>الوصف والتفاصيل</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>17. خطاف ترتيب الملفات لمسار محدد</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>رتب المسار, نظم المجلد, ترتيب مسار</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Gemini 3.6 Flash (Medium)` 
+ البديل: `Gemini 3.5 Flash (Medium)`</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[windows-file-organizer]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>تنظيم وفرز الملفات داخل مجلد أو مسار مخصص يحدده المستخدم بذكاء ودقة.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **تنظيم وفرز الملفات:** تصنيف الملفات داخل مجلد محدد بذكاء ودقة.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>اسم الخطاف</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>المحفزات (الخطاف للنسخ)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>النموذج الأساسي والبديل</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>الوكلاء المسؤولون</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>الهدف الأساسي</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>الوصف والتفاصيل</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>18. خطاف إدارة تليجرام</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>شغل البوت, تفعيل تليجرام, Telegram Bot</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Gemini 3.5 Flash (Medium)` 
+ البديل: `Gemini 3.1 Pro (Low)`</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[devops-deployer], [persistent-memory-engine]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>تشغيل بوت تليجرام في الخلفية بنمط الاستماع للطلبات عن بعد دون تعارض.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **التشغيل بنمط الاستماع الفردي (One-Shot Polling):** تشغيل البوت للاستماع لطلب واحد دون تعارض مع بيئة التطوير.</t>
         </is>
       </c>
     </row>
@@ -600,61 +2688,1162 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="80" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>م</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>اسم الخطاف</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Prompt</t>
+          <t>المحفزات (الخطاف للنسخ)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Notes or description</t>
+          <t>النموذج الأساسي والبديل</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>الوكلاء المسؤولون</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>الهدف الأساسي</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>الوصف والتفاصيل</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>2. جدول زمني</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>`"جدول زمني"`, `"جدول أنشطة"`, `"WBS"`</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>الوكلاء المسؤولون: `schedule-builder`
-الوصف العام: بناء الجدول الزمني والمسار الحرج
-الإجراءات التفصيلية:
-1. يقرأ مرجع الجداول الزمنية من `references/جداول_زمنية/`
-  2. يسأل عن: بنود العمل، المدة الإجمالية، تاريخ البدء
-  3. يبني WBS ثم جدول الأنشطة
-  4. يحسب المسار الحرج
-  5. ينتج ملف `A-XX-Activities.xlsx` + الجدول الزمني PDF</t>
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>1. خطاف البدء والافتتاح</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>بسم الله, بسم الله الرحمن الرحيم</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Gemini 3.7 Flash (High)` 
+ البديل: `Gemini 3.6 Flash (Medium)`</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[prompt-engineer], [agent-optimizer]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>تهيئة الجلسة، التحقق من القواعد الفنية واللغوية، وترشيد الاستهلاك.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **تفعيل القواعد والتعليمات:** مراجعة وتطبيق كافة التوجيهات البرمجية واللغوية في المشروع (مثل الكتابة باللغة العربية، وتنسيق RTL).
+  2. **تحسين وترشيد الاستهلاك:** تحليل سياق المحادثة وتوجيهها لتكون بأعلى كفاءة مع توفير استهلاك التوكنز.
+  3. **إعلان الجاهزية:** إشعار المستخدم بتفعيل القواعد واستعداد الطاقم البرمجي للعمل.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>اسم الخطاف</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>المحفزات (الخطاف للنسخ)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>النموذج الأساسي والبديل</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>الوكلاء المسؤولون</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>الهدف الأساسي</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>الوصف والتفاصيل</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>19. خطاف التدقيق البرمجي الشامل وحراسة الجودة</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>تدقيق الجودة, فحص الكود النظيف, حراسة الجودة, clean code audit</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Claude Opus 4.6 (Thinking)`</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[code-reviewer-quality], [clean-code-guard], [test-guard], [docs-guard]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>تفعيل بوابات الحماية الثلاث لفحص الكود النظيف، سلامة الاختبارات، ومطابقة التوثيق.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **تفعيل بوابات الحماية الثلاث:** فحص الكود النظيف (`clean-code-guard`)، سلامة الاختبارات (`test-guard`)، ومطابقة التوثيق (`docs-guard`).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>اسم الخطاف</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>المحفزات (الخطاف للنسخ)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>النموذج الأساسي والبديل</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>الوكلاء المسؤولون</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>الهدف الأساسي</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>الوصف والتفاصيل</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>20. خطاف استكشاف وتكامل الموارد العالمية</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>استكشف المورد, حلل المستودع, تكامل المورد, scout resource, integrate repo</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[resource-scout-integrator], [ui-ux-pro-max], [github-talent-scout], [skill-forge-builder], [agent-optimizer], [frontend-design-builder], [git-github-manager], [powershell-runtime-pro]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>تحليل المستودعات الخارجية واستيراد المهارات وتعميمها وتحديث الخطافات والإكسيل وتطبيق مكتبة الأوامر ودليل hooks_user_guide.md ومزامنة المنظومة.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **استيراد وتعميم المهارات العالمية:** تحليل المستودعات الخارجية وبناء مهارات `SKILL.md` ونشرها عالمياً وتحديث المنظومة.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>اسم الخطاف</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>المحفزات (الخطاف للنسخ)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>النموذج الأساسي والبديل</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>الوكلاء المسؤولون</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>الهدف الأساسي</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>الوصف والتفاصيل</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>21. خطاف المزامنة السحابية والمساهمة المجتمعية</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>مزامنة المنظومة, sync ecosystem, ارسل pull request, مساهمة في المستودع, create PR, contribute repo</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Gemini 3.7 Flash (High)` 
+ البديل: `Claude Sonnet 4.6 (Thinking)`</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[git-github-manager], [persistent-memory-engine], [agent-optimizer], [docs-guard]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>للمطور المالك: مطابقة ومزامنة كافة الإضافات والمهارات وتطبيق الأوامر مع GitHub. للمساهمين والمجتمع: تجهيز فرع الميزة وإنشاء وتوجيه Pull Request للمستودع المركزي للمشاركة.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **المسار الأول (للمطور المالك / Maintainer):**
+     - تشغيل `sync_global_ecosystem.py` لمطابقة كامل منظومة الوكلاء والمهارات والمراجع مع المسار العالمي ورفعها إلى مستودع GitHub الرئيسي بنقرة واحدة.
+  2. **المسار الثاني (للمساهمين والمجتمع / Community &amp; Contributors):**
+     - عند إضافة مهارة أو ميزة جديدة في نسخة Fork، يقوم الخطاف بفحص توافق الكود والتوثيق مع معايير Autovem.
+     - إنشاء فرع مساهمة (Feature Branch) وصياغة رسالة الالتزام وفق مواصفات Conventional Commits.
+     - فتح وتوجيه رابط **Pull Request** تلقائياً إلى المستودع المركزي [Claude-Antigravity-Workspace على GitHub](https://github.com/ibrahimalkateb965-tech/Claude-Antigravity-Workspace) لمراجعتها ودمجها لصالح المجتمع.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>اسم الخطاف</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>المحفزات (الخطاف للنسخ)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>النموذج الأساسي والبديل</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>الوكلاء المسؤولون</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>الهدف الأساسي</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>الوصف والتفاصيل</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>22. خطاف قيادة وإدارة الأسطول التشاركي</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>أسطول الـ CLIs, تشغيل الأسطول, تنسيق الأسطول, fleet orchestrator, multi cli fleet, إدارة الأسطول</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Opus 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[fleet-orchestrator], [code-architect], [agent-optimizer], [persistent-memory-engine]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>تفعيل وضبط أسطول الوكلاء المتعدد، إدارة وتنسيق التكليف بين CLIs، حوكمة بوابات مراجعة الأكواد، وترشيد التوكنز.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **التهيئة والتوليد التلقائي (Auto-Provisioning):**
+     - فحص وجود مجلد `fleet_templates/` وملف `fleet_config.json` في المشروع وتوليدهما تلقائياً عند عدم وجودهما.
+  2. **توزيع المسؤوليات والحدود الحصرية وضبط النماذج:**
+     - تحديد ملكية الملفات والمهام في `fleet_config.json` لمنع التصادم:
+       - **Claude Code CLI** (النموذج: `Claude 5 Opus / Opus Max`): التخطيط والمراجعة المعمارية، **التنفيذ الحصري لكافة الاختبارات التلقائية**، واعتماد الأكواد وبوابات الجودة (Quality Gates).
+       - **OpenCode CLI** (النموذج: `Ox Alpha Unlimited`): التنفيذ الطرفي، إدارة قواعد البيانات Drift/ORM، وعملاء الاتصال والبيانات (كتابة وبناء فقط دون تشغيل أي اختبارات).
+       - **Antigravity CLI (`agcli`)** (النموذج: `Gemini 3.8 Flash High` / `hermes3:8b` Ollama): المنفذ الطرفي الذاتي لبناء الواجهات (UI)، تكييف المنصات، عقود الـ Domain، وهندسة الملفات (كتابة وبناء دون تشغيل اختبارات عبر سطر الأوامر دون نسخ ولصق).
+       - **Antigravity IDE** (النموذج: `Gemini 3.8 Flash High`): بيئة العمل التفاعلية وحاضنة المطور المركزية (Interactive Cockpit) لإدارة الجلسة والمحادثة واستعراض الفروقات (Diffs)؛ ولا تُوجّه أوامر تفويض الـ CLI البرمجية إليها لمنع تعليق الأتمتة.
+  3. **التشغيل المباشر لأدوات الـ CLI (Headless Direct Invocation):**
+     - تشغيل واستدعاء أدوات الـ CLI المثبتة مباشرة عبر سطر الأوامر غير التفاعلي:
+       - استدعاء `Claude Code CLI` للمراجعة المعمارية وتشغيل الاختبارات وتدقيق الكود عبر: `claude -p "&lt;prompt&gt;"` أو `claude --print`.
+       - استدعاء `OpenCode CLI` لتنفيذ الأوامر السريعة والطرفية وبناء قواعد البيانات عبر: `opencode run "&lt;message&gt;"`.
+       - استدعاء `Antigravity CLI` لمهام الواجهات وعقود الـ Domain عبر: `agcli run "&lt;message&gt;"`.
+     - معالجة وإدراج مخرجات الـ CLIs تلقائياً في دورة التطوير وبوابات الجودة.
+  4. **التحويل المستدام لنمط المحادثة (Session-Wide Fleet Mode Transformation):**
+     - **قاعدة حاسمة:** بمجرد استدعاء وتفعيل الخطاف 22 (بالمحفزات المعتمدة أو ذكر خطاف 22)، يدخل المساعد فوراً ومستداماً في **نمط قيادة الأسطول (Fleet Command Mode)** لكامل ما تبقى من الجلسة.
+     - تتحول كافة طلبات وأوامر المستخدم اللاحقة تلقائياً إلى أوامر وهياكل تفويض وتنسيق موجهة للأسطول باللغة الإنجليزية وفق الهيكل المعياري المعتمد (`Template 02: Task Delegation Protocol` و `Template 03: Code Review Audit`) مع حصر الملكية الدليلية، وفرض حظر تشغيل الاختبارات على غير Claude Code، وتأكيد خلو الأخطاء (`flutter analyze = 0`) دون الحاجة لتكرار تفعيل الخطاف في كل رسالة.
+  5. **احتكار الفحص والاختبار لـ Claude Code فقط (Testing Monopoly):**
+     - يُحظر حظراً تاماً تشغيل الاختبارات بواسطة OpenCode أو Antigravity. يتولى Claude Code تشغيل الاختبارات وفحص واعتماد أي كود مكتوب قبل دمجه.
+  6. **حوكمة بوابات الجودة وترشيد التوكنز:**
+     - مراجعة diffs كل مرحلة وفرض اللغة الإنجليزية بالكامل في طرفيات الـ CLIs مع حظر كتابة البويلربليت على النماذج العليا.
+  7. **إدارة الكوتا والتسليم السلس (Quota Failover &amp; Re-entry):**
+      - ضمان استمرارية المشروع وتسليم القيادة بسلاسة عند امتلاء كوتا أي نموذج مع تطبيق بروتوكول إعادة الدخول عند تجدد الحصة.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>اسم الخطاف</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>المحفزات (الخطاف للنسخ)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>النموذج الأساسي والبديل</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>الوكلاء المسؤولون</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>الهدف الأساسي</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>الوصف والتفاصيل</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>23. خطاف تحويل وأتمتة سكربتات المشاريع إلى MCP</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>حول إلى MCP, تحويل سكربتات لـ MCP, بناء أدوات MCP, convert scripts to mcp, scripts to mcp, ترقية السكربتات</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[mcp-tool-builder], [script-to-mcp-converter], [code-architect], [agent-optimizer]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>مسح سكربتات بايثون المبعثرة في مسار المشروع، تجريد منطق العمل وبناء دوال FastMCP ونماذج Pydantic، تسجيل الخادم، وأرشفة السكربتات في القرص الثانوي (G:) وحماية قرص C:.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **المسح والاكتشاف الشامل (Script Discovery &amp; AST Analysis):**
+     - تشغيل `project_scripts_to_mcp.py` لمسح كافة ملفات بايثون المتناثرة داخل مجلدات المشروع، وتحليل أسماء الدوال، المعاملات، والمخرجات برمجياً.
+  2. **تجريد المنطق وهيكلة Pydantic (Decoupling &amp; Schema Generation):**
+     - فصل كود المعالجة عن المسارات الصلبة (Hardcoded Paths)، وصياغة كلاسات Pydantic Request لكل أداة لضمان التحقق من صحة المدخلات.
+  3. **البناء والتسجيل في FastMCP (FastMCP Tool Registration):**
+     - دمج الدوال في خادم FastMCP موحد ومستقر مع إلزام ترميز UTF-8 ودعم التزامن `asyncio.to_thread`.
+     - تسجيل الخادم وأدواته في `mcp_config.json` للـ IDE والوكلاء.
+  4. **الأرشفة الآمنة وحماية قرص النظام (Secondary Drive Archiving):**
+     - نقل السكربتات القديمة تلقائياً إلى مجلد أرشيف منظم على القرص الثانوي (`G:\_scripts_archive` أو حسب القرص المخصص) مع حظر الحفظ على قرص النظام `C:\`.
+  5. **تحديث مهارات الوكلاء والذاكرة:**
+     - تحديث بطاقات المهارات في `.agents/skills` لتمكين الوكلاء المتخصصين من استدعاء أدوات الـ MCP الجديدة مباشرة.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>اسم الخطاف</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>المحفزات (الخطاف للنسخ)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>النموذج الأساسي والبديل</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>الوكلاء المسؤولون</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>الهدف الأساسي</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>الوصف والتفاصيل</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>24. خطاف أتمتة مسارات العمل ووكلاء n8n الذكية</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>ابني مسار n8n, أتمتة n8n, وكيل n8n, n8n ai agent, n8n workflow, تصميم ورك فلو</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[n8n-ai-agent-architect], [mcp-tool-builder], [backend-architect], [agent-optimizer]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>تصميم وبناء مسارات عمل ذكية مؤتمتة على n8n، ربط الوكلاء المتعددين (Multi-Agent Sub-workflows)، تتبع التحويلات وتأهيل العملاء، وربط خوادم MCP وقواعد البيانات الموجهة بالذكاء الاصطناعي.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **التصميم المعماري للمسار (`n8n-ai-agent-architect`):**
+     - اختيار النمط المعماري المناسب (Multi-Agent Router, ReAct Tools Agent, Evaluator-Optimizer Loop, أو Human-in-the-Loop).
+  2. **بناء وهيكلة أدوات الاستدعاء (Tool Calling &amp; JSON Schemas):**
+     - بناء وتوثيق أدوات HTTP Request و Custom JavaScript Tools مع فرض JSON Schema صارم يمنع هلوسة المعاملات.
+  3. **إدارة طبقات الذاكرة (Short-Term &amp; Vector Memory):**
+     - ربط الذاكرة القصيرة (Window Buffer) والذاكرة المستمرة (Postgres/Redis) ومخازن المتجهات الدلالية (Qdrant/Pinecone/Supabase).
+  4. **أتمتة العمليات التسويقية وتأهيل العملاء (Marketing &amp; CRM Pipelines):**
+     - بناء مسارات استقبال وتحليل بيانات العملاء المحتملين من Google Ads و Facebook وتوجيه الإشعارات اللحظية عبر WhatsApp و Slack وتحديث الـ CRM.
+  5. **تحصين الانقطاع ومعالجة الأخطاء (Fault Tolerance &amp; Sub-workflow Retries):**
+     - إضافة مسارات الخطأ (Error Trigger) وإعادة المحاولة مع التراجع التلقائي (Exponential Backoff) ونماذج LLM البديلة.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>اسم الخطاف</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>المحفزات (الخطاف للنسخ)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>النموذج الأساسي والبديل</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>الوكلاء المسؤولون</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>الهدف الأساسي</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>الوصف والتفاصيل</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>25. خطاف التصفير الاستراتيجي وتسليم الجلسة</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>التصفير الاستراتيجي, strategic clear, استعد للتصفير, تجهيز clear, تجميد الجلسة, pre-clear handoff, freeze session</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Opus 5 (Thinking)` 
+ البديل: `Claude Sonnet 5`</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[fleet-orchestrator], [persistent-memory-engine], [git-github-manager]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>تقييم وإنهاء أي مهام عالقة أو ذات أولوية عاجلة لتأمين استقرار الكود، ثم تجميد وتوثيق الحالة في CURRENT_STATE.md وتوليد برومبت الاستئناف الفوري قبل تنفيذ /clear أو /compact عند امتلاء الجلسة (session:90%+).</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **المرحلة الأولى: المسح السريع وإنهاء المهام العالقة ذات الأولوية (In-Flight Work Resolution &amp; Stabilization):**
+     - جرد فوري لأي مهام أو أوامر ذات أولوية قصوى قيد التنفيذ قبل اتخاذ قرار التصفير.
+     - إذا كانت المهمة قريبة من الإنجاز: يتم إكمالها فوراً وبناء الكود وفحصه برمجياً واعتماده بعمل `git commit` نظيف ومحكم.
+     - إذا كانت المهمة كبيرة وتحتاج جولات إضافية: يتم تثبيت الكود عند محطة استقرار آمنة (Compilable Milestone) وعزل أي تجارب ناقصة لضمان بقاء الفرع أخضر 100% وخالياً من أي أخطاء كسر بناء.
+  2. **المرحلة الثانية: تجميد الحالة وتوثيق سياق المشروع وحراسة الذاكرة (State Freeze &amp; Memory Quarantine):**
+     - مطابقة وتحديث ملف الحالة `fleet_orders/CURRENT_STATE.md` (أو `PROJECT_CONTEXT.md`) وتحديث بند "الخطوة التالية المحددة" (The One Thing To Do Next).
+     - فحص ومطابقة `git status --short --branch` للتأكد من خلو شجرة العمل من أي تعديلات تائهة أو غير معتمدة.
+     - تسجيل أي اكتشافات أو ملاحظات عتادية أو فخاخ برمجية جديدة في `MEMORY_STORE.md`.
+  3. **المرحلة الثالثة: تحديد القرارات وتوليد برومبت الاستئناف الفوري (Resume Prompt &amp; Green Light):**
+     - صياغة ملخص تسليم محكم يتضمن: ما تم إنجازه، آخر Commit معتمد، والخيارات المتاحة أمام المطور للجلسة القادمة.
+     - توليد برومبت استئناف دقيق (Ready to copy-paste) لنسخه ولصقه فور تنفيذ أمر التصفير:
+       `Read CLAUDE.md and fleet_orders/CURRENT_STATE.md. State where we are and present the choices for the next order.`
+     - منح الضوء الأخضر الصريح للمطور: تأكيد إمكانية تنفيذ أمر `/clear` أو `/compact` بأمان تام وبدون أي هدر للسياق.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>اسم الخطاف</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>المحفزات (الخطاف للنسخ)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>النموذج الأساسي والبديل</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>الوكلاء المسؤولون</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>الهدف الأساسي</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>الوصف والتفاصيل</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>26. خطاف إدارة وتحديث مكتبة الأوامر الذكية</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>أضف لمكتبة الأوامر, وثق في مكتبة الأوامر, أضف برومبت للإكسيل, تحديث مكتبة الأوامر, حفظ في مكتبة الأوامر, add prompt to library, curate prompt</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Gemini 3.8 Flash (High)` 
+ البديل: `Claude Sonnet 5`</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[prompt-engineer], [agent-optimizer], [code-architect]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>تحويل الأفكار والحلول البرمجية لبرومبتات مهندسة جاهزة للاستخدام، وإدراجها آلياً في التبويب المناسب داخل ملف "مكتبة الأوامر.xlsx" مع الحفاظ على التنسيق والخطوط وإبلاغ المستخدم بموقع ورقم الصف المضاف.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **الالتقاط والهندسة البرمجية للموجه (`[prompt-engineer]`):**
+     - استلام الفكرة، الميزة، أو الأمر البرمجي من سياق الجلسة الحالية.
+     - صياغته وهندسته كأمر معياري متكامل يتضمن:
+       - اسم الأمر بالعربية والإنجليزية مقروناً بإيموجي معبر (العمود B).
+       - الأمر البرمجي / الموجه الكامل (Command / Prompt) (العمود C).
+       - الوصف الدقيق، الهدف، وحالات الاستخدام المثلى (العمود D).
+  2. **التوجيه الذكي للتبويب المناسب (Smart Sheet Routing):**
+     - فحص كافة تبويبات ملف `G:\أرشيف_ونسخ_احتياطية\ملفات_مكررة_وعامة\AI\مكتبة الأوامر.xlsx`.
+     - توجيه الأمر تلقائياً للتبويب المتخصص:
+       - `CLI_Core.Claude`: أوامر الـ CLI، الأسطول، التصفير، والتحكم في المحركات.
+       - `Workflows_Pipelines.Claude`: مسارات العمل، CI/CD، البناء والتوزيع.
+       - `Gates_Hooks.Claude`: بوابات الجودة، الخطافات، والتدقيق المعماري.
+       - `Custom_Skills.Claude`: المهارات المخصصة، الوكلاء الفرعيون، وحزم الأدوات.
+       - `Config_Environments.Claude`: إعدادات البيئة، مسارات SDK، الذاكرة، و Gradle.
+       - `Construction_MCP_Suite`: أدوات الهندسة المدنية، جداول الكميات BOQ، والعقود.
+  3. **الإدراج البرمجي المحصن في الإكسيل (`prompt_library_curator.py` / `add-prompt`):**
+     - استدعاء أداة الأتمتة المدمجة `add-prompt`.
+     - حساب الرقم التسلسلي التالي (`No`) واكتشاف الصف النظيف القادم تلقائياً.
+     - تطبيق التنسيق الدقيق للخلايا (خط Segoe UI 10pt، خط Consolas للكود، محاذاة اليمين واليسار المناسبة، والحدود الرقيقة Thin Borders).
+     - معالجة قفل الملفات: في حال كان الإكسيل مفتوحاً لدى المستخدم، يتم الاعتماد تلقائياً على Excel COM Automation للكتابة الحية دون أخطاء PermissionError.
+  4. **إشعار المستخدم بالموقع الدقيق:**
+      - طباعة تقرير تأكيد فوري يتضمن: اسم الأمر، اسم التبويب (Sheet Name)، ورقم الصف الدقيق (Row Number) لسهولة الوصول إليه واستنساخه مستقبلاً.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>اسم الخطاف</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>المحفزات (الخطاف للنسخ)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>النموذج الأساسي والبديل</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>الوكلاء المسؤولون</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>الهدف الأساسي</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>الوصف والتفاصيل</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>27. خطاف الاستشارة الاستراتيجية لإدارة نافذة السياق</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>مستشار السياق, إدارة السياق, مستشار التوكنز, ترشيد السياق, فحص نافذة السياق, context advisor, manage context, agy context advice, قرارات السياق</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Gemini 3.8 Flash (High)` 
+ البديل: `Claude Sonnet 5`</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[prompt-engineer], [agent-optimizer], [code-architect]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>تحليل لحظي ودقيق لاستهلاك السياق والتوكنز في Antigravity IDE/agcli، تصنيف الجلسة ضمن 4 مناطق أمان (خضراء، صفراء، برتقالية، حمراء)، وتوجيه المطور للقرار المعماري الأنسب (استمرار، ترشيد، ضغط، أو تصفير استراتيجي وتسليم).</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **الاستعلام الآلي عن استهلاك التوكنز والسياق (`context_advisor.py` / `ag-context -a`):**
+     - قراءة التليمتري الحية من قاعدة بيانات الجلسة الحالية (`input_tokens`, `output_tokens`, `thinking_tokens`, `limit`, `velocity`).
+     - المعايرة على **النطاق الذهبي للإنتاجية القصوى والدقة (30,000 إلى 300,000 توكن)** لحماية النموذج من تشتت الانتباه.
+  2. **التشخيص وتحديد منطقة الأمان (Context Health Zone Diagnostic):**
+     - 🟢 **المنطقة الخضراء (&lt; 180k توكن | أقل من 60% من النطاق الذهبي):** أمان تام وانتباه كامل (100% Attention Fidelity)؛ الاستمرار في التطوير دون أي تدخل مع ترشيد القراءة.
+     - 🟡 **المنطقة الصفراء (180k إلى 240k توكن | 60% - 80%):** تنبيه مبكر واقتراب من حافة النطاق الذهبي؛ حظر قراءة الملفات الكاملة والاعتماد الحصري على التوقيعات (Signatures) وأجزاء الأسطر عبر `lean-ctx`.
+     - 🟠 **المنطقة البرتقالية (240k إلى 300k توكن | 80% - 100%):** منطقة التخطيط للتسليم والضغط؛ تثبيت الكود الحالي بعمل `git commit`، وتوثيق الدروس في `MEMORY_STORE.md`, والاستعداد للضغط أو التصفير.
+     - 🔴 **المنطقة الحمراء (&gt; 300k توكن | تجاوز سقف النطاق الذهبي):** خروج صريح من نطاق الدقة القصوى؛ خطر فقدان الانتباه والهلوسة، والتفعيل الفوري الإلزامي للخطاف 25 (التصفير الاستراتيجي وتسليم الجلسة) وتوليد برومبت الاستئناف ثم تنفيذ `/clear`.
+  3. **توليد القرار الاستراتيجي والأوامر الجاهزة:**
+     - تقديم ملخص فني موجز باللغة العربية بتنسيق RTL.
+     - تقديم الأمر التكليفي أو التنفيذي الجاهز للنسخ بنقرة واحدة وفقاً للمنطقة المحددة.
+  4. **حوكمة استدعاء الوكلاء الفرعيين وترشيد التوكنز (Subagent Budgeting &amp; Governance):**
+     - حظر إطلاق أسراب متزامنة (Swarms) واقتصار الاستدعاء على وكيل مفرد متسلسل بهدف محدد.
+     - إلزام الوكلاء الفرعيين ببروتوكول القراءة المتدرجة (`mode=signatures`) وتمرير مقاطع الأسطر المحددة فقط.
+     - منع تشغيل الوكلاء الفرعيين كلياً في المنطقة الحمراء (&gt; 300k) وإلزام التصفير الاستراتيجي أولاً.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>اسم الخطاف</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>المحفزات (الخطاف للنسخ)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>النموذج الأساسي والبديل</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>الوكلاء المسؤولون</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>الهدف الأساسي</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>الوصف والتفاصيل</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>28. خطاف ترحيل وتطهير أدوات المحرر والذكاء الاصطناعي</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>تطهير المحرر, نقل أدوات المحرر, ترحيل أدوات المحرر, تطهير المشروع, evacuate editor tools, clean workspace tooling, evacuate-tools</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Gemini 3.8 Flash (High)` 
+ البديل: `Claude Sonnet 5`</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[devops-deployer], [agent-optimizer], [code-architect]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>فحص ومزامنة أدوات المحرر في الإعدادات العالمية (~/.gemini/config)، ونقل كافة الأدلة والمستندات والسكربتات إلى المستودع المركزي (Claude+Antigravity) بعد التحقق التشفيري الإلزامي (SHA-256) قبل الحذف، وتنظيف مخلفات الذاكرة وحطام JVM لضمان نقاء بيئة المشاريع البرمجية.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **المزامنة والتحديث للسيستم العالمي (`C:\Users\Kt\.gemini\config\tools\`):**
+     - جرد أدوات المحرر في مجلد `tools/` بالمشروع ومقارنتها بالنسخ العالمية وتحديثها لضمان عدم ضياع أي ميزة جديدة.
+  2. **الترحيل والأرشفة المركزية (`F:\AI PROJECTS\Claude+Antigravity\`):**
+     - نقل أدلة المحرر (`*.docx`, `*.pdf`, `*.md`) إلى مجلد `docs/`، والمخططات إلى `assets/`، والسكربتات إلى `tools/`.
+  3. **التدقيق التشفيري الإلزامي قبل الحذف (SHA-256 Verification):**
+     - يُحظر حذف أي ملف محلي إلا بعد حساب بصمة SHA-256 للمصدر والوجهة والتأكد من التطابق التام 100%. وفي حال وجود نسخة أحدث في المركز، تُحفظ كنسخة أرشيفية.
+  4. **التطهير الآمن للمشروع المحلي (Clean Workspace Guarantee):**
+     - حذف الأدوات المنقولة، وإزالة مجلد `tools/` بعد فراغه، وتنظيف مخلفات JVM (`hs_err_*.log`, `replay_*.log`) وأقفال Word المؤقتة، واستعادة الشجرة النظيفة الخالية من أي Untracked files.
+&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -669,60 +3858,92 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="80" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>م</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>اسم الخطاف</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Prompt</t>
+          <t>المحفزات (الخطاف للنسخ)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Notes or description</t>
+          <t>النموذج الأساسي والبديل</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>الوكلاء المسؤولون</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>الهدف الأساسي</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>الوصف والتفاصيل</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>3. منهجية</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>`"منهجية"`, `"خطة عمل"`</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>الوكلاء المسؤولون: `methodology-writer`
-الوصف العام: كتابة منهجية إنجاز الأعمال
-الإجراءات التفصيلية:
-1. يقرأ مرجع المنهجيات من `references/منهجيات/`
-  2. يحدد نوع المنهجية المطلوبة (إنشاء / صيانة / توريدات)
-  3. يكتب المنهجية وفق الهيكل المرجعي
-  4. ينتج ملف DOCX بتنسيق RTL احترافي</t>
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2. خطاف هندسة السياق</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>سياق المشروع, هندسة السياق</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Claude Opus 4.6 (Thinking)`</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[prompt-engineer], [agent-optimizer]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>إنشاء وتحديث ملف `PROJECT_CONTEXT.md` لضمان التوجيه وتفادي الانحراف التقني.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **مراجعة القواعد واستيراد الذاكرة العالمية:** يقوم الوكيل `[prompt-engineer]` بمراجعة الدستور المحلي والعالمي (`AGENTS.md`) بدقة، واستيراد البيانات من ملفات **الذاكرة العالمية (Global Memory)** و **الأنماط العالمية (Global Patterns)** لضمان تطبيق الدروس العابرة للمشاريع.
+  2. **قراءة هيكل المشروع:** تحليل البنية والقرارات المعمارية الحالية للمشروع.
+  3. **توليد أو تحديث الملف:** كتابة أو تعديل ملف `PROJECT_CONTEXT.md` ليعكس التحديثات المعمارية والقرارات التقنية.
+  4. **التأكيد والمزامنة:** إعلام طاقم الوكلاء بالتحديثات المعتمدة لضمان التوافق.</t>
         </is>
       </c>
     </row>
@@ -737,60 +3958,92 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="80" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>م</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>اسم الخطاف</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Prompt</t>
+          <t>المحفزات (الخطاف للنسخ)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Notes or description</t>
+          <t>النموذج الأساسي والبديل</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>الوكلاء المسؤولون</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>الهدف الأساسي</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>الوصف والتفاصيل</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>4. جدول كميات</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>`"جدول كميات"`, `"مقايسة"`, `"BOQ"`</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>الوكلاء المسؤولون: `boq-analyst`
-الوصف العام: إنشاء جدول الكميات وتحليل الأسعار
-الإجراءات التفصيلية:
-1. يقرأ مرجع جداول الكميات من `references/جداول_كميات/`
-  2. يستخرج البنود من كراسة الشروط أو مدخلات المستخدم
-  3. يبني جدول الكميات مع الأسعار الإفرادية
-  4. يحسب الإجمالي + ضريبة القيمة المضافة 15%</t>
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>3. خطاف التخصيص والتصدير الذكي لطاقم المشروع</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>اعتمد سياق المشروع, تخصيص وكلاء المشروع, تصدير بيئة المشروع, تخصيص الوكلاء</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[code-architect], [agent-optimizer], [prompt-engineer]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>تحليل سياق المشروع وتصدير حزم الوكلاء محلياً مع التنظيف التلقائي (Pruning) وتوليد سكربت المزامنة.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **تحليل سياق المشروع المعتمد (`project_agent_tailor.py`):** فحص ملف `PROJECT_CONTEXT.md` واكتشاف حزم التقنيات المستخدمة (مثل: `android_compose`, `web`, `python_ai`, `construction_survey`).
+  2. **تصدير حزم الوكلاء والمهارات المطلوبة:** نسخ مهارات وبطاقات الوكلاء المتخصصين وحزمة النواة حصرياً إلى مجلد المشروع المحلي `.agents/`.
+  3. **التنظيف التلقائي الصارم للمهارات الفائضة (Pruning Engine):** مسح وحذف أي مهارات أو بطاقات وكلاء غير مستخدمة في المشروع المستهدف، لحماية نافذة السياق (Context Budget) من الهدر بنسبة 100%.
+  4. **توليد قالب المزامنة المحلي (`sync_local_agents.py`):** إنشاء سكربت خفيف داخل المشروع لتمكين المطور من تحديث طاقم المشروع بنقرة زر واحدة مستقبلاً دون المساس بخصوصية المشروع.</t>
         </is>
       </c>
     </row>
@@ -805,61 +4058,92 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="80" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>م</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>اسم الخطاف</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Prompt</t>
+          <t>المحفزات (الخطاف للنسخ)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Notes or description</t>
+          <t>النموذج الأساسي والبديل</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>الوكلاء المسؤولون</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>الهدف الأساسي</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>الوصف والتفاصيل</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>5. إدارة مخاطر</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>`"مخاطر"`, `"خطة طوارئ"`</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>الوكلاء المسؤولون: `risk-planner`
-الوصف العام: إعداد مصفوفة المخاطر
-الإجراءات التفصيلية:
-1. يحلل نوع المشروع وموقعه
-  2. يحدد المخاطر المحتملة (فنية، مالية، بيئية، تنظيمية)
-  3. يقيّم كل خطر (احتمالية × أثر)
-  4. يضع استراتيجيات الاستجابة
-  5. ينتج مصفوفة المخاطر وخطة الطوارئ DOCX</t>
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>4. خطاف الإشراف العام وتصحيح المسار</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>تصحيح مسار, تعديل البرومبت, خطأ بالخطاف, تصحيح خطاف</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[prompt-engineer], [agent-optimizer]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>تصحيح الخطافات الخاطئة والبرومبتات غير الاحترافية وتوجيهها للمسار الصحيح تلقائياً.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **الرصد التلقائي والإيقاف:** يقوم الوكيل الرئيسي بمراقبة المحادثة. عند استخدام المستخدم لمحفز "تصحيح مسار"، أو عند رصد دخول وكيل في دائرة مفرغة، يتم اعتراض العمل وإيقافه فوراً.
+  2. **التشريح الاستباقي الصارم (Prompt Autopsy &amp; Root-Cause Analysis):** يُمنع على `prompt-engineer` تقديم برومبت جديد مباشرة. يجب أولاً طباعة قسم `[ROOT-CAUSE ANALYSIS]` يشرح بوضوح سبب الانحراف السابق (هلوسة وكيل، غياب سياق، أو معمارية خاطئة).
+  3. **حماية السياق (Context Preservation):** تحديد المتطلبات أو الملفات التي كانت تنقص الوكيل السابق للعمل بشكل صحيح تحت قسم `[MISSING ARTIFACTS / INFO]`.
+  4. **إعادة الصياغة والتوجيه القاطع (Explicit Rerouting):** توليد التوجيه الهندسي الجديد تحت قسم `[RE-ENGINEERED PROMPT]` مقترناً بشكل صريح بالوكيل الفرعي المستهدف `[TARGET HOOK]` الذي سيستلم المهمة ليكملها بنظافة.</t>
         </is>
       </c>
     </row>
@@ -874,60 +4158,92 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="80" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>م</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>اسم الخطاف</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Prompt</t>
+          <t>المحفزات (الخطاف للنسخ)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Notes or description</t>
+          <t>النموذج الأساسي والبديل</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>الوكلاء المسؤولون</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>الهدف الأساسي</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>الوصف والتفاصيل</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>6. تنسيق وإخراج</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>`"تنسيق"`, `"PDF"`, `"إخراج نهائي"`</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>الوكلاء المسؤولون: `document-formatter`
-الوصف العام: التنسيق النهائي والتحويل
-الإجراءات التفصيلية:
-1. يستقبل الملفات الخام (DOCX/XLSX)
-  2. يطبق التنسيقات المعتمدة (خطوط، ألوان، شعارات)
-  3. يحوّل إلى PDF مع خطوط مدمجة
-  4. يتحقق من جودة المخرج النهائي</t>
+        <v>5</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>5. خطاف خط الإنتاج البرمجي</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>ابدأ ميزة, تطوير ميزة, اصنع ميزة, إصلاح ميزة</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Claude Opus 4.6 (Thinking)`</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[code-architect], [ui-ux-pro-max], [clean-code-guard], [test-guard]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>تنفيذ دورة التطوير الكاملة (المعمارية، الذكاء التصميمي، البرمجة، حراسة الكود النظيف، والفحص والاختبار).</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **التصميم الهيكلي والذكاء التصميمي (`code-architect` + `ui-ux-pro-max`):** تحديد المعمارية المناسبة، واستدعاء محرك الاستدلال التصميمي لتحديد نمط الواجهات (Style)، باليت الألوان الدلالية، والخطوط وقواعد سهولة الوصول بدقة قبل كتابة أي واجهة.
+  2. **التدقيق المعماري الصارم (Devil's Advocate Audit):** مراجعة الخطة وكشف الثغرات وحالات الحافة لمنع الآثار الجانبية.
+  3. **الكتابة البرمجية والتنفيذ:** كتابة الكود وبناء الواجهات وقواعد البيانات محلياً.
+  4. **المراجعة وضمان الجودة (`clean-code-guard` + `test-guard`):** فحص الكود للأمان، الأداء، والتوافق مع المعايير.</t>
         </is>
       </c>
     </row>
@@ -942,60 +4258,91 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="80" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>م</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>اسم الخطاف</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Prompt</t>
+          <t>المحفزات (الخطاف للنسخ)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Notes or description</t>
+          <t>النموذج الأساسي والبديل</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>الوكلاء المسؤولون</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>الهدف الأساسي</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>الوصف والتفاصيل</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>7. مطابقة</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>`"مراجعة كود"`, `"مطابقة"`, `"تدقيق"`</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>الوكلاء المسؤولون: `saudi-code-validator`
-الوصف العام: فحص الاشتراطات والمطابقة
-الإجراءات التفصيلية:
-1. يقرأ المستند المُنتَج
-  2. يفحصه مقابل اشتراطات الكود السعودي
-  3. يتحقق من معايير التقييم الفني للجهة المالكة
-  4. يصدر تقرير مطابقة (نجاح / ملاحظات تحتاج تعديل)</t>
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>6. خطاف التكامل الفني</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>ربط API, تكامل خارجي</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Gemini 3.7 Flash (High)` 
+ البديل: `Claude Sonnet 4.6 (Thinking)`</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[devops-deployer], [backend-architect]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>ربط وتكامل الخدمات الخارجية بعد مراجعة وثائقها الرسمية وتأمين المتغيرات.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **قراءة الوثائق:** يقرأ الوكيل `[devops-deployer]` وثائق الـ API الخارجية الرسمية المدخلة قبل البدء بالدمج.
+  2. **تحصين الانقطاع (API FAULT TOLERANCE CHECK):** بناء Interceptor لمعالجة انقطاع الشبكة وإعادة المحاولة وتأمين المفاتيح في متغيرات البيئة.
+  3. **توليد الـ Wrapper:** عزل منطق التكامل في كلاسات مغلفة منفصلة لتجنب تشتيت الكود الأساسي للمشروع.</t>
         </is>
       </c>
     </row>
@@ -1010,61 +4357,90 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="80" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>م</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>اسم الخطاف</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Prompt</t>
+          <t>المحفزات (الخطاف للنسخ)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Notes or description</t>
+          <t>النموذج الأساسي والبديل</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>الوكلاء المسؤولون</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>الهدف الأساسي</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>الوصف والتفاصيل</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>8. ضبط مرجع</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>`"ضبط مرجع"`, `"أضف مرجع"`, `"هذا الملف نموذج"`</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>الوكلاء المسؤولون: `reference-calibrator`
-الوصف العام: تحليل ملف نموذجي وفهرسته
-الإجراءات التفصيلية:
-1. يستقبل مسار الملف النموذجي من المستخدم
-  2. يحلل الملف ويستخرج الهيكل والأنماط
-  3. ينشئ بطاقة مرجعية في `cards/`
-  4. ينسخ الملف إلى المجلد الفرعي المناسب
-  5. يحدّث الفهرس `index.md`</t>
+        <v>7</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>7. خطاف تدقيق الصيانة</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>تدقيق صيانة, مراجعة DRY, كود نظيف</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Gemini 3.7 Flash (High)`</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[code-reviewer-quality], [clean-code-guard], [performance-optimizer]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>مراجعة الكود البرمجي بانتظام لمنع التكرار وتراكم الديون التقنية وتطبيق معايير الكود النظيف.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **فحص الكود النظيف والمكرر:** استدعاء الوكيل `[code-reviewer-quality]` و `[clean-code-guard]` لمسح الملفات والتحقق من عدم وجود دوال مكررة (تطبيق DRY/KISS/YAGNI).
+  2. **فحص Recomposition والأداء:** قياس كفاءة الرسم وإعاقات الأداء في Compose بواسطة `[performance-optimizer]`.</t>
         </is>
       </c>
     </row>
@@ -1079,61 +4455,90 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="80" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>م</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>اسم الخطاف</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Prompt</t>
+          <t>المحفزات (الخطاف للنسخ)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Notes or description</t>
+          <t>النموذج الأساسي والبديل</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>الوكلاء المسؤولون</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>الهدف الأساسي</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>الوصف والتفاصيل</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>9. تنظيم الأرشيف</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>`"ترتيب ملفات"`, `"تنظيم مجلد"`, `"monorepo"`, `"تنظيم الأرشيف"`</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>الوكلاء المسؤولون: `monorepo-architect`
-الوصف العام: تحليل هياكل المجلدات وتنظيمها برمجياً بأمان
-الإجراءات التفصيلية:
-1. يقوم بجرد وتحليل كافة الملفات والمجلدات في المسار المستهدف.
-  2. يصنفها إلى مجموعات منطقية (إدارية، مالية، مشاريع، تصاميم).
-  3. يعرض بنية مجلدات مقترحة (Folder Tree) وجدول توزيع تفصيلي للمستخدم للتأكيد.
-  4. ينتظر موافقة المستخدم الصريحة قبل أي عملية نقل.
-  5. ينشئ سكريبت بايثون آمن لنقل وتوزيع الملفات برمجياً مع تجنب الملفات النشطة والمجلدات المحمية.</t>
+        <v>8</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>8. خطاف الفحص الأمني</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>فحص أمني, مراجعة أمان</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Sonnet 4.6 (Thinking)` 
+ البديل: `Claude Opus 4.6 (Thinking)`</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[security-auditor], [code-reviewer-quality]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>مراجعة ثغرات الأمان والتحقق من صحة المدخلات وتشفير البيانات وتأمين الوصول.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **مصفوفة الثغرات الصارمة (VULNERABILITY MATRIX):** مسح إجباري لـ AndroidManifest والمكونات المكشوفة وتسريب البيانات.
+  2. **التحقق من صحة المدخلات وتشفير البيانات:** فحص تشفير البيانات الحساسة والجلسات وتأمين الوصول محلياً وسحابياً.</t>
         </is>
       </c>
     </row>

--- a/HOOKS_GUIDE.xlsx
+++ b/HOOKS_GUIDE.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. خطاف خط الإنتاج البرمجي" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. خطاف التكامل الفني" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7. خطاف تدقيق الصيانة" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8. خطاف الفحص الأمني" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8. خطاف الفحص الأمني ودرع Vi" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9. خطاف مراجعة وتحديث المكتب" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10. خطاف الفحص والاختبار التل" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11. خطاف معالجة الأخطاء والأع" sheetId="12" state="visible" r:id="rId12"/>
@@ -36,6 +36,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26. خطاف إدارة وتحديث مكتبة ا" sheetId="27" state="visible" r:id="rId27"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="27. خطاف الاستشارة الاستراتيج" sheetId="28" state="visible" r:id="rId28"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="28. خطاف ترحيل وتطهير أدوات ا" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="29. خطاف ترقية ومعايرة مصفوفة" sheetId="30" state="visible" r:id="rId30"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -477,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -808,12 +809,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>8. خطاف الفحص الأمني</t>
+          <t>8. خطاف الفحص الأمني ودرع Vibe Coding</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>فحص أمني, مراجعة أمان</t>
+          <t>فحص أمني, مراجعة أمان, درع الأمان, vibe security, فحص الثغرات</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -824,19 +825,26 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>[security-auditor], [code-reviewer-quality]</t>
+          <t>[security-auditor], [vibe-coding-security-shield], [code-reviewer-quality]</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>مراجعة ثغرات الأمان والتحقق من صحة المدخلات وتشفير البيانات وتأمين الوصول.</t>
+          <t>مراجعة ثغرات الأمان عبر الدرع السداسي (Semgrep, Gitleaks, Trivy, ZAP, Checkov, Renovate) وتأمين الأكواد والمفاتيح والتبعيات قبل الإنتاج.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  1. **مصفوفة الثغرات الصارمة (VULNERABILITY MATRIX):** مسح إجباري لـ AndroidManifest والمكونات المكشوفة وتسريب البيانات.
-  2. **التحقق من صحة المدخلات وتشفير البيانات:** فحص تشفير البيانات الحساسة والجلسات وتأمين الوصول محلياً وسحابياً.</t>
+  1. **تفعيل الركائز الست لدرع الأمان (`vibe-coding-security-shield`):**
+     - **Semgrep (SAST):** فحص المنطق والأكواد المولدة بالذكاء الاصطناعي لمنع الحقن (Injection) والثغرات الإنشائية.
+     - **Gitleaks:** التحقق الصارم من انعدام تسريب المفاتيح ورموز الوصول السرية في الـ Staging وتاريخ الـ Git.
+     - **Trivy:** فحص التبعيات وصور Docker وكشف ثغرات CVEs وتوليد الـ SBOM.
+     - **OWASP ZAP (DAST):** الفحص الديناميكي للواجهات ونقاط الـ API بعد تشغيل التطبيق في بيئة الاختبار.
+     - **Checkov:** فحص أخطاء البنية التحتية والـ Misconfigurations في Dockerfile و Terraform.
+     - **Renovate:** أتمتة تحديثات التبعيات وسد الثغرات الأمنية دورياً عبر الـ PRs.
+  2. **مصفوفة الثغرات الصارمة (VULNERABILITY MATRIX):** مسح إجباري لـ AndroidManifest والمكونات المكشوفة وتسريب البيانات.
+  3. **التحقق من صحة المدخلات وتشفير البيانات:** فحص تشفير البيانات الحساسة والجلسات وتأمين الوصول محلياً وسحابياً.</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1242,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>تدقيق الجودة, فحص الكود النظيف, حراسة الجودة, clean code audit</t>
+          <t>تدقيق الجودة, فحص الكود النظيف, حراسة الجودة, clean code audit, wp guard, woo guard, debate review</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1245,18 +1253,26 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>[code-reviewer-quality], [clean-code-guard], [test-guard], [docs-guard]</t>
+          <t>[code-reviewer-quality], [clean-code-guard], [test-guard], [docs-guard], [wp-guard], [woo-guard], [debate-review]</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>تفعيل بوابات الحماية الثلاث لفحص الكود النظيف، سلامة الاختبارات، ومطابقة التوثيق.</t>
+          <t>تفعيل بوابات الحماية الشاملة للكود النظيف، سلامة الاختبارات، مطابقة التوثيق، حراسة ووردبريس وووكومرس، والمناظرة التنافسية للـ PRs.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  1. **تفعيل بوابات الحماية الثلاث:** فحص الكود النظيف (`clean-code-guard`)، سلامة الاختبارات (`test-guard`)، ومطابقة التوثيق (`docs-guard`).</t>
+  1. **بوابات الحماية العامة للنواة (Core Guard Gates):**
+     - **الكود النظيف (`clean-code-guard`):** فحص الديف ومطابقة القواعد الـ 24 لمنع بلع الأخطاء والتعقيد الزائد والدوال الوهمية مع المراجع التخصصية.
+     - **سلامة الاختبارات (`test-guard`):** حراسة كود الاختبارات ومنع إساءة الـ Mocks وتأكيد فحص السلوك الحقيقي عبر مراجع pytest و jest و llm-app-testing.
+     - **مطابقة التوثيق (`docs-guard`):** منع الهلوسة في أسماء الدوال ومطابقة ملفات التوثيق و README مع الكود الحي.
+  2. **بوابات حراسة المنصات والتجارة الإلكترونية (Platform &amp; E-Commerce Guards):**
+     - **حراسة ووردبريس (`wp-guard`):** فحص الإضافات والقوالب، فرض التعقيم والهروب (Sanitization &amp; Escaping)، الـ Nonces، وصلاحيات المستخدم، وتأمين الاستعلامات.
+     - **حراسة ووكومرس (`woo-guard`):** حراسة العمليات المالية، منع الالتفاف على كائنات HPOS CRUD، وتأمين الـ Checkout ومطابقة معايير الدفع.
+  3. **المناظرة البرمجية التنافسية للـ Pull Requests (`debate-review`):**
+     - تشغيل مناظرة ثنائية بين نموذجين مختلفين (Main Reviewer vs Debate Reviewer) لفحص التفرعات والـ PRs وإصدار تعليقات سطرية دقيقة P0/P1/P2 خالية من النقاط العمياء.</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1287,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>استكشف المورد, حلل المستودع, تكامل المورد, scout resource, integrate repo</t>
+          <t>استكشف المورد, حلل المستودع, تكامل المورد, scout resource, integrate repo, duckai bridge, تحديث صفحة HTML, update html</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1282,18 +1298,29 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>[resource-scout-integrator], [ui-ux-pro-max], [github-talent-scout], [skill-forge-builder], [agent-optimizer], [frontend-design-builder], [git-github-manager], [powershell-runtime-pro]</t>
+          <t>[resource-scout-integrator], [duckai-research-bridge], [graft], [ui-ux-pro-max], [github-talent-scout], [skill-forge-builder], [agent-optimizer], [frontend-design-builder], [git-github-manager]</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>تحليل المستودعات الخارجية واستيراد المهارات وتعميمها وتحديث الخطافات والإكسيل وتطبيق مكتبة الأوامر ودليل hooks_user_guide.md ومزامنة المنظومة.</t>
+          <t>تحليل المستودعات الخارجية واستيراد وتعميم المهارات، وتحديث الخطافات والإكسيل والتحديث الآلي لصفحات HTML لمكتبة الأوامر التفاعلية ومزامنة المنظومة.</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  1. **استيراد وتعميم المهارات العالمية:** تحليل المستودعات الخارجية وبناء مهارات `SKILL.md` ونشرها عالمياً وتحديث المنظومة.</t>
+  1. **استيراد وتعميم المهارات العالمية:** تحليل المستودعات الخارجية وبناء مهارات `SKILL.md` ونشرها عالمياً وتحديث المنظومة.
+  2. **الحزم والموارد المعتمدة والمدمجة:**
+     - **حزمة بوابات الحراسة الشاملة (`guard-skills`):** تضم `clean-code-guard`, `test-guard`, `docs-guard`, `wp-guard`, `woo-guard` بكامل مراجعها التخصصية وموجهات OpenAI/Claude.
+     - **حزمة المراجعة التنافسية ومتابعة الـ PRs (`review-skills`):** تضم `debate-review` للمناظرة الثنائية المستقلة و `babysit-pr` للمتابعة الدورية الآلية وحل الملاحظات حتى الوصول لبوابة الدمج.
+     - **درع Vibe Coding السداسي (`vibe-coding-security-shield`):** حزم فحص Semgrep, Gitleaks, Trivy, OWASP ZAP, Checkov, Renovate لحماية الأكواد المولدة بالذكاء الاصطناعي.
+     - **مستشار هورموزي لنمو الأعمال (`hormozi-growth-advisor`):** أطر $100M Offers، معادلة القيمة، مصفوفة التوسع عبر 10 مراحل، والـ 12 Playbook.
+     - **نظام ThreeUI ثلاثي الأبعاد (`threeui-design-system`):** واجهات الويب ثلاثية الأبعاد، إضاءات الشيدر المتوهجة، ومكونات الـ 3D التفاعلية مع منع تسريب الذاكرة.
+     - **محرك سياق وخريطة الأكواد المعرفية Graft (`graft`):** بناء خرائط معرفية محلية ومستدامة عبر Tree-sitter AST لتقليل استهلاك التوكنز بنسبة 42% واستدعاءات الأدوات بنسبة 46% وتسريع استجابة Claude Code والأسطول بنسبة 60% وزيادة دقة الحلول +12 نقطة.
+     - **جسر أبحاث الذكاء الاصطناعي المجاني Duck.ai (`duckai-research-bridge`):** ربط أبحاث الويب ونماذج الاستدلال الخفيفة والمجانية (GPT-4o-mini, Claude 3 Haiku, Llama 3.3) للبحث الاستكشافي، واجهات الـ Dev/Staging لعملاء n8n و FastMCP، وحماية كوتا النماذج التجارية المدفوعة لوكالة Autovem.
+  3. **التحديث التلقائي الشامل لصفحة مكتبة الأوامر HTML (Smart Prompt Library Web View Sync):**
+     - عند استكشاف، اعتماد، أو تعديل أي خطافات جديدة في المنظومة، يُلزم الخطاف بتشغيل محرك تحديث صفحة الـ HTML (`python update_html.py`) فوراً وبشكل تلقائي.
+     - يقوم المحرك بتحليل `HOOKS_GUIDE.md` وحقن بيانات الخطافات المعتمدة (الرقم، الاسم، المحفزات، الأهداف، مستويات النماذج، الوكلاء المسؤولون، والتفاصيل الكاملة) مباشرة داخل مصفوفة `libraryData` في كافة صفحات تطبيق الويب التفاعلي لمكتبة الأوامر الذكية (`03_Dynamic_Prompt_Library/index.html`)، مع استدعاء `convert_hooks_to_sheets.py` لتحديث مصنف `HOOKS_GUIDE.xlsx`، وتوثيق الأوامر المهندسة في `مكتبة الأوامر.xlsx`.</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1388,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>[fleet-orchestrator], [code-architect], [agent-optimizer], [persistent-memory-engine]</t>
+          <t>[fleet-orchestrator], [graft], [code-architect], [agent-optimizer], [persistent-memory-engine]</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1620,7 +1647,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>[prompt-engineer], [agent-optimizer], [code-architect]</t>
+          <t>[context-governance], [graft], [prompt-engineer], [agent-optimizer], [code-architect]</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1689,7 +1716,59 @@
   3. **التدقيق التشفيري الإلزامي قبل الحذف (SHA-256 Verification):**
      - يُحظر حذف أي ملف محلي إلا بعد حساب بصمة SHA-256 للمصدر والوجهة والتأكد من التطابق التام 100%. وفي حال وجود نسخة أحدث في المركز، تُحفظ كنسخة أرشيفية.
   4. **التطهير الآمن للمشروع المحلي (Clean Workspace Guarantee):**
-     - حذف الأدوات المنقولة، وإزالة مجلد `tools/` بعد فراغه، وتنظيف مخلفات JVM (`hs_err_*.log`, `replay_*.log`) وأقفال Word المؤقتة، واستعادة الشجرة النظيفة الخالية من أي Untracked files.
+     - حذف الأدوات المنقولة، وإزالة مجلد `tools/` بعد فراغه، وتنظيف مخلفات JVM (`hs_err_*.log`, `replay_*.log`) وأقفال Word المؤقتة، واستعادة الشجرة النظيفة الخالية من أي Untracked files.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>29. خطاف ترقية ومعايرة مصفوفة نماذج أسطول الـ CLIs</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>تحديث نماذج الأسطول, ترقية نماذج الأسطول, معايرة نماذج الأسطول, ترقية النماذج, تحديث مصفوفة النماذج, upgrade fleet models, calibrate fleet models, fleet model update, update fleet models</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Opus 5.5 / Opus Max (Thinking)` 
+ البديل: `Gemini 3.8 Flash (High)`</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>[fleet-orchestrator], [agent-optimizer], [code-architect], [prompt-engineer], [persistent-memory-engine]</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>ترقية ومعايرة مصفوفة نماذج أسطول الوكلاء المتعدد لاعتماد أحدث أجيال الذكاء الاصطناعي (Claude Opus 5.5 Max و Sonnet 5.5 و Gemini 3.8 Flash High و GLM 5.3 Flash و Codex GPT-5.6 Soul)، وتحديث قيود [C-11] و [C-21] و [C-38]، وتحديث ملفات fleet_config.json وقوالب التفويض، وتطبيق الويب التفاعلي ومكتبة الأوامر.</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **المعايرة والترقية الشاملة لمصفوفة النماذج (Model Matrix Calibration):**
+     - ترقية نموذج القيادة المعمارية والفحص الحصري للاختبارات إلى: `Claude Opus 5.5 / Opus Max (Thinking)`.
+     - ترقية نموذج التطوير البرمجي اليومي وصناعة الميزات إلى: `Claude Sonnet 5.5`.
+     - تثبيت وتأكيد نماذج الطرفية وترشيد الكوتا: `OpenCode CLI` بنموذجي `GLM 5.3 Flash` و `Meta Muse Spark 1.3`.
+     - تثبيت منفذ واجهات Antigravity CLI / IDE: `Gemini 3.8 Flash (High Reasoning)`.
+     - تثبيت متخصص الخوارزميات والمعالجة العميقة: `Codex CLI (GPT-5.6 Soul)`.
+  2. **تحديث القيود التقنية الإلزامية (Invariants Update):**
+     - تحديث بنود [C-11] و [C-21] و [C-38] في ملف سياق الحقن الإلزامي `ACTIVE_CONTEXT_INJECTION.md`.
+  3. **المزامنة البرمجية لملفات تهيئة الأسطول (`fleet_config.json`):**
+     - فحص وتحديث حقول `active_model` في كافة ملفات `fleet_config.json` عبر المشاريع لاعتماد الجيل 5.5.
+  4. **تحديث تطبيق الويب التفاعلي والإكسيل ومكتبة الأوامر:**
+     - استدعاء `update_html.py` لتحديث مصفوفة بيانات `03_Dynamic_Prompt_Library/index.html` (29 خطافاً).
+     - استدعاء `convert_hooks_to_sheets.py` لتحديث مصنف `HOOKS_GUIDE.xlsx`.
+     - إدراج الأمر الموجه في مصنف `مكتبة الأوامر.xlsx` تحت تبويب `CLI_Core.Claude`.
+  5. **توثيق الذاكرة المستدامة (Memory Invariant):**
+     - تسجيل قرار ترقية المعمارية (ADR) في `MEMORY_STORE.md` محلياً وعالمياً.
 &lt;/div&gt;</t>
         </is>
       </c>
@@ -2847,7 +2926,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>تدقيق الجودة, فحص الكود النظيف, حراسة الجودة, clean code audit</t>
+          <t>تدقيق الجودة, فحص الكود النظيف, حراسة الجودة, clean code audit, wp guard, woo guard, debate review</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -2858,18 +2937,26 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>[code-reviewer-quality], [clean-code-guard], [test-guard], [docs-guard]</t>
+          <t>[code-reviewer-quality], [clean-code-guard], [test-guard], [docs-guard], [wp-guard], [woo-guard], [debate-review]</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>تفعيل بوابات الحماية الثلاث لفحص الكود النظيف، سلامة الاختبارات، ومطابقة التوثيق.</t>
+          <t>تفعيل بوابات الحماية الشاملة للكود النظيف، سلامة الاختبارات، مطابقة التوثيق، حراسة ووردبريس وووكومرس، والمناظرة التنافسية للـ PRs.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  1. **تفعيل بوابات الحماية الثلاث:** فحص الكود النظيف (`clean-code-guard`)، سلامة الاختبارات (`test-guard`)، ومطابقة التوثيق (`docs-guard`).</t>
+  1. **بوابات الحماية العامة للنواة (Core Guard Gates):**
+     - **الكود النظيف (`clean-code-guard`):** فحص الديف ومطابقة القواعد الـ 24 لمنع بلع الأخطاء والتعقيد الزائد والدوال الوهمية مع المراجع التخصصية.
+     - **سلامة الاختبارات (`test-guard`):** حراسة كود الاختبارات ومنع إساءة الـ Mocks وتأكيد فحص السلوك الحقيقي عبر مراجع pytest و jest و llm-app-testing.
+     - **مطابقة التوثيق (`docs-guard`):** منع الهلوسة في أسماء الدوال ومطابقة ملفات التوثيق و README مع الكود الحي.
+  2. **بوابات حراسة المنصات والتجارة الإلكترونية (Platform &amp; E-Commerce Guards):**
+     - **حراسة ووردبريس (`wp-guard`):** فحص الإضافات والقوالب، فرض التعقيم والهروب (Sanitization &amp; Escaping)، الـ Nonces، وصلاحيات المستخدم، وتأمين الاستعلامات.
+     - **حراسة ووكومرس (`woo-guard`):** حراسة العمليات المالية، منع الالتفاف على كائنات HPOS CRUD، وتأمين الـ Checkout ومطابقة معايير الدفع.
+  3. **المناظرة البرمجية التنافسية للـ Pull Requests (`debate-review`):**
+     - تشغيل مناظرة ثنائية بين نموذجين مختلفين (Main Reviewer vs Debate Reviewer) لفحص التفرعات والـ PRs وإصدار تعليقات سطرية دقيقة P0/P1/P2 خالية من النقاط العمياء.</t>
         </is>
       </c>
     </row>
@@ -2944,7 +3031,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>استكشف المورد, حلل المستودع, تكامل المورد, scout resource, integrate repo</t>
+          <t>استكشف المورد, حلل المستودع, تكامل المورد, scout resource, integrate repo, duckai bridge, تحديث صفحة HTML, update html</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -2955,18 +3042,29 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>[resource-scout-integrator], [ui-ux-pro-max], [github-talent-scout], [skill-forge-builder], [agent-optimizer], [frontend-design-builder], [git-github-manager], [powershell-runtime-pro]</t>
+          <t>[resource-scout-integrator], [duckai-research-bridge], [graft], [ui-ux-pro-max], [github-talent-scout], [skill-forge-builder], [agent-optimizer], [frontend-design-builder], [git-github-manager]</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>تحليل المستودعات الخارجية واستيراد المهارات وتعميمها وتحديث الخطافات والإكسيل وتطبيق مكتبة الأوامر ودليل hooks_user_guide.md ومزامنة المنظومة.</t>
+          <t>تحليل المستودعات الخارجية واستيراد وتعميم المهارات، وتحديث الخطافات والإكسيل والتحديث الآلي لصفحات HTML لمكتبة الأوامر التفاعلية ومزامنة المنظومة.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  1. **استيراد وتعميم المهارات العالمية:** تحليل المستودعات الخارجية وبناء مهارات `SKILL.md` ونشرها عالمياً وتحديث المنظومة.</t>
+  1. **استيراد وتعميم المهارات العالمية:** تحليل المستودعات الخارجية وبناء مهارات `SKILL.md` ونشرها عالمياً وتحديث المنظومة.
+  2. **الحزم والموارد المعتمدة والمدمجة:**
+     - **حزمة بوابات الحراسة الشاملة (`guard-skills`):** تضم `clean-code-guard`, `test-guard`, `docs-guard`, `wp-guard`, `woo-guard` بكامل مراجعها التخصصية وموجهات OpenAI/Claude.
+     - **حزمة المراجعة التنافسية ومتابعة الـ PRs (`review-skills`):** تضم `debate-review` للمناظرة الثنائية المستقلة و `babysit-pr` للمتابعة الدورية الآلية وحل الملاحظات حتى الوصول لبوابة الدمج.
+     - **درع Vibe Coding السداسي (`vibe-coding-security-shield`):** حزم فحص Semgrep, Gitleaks, Trivy, OWASP ZAP, Checkov, Renovate لحماية الأكواد المولدة بالذكاء الاصطناعي.
+     - **مستشار هورموزي لنمو الأعمال (`hormozi-growth-advisor`):** أطر $100M Offers، معادلة القيمة، مصفوفة التوسع عبر 10 مراحل، والـ 12 Playbook.
+     - **نظام ThreeUI ثلاثي الأبعاد (`threeui-design-system`):** واجهات الويب ثلاثية الأبعاد، إضاءات الشيدر المتوهجة، ومكونات الـ 3D التفاعلية مع منع تسريب الذاكرة.
+     - **محرك سياق وخريطة الأكواد المعرفية Graft (`graft`):** بناء خرائط معرفية محلية ومستدامة عبر Tree-sitter AST لتقليل استهلاك التوكنز بنسبة 42% واستدعاءات الأدوات بنسبة 46% وتسريع استجابة Claude Code والأسطول بنسبة 60% وزيادة دقة الحلول +12 نقطة.
+     - **جسر أبحاث الذكاء الاصطناعي المجاني Duck.ai (`duckai-research-bridge`):** ربط أبحاث الويب ونماذج الاستدلال الخفيفة والمجانية (GPT-4o-mini, Claude 3 Haiku, Llama 3.3) للبحث الاستكشافي، واجهات الـ Dev/Staging لعملاء n8n و FastMCP، وحماية كوتا النماذج التجارية المدفوعة لوكالة Autovem.
+  3. **التحديث التلقائي الشامل لصفحة مكتبة الأوامر HTML (Smart Prompt Library Web View Sync):**
+     - عند استكشاف، اعتماد، أو تعديل أي خطافات جديدة في المنظومة، يُلزم الخطاف بتشغيل محرك تحديث صفحة الـ HTML (`python update_html.py`) فوراً وبشكل تلقائي.
+     - يقوم المحرك بتحليل `HOOKS_GUIDE.md` وحقن بيانات الخطافات المعتمدة (الرقم، الاسم، المحفزات، الأهداف، مستويات النماذج، الوكلاء المسؤولون، والتفاصيل الكاملة) مباشرة داخل مصفوفة `libraryData` في كافة صفحات تطبيق الويب التفاعلي لمكتبة الأوامر الذكية (`03_Dynamic_Prompt_Library/index.html`)، مع استدعاء `convert_hooks_to_sheets.py` لتحديث مصنف `HOOKS_GUIDE.xlsx`، وتوثيق الأوامر المهندسة في `مكتبة الأوامر.xlsx`.</t>
         </is>
       </c>
     </row>
@@ -3154,7 +3252,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>[fleet-orchestrator], [code-architect], [agent-optimizer], [persistent-memory-engine]</t>
+          <t>[fleet-orchestrator], [graft], [code-architect], [agent-optimizer], [persistent-memory-engine]</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -3713,7 +3811,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>[prompt-engineer], [agent-optimizer], [code-architect]</t>
+          <t>[context-governance], [graft], [prompt-engineer], [agent-optimizer], [code-architect]</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -3842,8 +3940,7 @@
   3. **التدقيق التشفيري الإلزامي قبل الحذف (SHA-256 Verification):**
      - يُحظر حذف أي ملف محلي إلا بعد حساب بصمة SHA-256 للمصدر والوجهة والتأكد من التطابق التام 100%. وفي حال وجود نسخة أحدث في المركز، تُحفظ كنسخة أرشيفية.
   4. **التطهير الآمن للمشروع المحلي (Clean Workspace Guarantee):**
-     - حذف الأدوات المنقولة، وإزالة مجلد `tools/` بعد فراغه، وتنظيف مخلفات JVM (`hs_err_*.log`, `replay_*.log`) وأقفال Word المؤقتة، واستعادة الشجرة النظيفة الخالية من أي Untracked files.
-&lt;/div&gt;</t>
+     - حذف الأدوات المنقولة، وإزالة مجلد `tools/` بعد فراغه، وتنظيف مخلفات JVM (`hs_err_*.log`, `replay_*.log`) وأقفال Word المؤقتة، واستعادة الشجرة النظيفة الخالية من أي Untracked files.</t>
         </is>
       </c>
     </row>
@@ -3952,6 +4049,119 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>اسم الخطاف</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>المحفزات (الخطاف للنسخ)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>النموذج الأساسي والبديل</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>الوكلاء المسؤولون</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>الهدف الأساسي</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>الوصف والتفاصيل</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>29. خطاف ترقية ومعايرة مصفوفة نماذج أسطول الـ CLIs</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>تحديث نماذج الأسطول, ترقية نماذج الأسطول, معايرة نماذج الأسطول, ترقية النماذج, تحديث مصفوفة النماذج, upgrade fleet models, calibrate fleet models, fleet model update, update fleet models</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Opus 5.5 / Opus Max (Thinking)` 
+ البديل: `Gemini 3.8 Flash (High)`</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[fleet-orchestrator], [agent-optimizer], [code-architect], [prompt-engineer], [persistent-memory-engine]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>ترقية ومعايرة مصفوفة نماذج أسطول الوكلاء المتعدد لاعتماد أحدث أجيال الذكاء الاصطناعي (Claude Opus 5.5 Max و Sonnet 5.5 و Gemini 3.8 Flash High و GLM 5.3 Flash و Codex GPT-5.6 Soul)، وتحديث قيود [C-11] و [C-21] و [C-38]، وتحديث ملفات fleet_config.json وقوالب التفويض، وتطبيق الويب التفاعلي ومكتبة الأوامر.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات:**
+  1. **المعايرة والترقية الشاملة لمصفوفة النماذج (Model Matrix Calibration):**
+     - ترقية نموذج القيادة المعمارية والفحص الحصري للاختبارات إلى: `Claude Opus 5.5 / Opus Max (Thinking)`.
+     - ترقية نموذج التطوير البرمجي اليومي وصناعة الميزات إلى: `Claude Sonnet 5.5`.
+     - تثبيت وتأكيد نماذج الطرفية وترشيد الكوتا: `OpenCode CLI` بنموذجي `GLM 5.3 Flash` و `Meta Muse Spark 1.3`.
+     - تثبيت منفذ واجهات Antigravity CLI / IDE: `Gemini 3.8 Flash (High Reasoning)`.
+     - تثبيت متخصص الخوارزميات والمعالجة العميقة: `Codex CLI (GPT-5.6 Soul)`.
+  2. **تحديث القيود التقنية الإلزامية (Invariants Update):**
+     - تحديث بنود [C-11] و [C-21] و [C-38] في ملف سياق الحقن الإلزامي `ACTIVE_CONTEXT_INJECTION.md`.
+  3. **المزامنة البرمجية لملفات تهيئة الأسطول (`fleet_config.json`):**
+     - فحص وتحديث حقول `active_model` في كافة ملفات `fleet_config.json` عبر المشاريع لاعتماد الجيل 5.5.
+  4. **تحديث تطبيق الويب التفاعلي والإكسيل ومكتبة الأوامر:**
+     - استدعاء `update_html.py` لتحديث مصفوفة بيانات `03_Dynamic_Prompt_Library/index.html` (29 خطافاً).
+     - استدعاء `convert_hooks_to_sheets.py` لتحديث مصنف `HOOKS_GUIDE.xlsx`.
+     - إدراج الأمر الموجه في مصنف `مكتبة الأوامر.xlsx` تحت تبويب `CLI_Core.Claude`.
+  5. **توثيق الذاكرة المستدامة (Memory Invariant):**
+     - تسجيل قرار ترقية المعمارية (ADR) في `MEMORY_STORE.md` محلياً وعالمياً.
+&lt;/div&gt;</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -4510,12 +4720,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>8. خطاف الفحص الأمني</t>
+          <t>8. خطاف الفحص الأمني ودرع Vibe Coding</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>فحص أمني, مراجعة أمان</t>
+          <t>فحص أمني, مراجعة أمان, درع الأمان, vibe security, فحص الثغرات</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -4526,19 +4736,26 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>[security-auditor], [code-reviewer-quality]</t>
+          <t>[security-auditor], [vibe-coding-security-shield], [code-reviewer-quality]</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>مراجعة ثغرات الأمان والتحقق من صحة المدخلات وتشفير البيانات وتأمين الوصول.</t>
+          <t>مراجعة ثغرات الأمان عبر الدرع السداسي (Semgrep, Gitleaks, Trivy, ZAP, Checkov, Renovate) وتأمين الأكواد والمفاتيح والتبعيات قبل الإنتاج.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>* **طريقة العمل والإجراءات:**
-  1. **مصفوفة الثغرات الصارمة (VULNERABILITY MATRIX):** مسح إجباري لـ AndroidManifest والمكونات المكشوفة وتسريب البيانات.
-  2. **التحقق من صحة المدخلات وتشفير البيانات:** فحص تشفير البيانات الحساسة والجلسات وتأمين الوصول محلياً وسحابياً.</t>
+  1. **تفعيل الركائز الست لدرع الأمان (`vibe-coding-security-shield`):**
+     - **Semgrep (SAST):** فحص المنطق والأكواد المولدة بالذكاء الاصطناعي لمنع الحقن (Injection) والثغرات الإنشائية.
+     - **Gitleaks:** التحقق الصارم من انعدام تسريب المفاتيح ورموز الوصول السرية في الـ Staging وتاريخ الـ Git.
+     - **Trivy:** فحص التبعيات وصور Docker وكشف ثغرات CVEs وتوليد الـ SBOM.
+     - **OWASP ZAP (DAST):** الفحص الديناميكي للواجهات ونقاط الـ API بعد تشغيل التطبيق في بيئة الاختبار.
+     - **Checkov:** فحص أخطاء البنية التحتية والـ Misconfigurations في Dockerfile و Terraform.
+     - **Renovate:** أتمتة تحديثات التبعيات وسد الثغرات الأمنية دورياً عبر الـ PRs.
+  2. **مصفوفة الثغرات الصارمة (VULNERABILITY MATRIX):** مسح إجباري لـ AndroidManifest والمكونات المكشوفة وتسريب البيانات.
+  3. **التحقق من صحة المدخلات وتشفير البيانات:** فحص تشفير البيانات الحساسة والجلسات وتأمين الوصول محلياً وسحابياً.</t>
         </is>
       </c>
     </row>

--- a/HOOKS_GUIDE.xlsx
+++ b/HOOKS_GUIDE.xlsx
@@ -37,6 +37,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="27. خطاف الاستشارة الاستراتيج" sheetId="28" state="visible" r:id="rId28"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="28. خطاف ترحيل وتطهير أدوات ا" sheetId="29" state="visible" r:id="rId29"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="29. خطاف ترقية ومعايرة مصفوفة" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30. خطاف توجيه وتفعيل الأسطول" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="31. خطاف معاينة وتنسيق العمل " sheetId="32" state="visible" r:id="rId32"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -478,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1768,7 +1770,130 @@
      - استدعاء `convert_hooks_to_sheets.py` لتحديث مصنف `HOOKS_GUIDE.xlsx`.
      - إدراج الأمر الموجه في مصنف `مكتبة الأوامر.xlsx` تحت تبويب `CLI_Core.Claude`.
   5. **توثيق الذاكرة المستدامة (Memory Invariant):**
-     - تسجيل قرار ترقية المعمارية (ADR) في `MEMORY_STORE.md` محلياً وعالمياً.
+     - تسجيل قرار ترقية المعمارية (ADR) في `MEMORY_STORE.md` محلياً وعالمياً.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>30. خطاف توجيه وتفعيل الأسطول لأي مساحة عمل</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>وجه الأسطول, اربط الأسطول بالتطبيق, توجيه الأسطول للمشروع, استهدف هذا المشروع, target workspace fleet, fleet target app, ربط اللابتوب الثاني بالمشروع, الخطاف 30</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Opus 5.5 / Opus Max (Thinking)` 
+ البديل: `Gemini 3.8 Flash (High)`</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>[fleet-orchestrator], [devops-deployer], [code-architect], [prompt-engineer]</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>الكشف التلقائي عن مستودع مساحة العمل الحالية ونوع التقنية، وتوجيه ومزامنة عمال اللابتوب الثاني (G1, G2, G3, G4) لخدمة تطوير هذا التطبيق فورياً عبر GitHub و Tailscale مع سحب الفروع واعتمادها في قمرة القيادة.</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات الآلية بمجرد إطلاق الخطاف:**
+  1. **الكشف الذكي التلقائي عن مساحة العمل الحالية (Workspace Context Discovery):**
+     - استخراج عنوان المستودع المركزي عبر `git remote get-url origin`.
+     - استخراج الفرع النشط عبر `git rev-parse --abbrev-ref HEAD` (افتراضياً `main`).
+     - اكتشاف نوع وبيئة التطبيق تلقائياً (Tech Stack): أندرويد (Compose/Kotlin)، فلاتر (Flutter)، ويب (React/Next)، أو خادم (FastAPI/Node).
+  2. **تهيئة بنية أوامر الأسطول في المشروع الحالي (Fleet Orders Scaffolding):**
+     - إنشاء مجلدات العمل التنظيمية للمشروع إن لم تكن موجودة:
+       `fleet_orders/incoming/` و `fleet_orders/in_progress/` و `fleet_orders/completed/`.
+     - إنشاء وتحديث ملف استهداف الأسطول المحلي `fleet_target.json` لتوثيق معلمات الربط للمشروع الحالي.
+  3. **بوابة الاعتماد المعماري الإلزامية لـ Claude Code قبل التوجيه (Mandatory Claude Code Pre-Dispatch Gate) [حظر صارم]:**
+     - يُحظر منعاً باتاً إرسال أو مزامنة أي توجيه أو أمر عمل إلى اللابتوب الثاني (Machine 2) إلا بعد قيام **Claude Code CLI (Opus Max)** بمراجعة وتدقيق معلمات التوجيه ومطابقة المستودع وخطة التوزيع، وإصدار وسم الاعتماد الصريح: `[APPROVED FOR REMOTE DISPATCH]`.
+     - في حال غياب الاعتماد، يظل التوجيه في حالة مسودة معلقة (`DRAFT_PENDING_CLAUDE_APPROVAL`) وتُقفل قنوات الإرسال للابتوب الثاني لحماية بيئة الإنتاج من أي استهداف خاطئ أو تسريب للملفات المحجورة.
+  4. **التوجيه والمزامنة الآلية للعقدة البعيدة (Remote Node Synchronization):**
+     - فور صدور اعتماد Claude Code، يتم فحص جاهزية اللابتوب الثاني (`python tools/remote_fleet_dispatch.py --ping`).
+     - إرسال توجيه فوري للابتوب الثاني لربط وتحديث المستودع المستهدف وسحب الفرع النشط:
+       `ssh autovem-worker-01 "cd ~/projects &amp;&amp; git remote set-url origin &lt;target_repo&gt; &amp;&amp; git fetch origin"`.
+  5. **ربط وتنشيط لوحة التحكم المركزية (Fleet Cockpit Binding :8088):**
+     - ربط خادم لوحة التحكم ([http://localhost:8088](http://localhost:8088)) بمجلد أوامر مساحة العمل الحالية.
+     - تخصيص العمال الأربعة وفقاً لطبيعة التطبيق:
+       - `Worker G1` (UI / Frontend - Jetpack Compose / Web).
+       - `Worker G2` (Backend / APIs / Domain Logic).
+       - `Worker G3` (Database / Schemas / Migrations - OpenCode Zen).
+       - `Worker G4` (Large Context / Docs / Batch).
+  6. **تأكيد سريان الضوابط المعمارية واحتكار الاختبارات [C-21]:**
+     - إلزام عمال اللابتوب الثاني بإنتاج الكود في فروع الميزات (`fleet/&lt;feature&gt;`) ودفعها لـ GitHub، مع احتكار تشغيل الاختبارات والاعتماد النهائي `[APPROVED]` لـ Claude Code CLI على جهاز المطور الرئيسي.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>31. خطاف معاينة وتنسيق العمل الجماعي لأسطول الـ CLIs</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>معاينة العمل الجماعي للأسطول, تشغيل فريق الأسطول, fleet teamwork, fleet teamwork preview, فريق عمل الأسطول, تنسيق فريق الأسطول, الخطاف 31</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Opus 5.5 / Opus Max (Thinking)` 
+ البديل: `Gemini 3.8 Flash (High)`</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>[fleet-orchestrator], [code-architect], [agent-optimizer], [test-guard], [webapp-qa-tester]</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>تفعيل وإدارة فريق عمل الأسطول الموزع (Parallel Multi-CLI Teamwork) المستوحى من هندسة teamwork-preview، لتوزيع مهام الاستكشاف، البناء، المراجعة والفحص التنافسي واحتكار الاختبارات لـ Claude Code.</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>* **الفلسفة المستخلصة من الهندسة العكسية لـ Al Mustafa REA:**
+  - تحويل وتوزيع نمط العمل المتسلسل في أمر `teamwork-preview` الخاص بـ Antigravity (والذي يستهلك 7 أضعاف التوكنز داخل بيئة واحدة) إلى **فريق عمل أسطول متكامل ومتعدد الـ CLIs (Distributed Multi-CLI Teamwork)** يوزع الأدوار بذكاء واحترافية:
+    1. **قائد الأسطول والمنسق الأعلى (Master Orchestrator):** `Claude Code CLI (Opus 5.5 Max)` بالتعاون مع `Antigravity IDE` كقمرة قيادة تفاعلية وبصرية للمطور.
+    2. **مسار الاستكشاف والتفكيك المتوازي (Parallel Survey Explorers):**
+       - **المستكشف الأول (Frontend &amp; Assets):** `Antigravity CLI (agcli)` أو عامل جيميناي 1 (`Worker 1`).
+       - **المستكشف الثاني (Database &amp; Persistence):** `OpenCode CLI (GLM 5.3 Flash)` أو عامل جيميناي 2 (`Worker 2`).
+       - **المستكشف الثالث (Domain &amp; Compliance):** `OpenCode Meta Muse Spark 1.3` أو عامل جيميناي 3 (`Worker 3`).
+    3. **مسار التنفيذ الإنشائي بالدفعات (Milestone Implementation Workers):**
+       - **منفذ الواجهات:** `Antigravity CLI (agcli)` و `Cline CLI` لبناء المكونات وواجهات Compose/Web.
+       - **منفذ قواعد البيانات والخلفية:** `OpenCode CLI (GLM 5.3 Flash)` وفق قاعدة الدفعات الرباعية (Max 4 Files Per Batch) [C-78].
+       - **منفذ السقالات والسكربتات:** `OpenCode Meta Muse Spark 1.3`.
+    4. **مسار الفحص والمراجعة التنافسية (Adversarial Review &amp; Stress Testing Track):**
+       - **المراجع المعماري (Reviewer 1):** `OpenCode DeepSeek V4` لفحص الحدود المعمارية، عقود الواجهات، ومنع التكرار (DRY).
+       - **مراجع المعايير والـ RTL (Reviewer 2):** `Antigravity CLI (agcli)` لفحص التوافق اللغوي وتنسيق BiDi/RTL وسلامة معرفات DOM.
+       - **المتحدي الأول (Challenger 1):** `OpenCode CLI` لتوليد واختبار سيناريوهات الضغط والحدود القصوى للبيانات.
+       - **المتحدي الثاني (Challenger 2 - Browser QA):** `Antigravity CLI (agcli)` مع مهارة `webapp-qa-tester` (Playwright / Chrome DevTools) لفحص المتصفح الحقيقي بتكلفة $0.00 وفق القيد [C-96].
+    5. **المحقق الجنائي والاحتكار الحصري للاختبارات (Forensic Auditor &amp; Exclusive Test Monopoly):**
+       - `Claude Code CLI (Opus Max)` ينفذ الاختبارات التلقائية حصرياً (`unit`, `integration`, `e2e`) ويتحقق من انعدام التزييف (Zero Facades / Genuine Byte Sizes) ويصدر ختم الاعتماد الرسمي `[APPROVED]` في `GATE_STATUS.md`.
+* **طريقة العمل والإجراءات الآلية (Execution Flow):**
+  1. **التهيئة وسقالة مساحة العمل (`init`):**
+     - تشغيل `python tools/fleet_teamwork_orchestrator.py init --name "&lt;Project&gt;" --objective "&lt;Goal&gt;"`.
+     - إنشاء مجلد `.agents/fleet_teamwork/` وضمان اقتصاره الصارم على البيانات الوصفية (Metadata-Only) دون أي ملفات كود أو نسخ ثنائية.
+  2. **توليد أوامر التفويض المعيارية (`delegate`):**
+     - توليد موجهات التفويض للمنفذين باللغة الإنجليزية طبقاً لـ `Template 02: Task Delegation Protocol`.
+     - ضخ الموجهات عبر قنوات التدفق `stdin` بترميز UTF-8 طبقاً للقيد [C-91].
+  3. **إدارة البوابات وتوثيق القرارات (`verdict` &amp; `status`):**
+     - تحديث حالات البوابات في `GATE_STATUS.md` بعد كل جولة فحص (PASS / FAIL / FIX_REQUIRED).
+     - توثيق الدروس المستفادة والقرارات المعمارية في `MEMORY_STORE.md` محلياً وعالمياً.
 &lt;/div&gt;</t>
         </is>
       </c>
@@ -4152,7 +4277,250 @@
      - استدعاء `convert_hooks_to_sheets.py` لتحديث مصنف `HOOKS_GUIDE.xlsx`.
      - إدراج الأمر الموجه في مصنف `مكتبة الأوامر.xlsx` تحت تبويب `CLI_Core.Claude`.
   5. **توثيق الذاكرة المستدامة (Memory Invariant):**
-     - تسجيل قرار ترقية المعمارية (ADR) في `MEMORY_STORE.md` محلياً وعالمياً.
+     - تسجيل قرار ترقية المعمارية (ADR) في `MEMORY_STORE.md` محلياً وعالمياً.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>اسم الخطاف</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>المحفزات (الخطاف للنسخ)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>النموذج الأساسي والبديل</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>الوكلاء المسؤولون</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>الهدف الأساسي</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>الوصف والتفاصيل</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>30. خطاف توجيه وتفعيل الأسطول لأي مساحة عمل</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>وجه الأسطول, اربط الأسطول بالتطبيق, توجيه الأسطول للمشروع, استهدف هذا المشروع, target workspace fleet, fleet target app, ربط اللابتوب الثاني بالمشروع, الخطاف 30</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Opus 5.5 / Opus Max (Thinking)` 
+ البديل: `Gemini 3.8 Flash (High)`</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[fleet-orchestrator], [devops-deployer], [code-architect], [prompt-engineer]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>الكشف التلقائي عن مستودع مساحة العمل الحالية ونوع التقنية، وتوجيه ومزامنة عمال اللابتوب الثاني (G1, G2, G3, G4) لخدمة تطوير هذا التطبيق فورياً عبر GitHub و Tailscale مع سحب الفروع واعتمادها في قمرة القيادة.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>* **طريقة العمل والإجراءات الآلية بمجرد إطلاق الخطاف:**
+  1. **الكشف الذكي التلقائي عن مساحة العمل الحالية (Workspace Context Discovery):**
+     - استخراج عنوان المستودع المركزي عبر `git remote get-url origin`.
+     - استخراج الفرع النشط عبر `git rev-parse --abbrev-ref HEAD` (افتراضياً `main`).
+     - اكتشاف نوع وبيئة التطبيق تلقائياً (Tech Stack): أندرويد (Compose/Kotlin)، فلاتر (Flutter)، ويب (React/Next)، أو خادم (FastAPI/Node).
+  2. **تهيئة بنية أوامر الأسطول في المشروع الحالي (Fleet Orders Scaffolding):**
+     - إنشاء مجلدات العمل التنظيمية للمشروع إن لم تكن موجودة:
+       `fleet_orders/incoming/` و `fleet_orders/in_progress/` و `fleet_orders/completed/`.
+     - إنشاء وتحديث ملف استهداف الأسطول المحلي `fleet_target.json` لتوثيق معلمات الربط للمشروع الحالي.
+  3. **بوابة الاعتماد المعماري الإلزامية لـ Claude Code قبل التوجيه (Mandatory Claude Code Pre-Dispatch Gate) [حظر صارم]:**
+     - يُحظر منعاً باتاً إرسال أو مزامنة أي توجيه أو أمر عمل إلى اللابتوب الثاني (Machine 2) إلا بعد قيام **Claude Code CLI (Opus Max)** بمراجعة وتدقيق معلمات التوجيه ومطابقة المستودع وخطة التوزيع، وإصدار وسم الاعتماد الصريح: `[APPROVED FOR REMOTE DISPATCH]`.
+     - في حال غياب الاعتماد، يظل التوجيه في حالة مسودة معلقة (`DRAFT_PENDING_CLAUDE_APPROVAL`) وتُقفل قنوات الإرسال للابتوب الثاني لحماية بيئة الإنتاج من أي استهداف خاطئ أو تسريب للملفات المحجورة.
+  4. **التوجيه والمزامنة الآلية للعقدة البعيدة (Remote Node Synchronization):**
+     - فور صدور اعتماد Claude Code، يتم فحص جاهزية اللابتوب الثاني (`python tools/remote_fleet_dispatch.py --ping`).
+     - إرسال توجيه فوري للابتوب الثاني لربط وتحديث المستودع المستهدف وسحب الفرع النشط:
+       `ssh autovem-worker-01 "cd ~/projects &amp;&amp; git remote set-url origin &lt;target_repo&gt; &amp;&amp; git fetch origin"`.
+  5. **ربط وتنشيط لوحة التحكم المركزية (Fleet Cockpit Binding :8088):**
+     - ربط خادم لوحة التحكم ([http://localhost:8088](http://localhost:8088)) بمجلد أوامر مساحة العمل الحالية.
+     - تخصيص العمال الأربعة وفقاً لطبيعة التطبيق:
+       - `Worker G1` (UI / Frontend - Jetpack Compose / Web).
+       - `Worker G2` (Backend / APIs / Domain Logic).
+       - `Worker G3` (Database / Schemas / Migrations - OpenCode Zen).
+       - `Worker G4` (Large Context / Docs / Batch).
+  6. **تأكيد سريان الضوابط المعمارية واحتكار الاختبارات [C-21]:**
+     - إلزام عمال اللابتوب الثاني بإنتاج الكود في فروع الميزات (`fleet/&lt;feature&gt;`) ودفعها لـ GitHub، مع احتكار تشغيل الاختبارات والاعتماد النهائي `[APPROVED]` لـ Claude Code CLI على جهاز المطور الرئيسي.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>اسم الخطاف</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>المحفزات (الخطاف للنسخ)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>النموذج الأساسي والبديل</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>الوكلاء المسؤولون</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>الهدف الأساسي</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>الوصف والتفاصيل</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>31. خطاف معاينة وتنسيق العمل الجماعي لأسطول الـ CLIs</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>معاينة العمل الجماعي للأسطول, تشغيل فريق الأسطول, fleet teamwork, fleet teamwork preview, فريق عمل الأسطول, تنسيق فريق الأسطول, الخطاف 31</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>الأساسي: `Claude Opus 5.5 / Opus Max (Thinking)` 
+ البديل: `Gemini 3.8 Flash (High)`</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[fleet-orchestrator], [code-architect], [agent-optimizer], [test-guard], [webapp-qa-tester]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>تفعيل وإدارة فريق عمل الأسطول الموزع (Parallel Multi-CLI Teamwork) المستوحى من هندسة teamwork-preview، لتوزيع مهام الاستكشاف، البناء، المراجعة والفحص التنافسي واحتكار الاختبارات لـ Claude Code.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>* **الفلسفة المستخلصة من الهندسة العكسية لـ Al Mustafa REA:**
+  - تحويل وتوزيع نمط العمل المتسلسل في أمر `teamwork-preview` الخاص بـ Antigravity (والذي يستهلك 7 أضعاف التوكنز داخل بيئة واحدة) إلى **فريق عمل أسطول متكامل ومتعدد الـ CLIs (Distributed Multi-CLI Teamwork)** يوزع الأدوار بذكاء واحترافية:
+    1. **قائد الأسطول والمنسق الأعلى (Master Orchestrator):** `Claude Code CLI (Opus 5.5 Max)` بالتعاون مع `Antigravity IDE` كقمرة قيادة تفاعلية وبصرية للمطور.
+    2. **مسار الاستكشاف والتفكيك المتوازي (Parallel Survey Explorers):**
+       - **المستكشف الأول (Frontend &amp; Assets):** `Antigravity CLI (agcli)` أو عامل جيميناي 1 (`Worker 1`).
+       - **المستكشف الثاني (Database &amp; Persistence):** `OpenCode CLI (GLM 5.3 Flash)` أو عامل جيميناي 2 (`Worker 2`).
+       - **المستكشف الثالث (Domain &amp; Compliance):** `OpenCode Meta Muse Spark 1.3` أو عامل جيميناي 3 (`Worker 3`).
+    3. **مسار التنفيذ الإنشائي بالدفعات (Milestone Implementation Workers):**
+       - **منفذ الواجهات:** `Antigravity CLI (agcli)` و `Cline CLI` لبناء المكونات وواجهات Compose/Web.
+       - **منفذ قواعد البيانات والخلفية:** `OpenCode CLI (GLM 5.3 Flash)` وفق قاعدة الدفعات الرباعية (Max 4 Files Per Batch) [C-78].
+       - **منفذ السقالات والسكربتات:** `OpenCode Meta Muse Spark 1.3`.
+    4. **مسار الفحص والمراجعة التنافسية (Adversarial Review &amp; Stress Testing Track):**
+       - **المراجع المعماري (Reviewer 1):** `OpenCode DeepSeek V4` لفحص الحدود المعمارية، عقود الواجهات، ومنع التكرار (DRY).
+       - **مراجع المعايير والـ RTL (Reviewer 2):** `Antigravity CLI (agcli)` لفحص التوافق اللغوي وتنسيق BiDi/RTL وسلامة معرفات DOM.
+       - **المتحدي الأول (Challenger 1):** `OpenCode CLI` لتوليد واختبار سيناريوهات الضغط والحدود القصوى للبيانات.
+       - **المتحدي الثاني (Challenger 2 - Browser QA):** `Antigravity CLI (agcli)` مع مهارة `webapp-qa-tester` (Playwright / Chrome DevTools) لفحص المتصفح الحقيقي بتكلفة $0.00 وفق القيد [C-96].
+    5. **المحقق الجنائي والاحتكار الحصري للاختبارات (Forensic Auditor &amp; Exclusive Test Monopoly):**
+       - `Claude Code CLI (Opus Max)` ينفذ الاختبارات التلقائية حصرياً (`unit`, `integration`, `e2e`) ويتحقق من انعدام التزييف (Zero Facades / Genuine Byte Sizes) ويصدر ختم الاعتماد الرسمي `[APPROVED]` في `GATE_STATUS.md`.
+* **طريقة العمل والإجراءات الآلية (Execution Flow):**
+  1. **التهيئة وسقالة مساحة العمل (`init`):**
+     - تشغيل `python tools/fleet_teamwork_orchestrator.py init --name "&lt;Project&gt;" --objective "&lt;Goal&gt;"`.
+     - إنشاء مجلد `.agents/fleet_teamwork/` وضمان اقتصاره الصارم على البيانات الوصفية (Metadata-Only) دون أي ملفات كود أو نسخ ثنائية.
+  2. **توليد أوامر التفويض المعيارية (`delegate`):**
+     - توليد موجهات التفويض للمنفذين باللغة الإنجليزية طبقاً لـ `Template 02: Task Delegation Protocol`.
+     - ضخ الموجهات عبر قنوات التدفق `stdin` بترميز UTF-8 طبقاً للقيد [C-91].
+  3. **إدارة البوابات وتوثيق القرارات (`verdict` &amp; `status`):**
+     - تحديث حالات البوابات في `GATE_STATUS.md` بعد كل جولة فحص (PASS / FAIL / FIX_REQUIRED).
+     - توثيق الدروس المستفادة والقرارات المعمارية في `MEMORY_STORE.md` محلياً وعالمياً.
 &lt;/div&gt;</t>
         </is>
       </c>
